--- a/Versão5/ABNT/Ontologia_15965_1F.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_1F.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63B30F35-442C-4A0A-806E-7AC083570905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFA7A991-4667-4E30-8147-8E0D372FF3B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
@@ -2027,7 +2027,105 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{9B49B867-F029-4368-B154-870C7BE57F68}"/>
   </cellStyles>
-  <dxfs count="64">
+  <dxfs count="76">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -3948,31 +4046,31 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:W169" headerRowCount="0" totalsRowShown="0" headerRowDxfId="63" headerRowBorderDxfId="62" tableBorderDxfId="61" totalsRowBorderDxfId="60">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:W169" headerRowCount="0" totalsRowShown="0" headerRowDxfId="75" headerRowBorderDxfId="74" tableBorderDxfId="73" totalsRowBorderDxfId="72">
   <tableColumns count="23">
-    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="59" dataDxfId="58"/>
-    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="57" dataDxfId="56"/>
-    <tableColumn id="3" xr3:uid="{38346B1D-47C6-4B44-A19C-766D16435669}" name="Classe" headerRowDxfId="55" dataDxfId="54"/>
-    <tableColumn id="9" xr3:uid="{9B194C8C-85D6-4BE2-B1AE-E11E335186F0}" name="Coluna6" headerRowDxfId="53" dataDxfId="52"/>
-    <tableColumn id="8" xr3:uid="{6F1A2D13-ED4B-47DE-AFA9-D11431CAA734}" name="Coluna5" headerRowDxfId="51" dataDxfId="50"/>
-    <tableColumn id="15" xr3:uid="{0C0DAD0A-A76E-4555-A1F1-F78A8F1BE2C2}" name="Coluna4" headerRowDxfId="49" dataDxfId="48"/>
-    <tableColumn id="14" xr3:uid="{C073F03F-8B8F-474F-AF29-E26DD9C1B19A}" name="Coluna3" headerRowDxfId="47" dataDxfId="46"/>
-    <tableColumn id="11" xr3:uid="{AE04A63A-3540-4CF3-9D9A-59CD3577B22C}" name="Coluna2" headerRowDxfId="45" dataDxfId="44"/>
-    <tableColumn id="10" xr3:uid="{F50D06F5-DC15-417E-BE0C-A36478AC8A38}" name="Coluna1" headerRowDxfId="43" dataDxfId="42"/>
-    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="41" dataDxfId="40"/>
-    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="39" dataDxfId="38"/>
-    <tableColumn id="4" xr3:uid="{4DBCD72F-75DB-4B77-9F22-145D8C5CB683}" name="Coluna7" headerRowDxfId="37" dataDxfId="36"/>
-    <tableColumn id="5" xr3:uid="{E1CD8226-B80B-4618-B8C8-0FC41451C0A8}" name="Coluna8" headerRowDxfId="35" dataDxfId="34"/>
-    <tableColumn id="6" xr3:uid="{8E7C1DDF-1846-4221-9B0E-C7E4CC7EA057}" name="Coluna9" headerRowDxfId="33" dataDxfId="32"/>
-    <tableColumn id="7" xr3:uid="{3D7A485C-E68B-4D3B-888E-DCFC8EAEE60D}" name="Coluna10" headerRowDxfId="31" dataDxfId="30"/>
-    <tableColumn id="16" xr3:uid="{FECF52FB-CC27-4CA6-B622-AF9F7DB3B554}" name="Coluna11" headerRowDxfId="29" dataDxfId="28"/>
-    <tableColumn id="17" xr3:uid="{D79F8B63-2EF5-45DD-9134-450A005B41F4}" name="Coluna12" headerRowDxfId="27" dataDxfId="26"/>
-    <tableColumn id="18" xr3:uid="{DAFF39A1-0FA6-4AF0-A3B6-380882A29861}" name="Coluna13" headerRowDxfId="25" dataDxfId="24"/>
-    <tableColumn id="19" xr3:uid="{87AE1228-C62F-45E2-A7B1-A0914F89FBE3}" name="Coluna14" headerRowDxfId="23" dataDxfId="22"/>
-    <tableColumn id="20" xr3:uid="{85EAA474-6B84-4EF5-95FF-852AF2C5EA5E}" name="Coluna15" headerRowDxfId="21" dataDxfId="20"/>
-    <tableColumn id="21" xr3:uid="{5B15C019-4680-4877-A95B-F683BA0C59DD}" name="Coluna16" headerRowDxfId="19" dataDxfId="18"/>
-    <tableColumn id="22" xr3:uid="{5C11667F-4365-4FD8-A625-69FCEAC4D24C}" name="Coluna17" headerRowDxfId="17" dataDxfId="16"/>
-    <tableColumn id="23" xr3:uid="{38F8B48D-5280-437C-BB95-24A464DAF74A}" name="Coluna18" headerRowDxfId="15" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="71" dataDxfId="70"/>
+    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="69" dataDxfId="68"/>
+    <tableColumn id="3" xr3:uid="{38346B1D-47C6-4B44-A19C-766D16435669}" name="Classe" headerRowDxfId="67" dataDxfId="66"/>
+    <tableColumn id="9" xr3:uid="{9B194C8C-85D6-4BE2-B1AE-E11E335186F0}" name="Coluna6" headerRowDxfId="65" dataDxfId="64"/>
+    <tableColumn id="8" xr3:uid="{6F1A2D13-ED4B-47DE-AFA9-D11431CAA734}" name="Coluna5" headerRowDxfId="63" dataDxfId="62"/>
+    <tableColumn id="15" xr3:uid="{0C0DAD0A-A76E-4555-A1F1-F78A8F1BE2C2}" name="Coluna4" headerRowDxfId="61" dataDxfId="60"/>
+    <tableColumn id="14" xr3:uid="{C073F03F-8B8F-474F-AF29-E26DD9C1B19A}" name="Coluna3" headerRowDxfId="59" dataDxfId="58"/>
+    <tableColumn id="11" xr3:uid="{AE04A63A-3540-4CF3-9D9A-59CD3577B22C}" name="Coluna2" headerRowDxfId="57" dataDxfId="56"/>
+    <tableColumn id="10" xr3:uid="{F50D06F5-DC15-417E-BE0C-A36478AC8A38}" name="Coluna1" headerRowDxfId="55" dataDxfId="54"/>
+    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="53" dataDxfId="52"/>
+    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="51" dataDxfId="50"/>
+    <tableColumn id="4" xr3:uid="{4DBCD72F-75DB-4B77-9F22-145D8C5CB683}" name="Coluna7" headerRowDxfId="49" dataDxfId="48"/>
+    <tableColumn id="5" xr3:uid="{E1CD8226-B80B-4618-B8C8-0FC41451C0A8}" name="Coluna8" headerRowDxfId="47" dataDxfId="46"/>
+    <tableColumn id="6" xr3:uid="{8E7C1DDF-1846-4221-9B0E-C7E4CC7EA057}" name="Coluna9" headerRowDxfId="45" dataDxfId="44"/>
+    <tableColumn id="7" xr3:uid="{3D7A485C-E68B-4D3B-888E-DCFC8EAEE60D}" name="Coluna10" headerRowDxfId="43" dataDxfId="42"/>
+    <tableColumn id="16" xr3:uid="{FECF52FB-CC27-4CA6-B622-AF9F7DB3B554}" name="Coluna11" headerRowDxfId="41" dataDxfId="40"/>
+    <tableColumn id="17" xr3:uid="{D79F8B63-2EF5-45DD-9134-450A005B41F4}" name="Coluna12" headerRowDxfId="39" dataDxfId="38"/>
+    <tableColumn id="18" xr3:uid="{DAFF39A1-0FA6-4AF0-A3B6-380882A29861}" name="Coluna13" headerRowDxfId="37" dataDxfId="36"/>
+    <tableColumn id="19" xr3:uid="{87AE1228-C62F-45E2-A7B1-A0914F89FBE3}" name="Coluna14" headerRowDxfId="35" dataDxfId="34"/>
+    <tableColumn id="20" xr3:uid="{85EAA474-6B84-4EF5-95FF-852AF2C5EA5E}" name="Coluna15" headerRowDxfId="33" dataDxfId="32"/>
+    <tableColumn id="21" xr3:uid="{5B15C019-4680-4877-A95B-F683BA0C59DD}" name="Coluna16" headerRowDxfId="31" dataDxfId="30"/>
+    <tableColumn id="22" xr3:uid="{5C11667F-4365-4FD8-A625-69FCEAC4D24C}" name="Coluna17" headerRowDxfId="29" dataDxfId="28"/>
+    <tableColumn id="23" xr3:uid="{38F8B48D-5280-437C-BB95-24A464DAF74A}" name="Coluna18" headerRowDxfId="27" dataDxfId="26"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -4499,7 +4597,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46139.327093518521</v>
+        <v>46146.344277314813</v>
       </c>
       <c r="C18" s="54" t="s">
         <v>449</v>
@@ -4799,7 +4897,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="AA1:AA2">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4949,7 +5047,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4994,7 +5092,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5009,7 +5107,7 @@
   <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.69921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.19921875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="9.296875" style="2" customWidth="1"/>
     <col min="3" max="3" width="9.19921875" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="4.5" style="46" customWidth="1"/>
     <col min="5" max="5" width="9" style="46" bestFit="1" customWidth="1"/>
@@ -17033,59 +17131,62 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="D1">
-    <cfRule type="cellIs" dxfId="10" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="cellIs" dxfId="9" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="10" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1">
-    <cfRule type="cellIs" dxfId="8" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="9" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1">
-    <cfRule type="cellIs" dxfId="7" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="15" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1">
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P1">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:W1048576">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V1">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/Versão5/ABNT/Ontologia_15965_1F.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_1F.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BC2BF0F-EDD0-440C-83C1-D12E6658BD3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36466956-B812-4E4C-8F1B-84F850EFEA69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4188" uniqueCount="537">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4188" uniqueCount="538">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -1680,9 +1680,6 @@
     <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 5I.</t>
   </si>
   <si>
-    <t>"Classificação de objetos da construção - 1F"</t>
-  </si>
-  <si>
     <t>"Operação"</t>
   </si>
   <si>
@@ -1702,6 +1699,12 @@
   </si>
   <si>
     <t>"Licitação obra"</t>
+  </si>
+  <si>
+    <t>"Normas"</t>
+  </si>
+  <si>
+    <t>"Classificação de Projeto e Construção"</t>
   </si>
 </sst>
 </file>
@@ -2240,15 +2243,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{9B49B867-F029-4368-B154-870C7BE57F68}"/>
   </cellStyles>
-  <dxfs count="71">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
+  <dxfs count="70">
     <dxf>
       <font>
         <b val="0"/>
@@ -2418,160 +2413,6 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="6"/>
-        <color rgb="FF000000"/>
-        <name val="Arial Nova Cond Light"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFCC"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="6"/>
-        <color auto="1"/>
-        <name val="Arial Nova Cond Light"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFEF2CB"/>
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="6"/>
-        <color auto="1"/>
-        <name val="Arial Nova Cond"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="6"/>
-        <color auto="1"/>
-        <name val="Arial Nova Cond"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -3487,6 +3328,160 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="6"/>
+        <color auto="1"/>
+        <name val="Arial Nova Cond"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="6"/>
+        <color auto="1"/>
+        <name val="Arial Nova Cond Light"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEF2CB"/>
+          <bgColor theme="9" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="6"/>
+        <color auto="1"/>
+        <name val="Arial Nova Cond"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="6"/>
+        <color rgb="FF000000"/>
+        <name val="Arial Nova Cond Light"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFCC"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -4233,31 +4228,31 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:W169" headerRowCount="0" totalsRowShown="0" headerRowDxfId="70" headerRowBorderDxfId="69" tableBorderDxfId="68" totalsRowBorderDxfId="67">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:W169" headerRowCount="0" totalsRowShown="0" headerRowDxfId="69" headerRowBorderDxfId="68" tableBorderDxfId="67" totalsRowBorderDxfId="66">
   <tableColumns count="23">
-    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="66" dataDxfId="65"/>
-    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="64" dataDxfId="63"/>
-    <tableColumn id="3" xr3:uid="{38346B1D-47C6-4B44-A19C-766D16435669}" name="Classe" headerRowDxfId="62" dataDxfId="61"/>
-    <tableColumn id="9" xr3:uid="{9B194C8C-85D6-4BE2-B1AE-E11E335186F0}" name="Coluna6" headerRowDxfId="60" dataDxfId="59"/>
-    <tableColumn id="8" xr3:uid="{6F1A2D13-ED4B-47DE-AFA9-D11431CAA734}" name="Coluna5" headerRowDxfId="58" dataDxfId="57"/>
-    <tableColumn id="15" xr3:uid="{0C0DAD0A-A76E-4555-A1F1-F78A8F1BE2C2}" name="Coluna4" headerRowDxfId="56" dataDxfId="55"/>
-    <tableColumn id="14" xr3:uid="{C073F03F-8B8F-474F-AF29-E26DD9C1B19A}" name="Coluna3" headerRowDxfId="54" dataDxfId="53"/>
-    <tableColumn id="11" xr3:uid="{AE04A63A-3540-4CF3-9D9A-59CD3577B22C}" name="Coluna2" headerRowDxfId="52" dataDxfId="51"/>
-    <tableColumn id="10" xr3:uid="{F50D06F5-DC15-417E-BE0C-A36478AC8A38}" name="Coluna1" headerRowDxfId="50" dataDxfId="49"/>
-    <tableColumn id="25" xr3:uid="{FF2B42B8-007D-4B78-A1E6-70321A25B422}" name="Coluna20" headerRowDxfId="23" dataDxfId="22"/>
-    <tableColumn id="24" xr3:uid="{B0850B61-1B8F-418B-98C0-04AB09902DE3}" name="Coluna19" headerRowDxfId="24" dataDxfId="21"/>
-    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="48" dataDxfId="47"/>
-    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="46" dataDxfId="45"/>
-    <tableColumn id="6" xr3:uid="{8E7C1DDF-1846-4221-9B0E-C7E4CC7EA057}" name="Coluna9" headerRowDxfId="44" dataDxfId="43"/>
-    <tableColumn id="7" xr3:uid="{3D7A485C-E68B-4D3B-888E-DCFC8EAEE60D}" name="Coluna10" headerRowDxfId="42" dataDxfId="41"/>
-    <tableColumn id="16" xr3:uid="{FECF52FB-CC27-4CA6-B622-AF9F7DB3B554}" name="Coluna11" headerRowDxfId="40" dataDxfId="39"/>
-    <tableColumn id="17" xr3:uid="{D79F8B63-2EF5-45DD-9134-450A005B41F4}" name="Coluna12" headerRowDxfId="38" dataDxfId="37"/>
-    <tableColumn id="18" xr3:uid="{DAFF39A1-0FA6-4AF0-A3B6-380882A29861}" name="Coluna13" headerRowDxfId="36" dataDxfId="35"/>
-    <tableColumn id="19" xr3:uid="{87AE1228-C62F-45E2-A7B1-A0914F89FBE3}" name="Coluna14" headerRowDxfId="34" dataDxfId="33"/>
-    <tableColumn id="20" xr3:uid="{85EAA474-6B84-4EF5-95FF-852AF2C5EA5E}" name="Coluna15" headerRowDxfId="32" dataDxfId="31"/>
-    <tableColumn id="21" xr3:uid="{5B15C019-4680-4877-A95B-F683BA0C59DD}" name="Coluna16" headerRowDxfId="30" dataDxfId="29"/>
-    <tableColumn id="22" xr3:uid="{5C11667F-4365-4FD8-A625-69FCEAC4D24C}" name="Coluna17" headerRowDxfId="28" dataDxfId="27"/>
-    <tableColumn id="23" xr3:uid="{38F8B48D-5280-437C-BB95-24A464DAF74A}" name="Coluna18" headerRowDxfId="26" dataDxfId="25"/>
+    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="65" dataDxfId="64"/>
+    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="63" dataDxfId="62"/>
+    <tableColumn id="3" xr3:uid="{38346B1D-47C6-4B44-A19C-766D16435669}" name="Classe" headerRowDxfId="61" dataDxfId="60"/>
+    <tableColumn id="9" xr3:uid="{9B194C8C-85D6-4BE2-B1AE-E11E335186F0}" name="Coluna6" headerRowDxfId="59" dataDxfId="58"/>
+    <tableColumn id="8" xr3:uid="{6F1A2D13-ED4B-47DE-AFA9-D11431CAA734}" name="Coluna5" headerRowDxfId="57" dataDxfId="56"/>
+    <tableColumn id="15" xr3:uid="{0C0DAD0A-A76E-4555-A1F1-F78A8F1BE2C2}" name="Coluna4" headerRowDxfId="55" dataDxfId="54"/>
+    <tableColumn id="14" xr3:uid="{C073F03F-8B8F-474F-AF29-E26DD9C1B19A}" name="Coluna3" headerRowDxfId="53" dataDxfId="52"/>
+    <tableColumn id="11" xr3:uid="{AE04A63A-3540-4CF3-9D9A-59CD3577B22C}" name="Coluna2" headerRowDxfId="51" dataDxfId="50"/>
+    <tableColumn id="10" xr3:uid="{F50D06F5-DC15-417E-BE0C-A36478AC8A38}" name="Coluna1" headerRowDxfId="49" dataDxfId="48"/>
+    <tableColumn id="25" xr3:uid="{FF2B42B8-007D-4B78-A1E6-70321A25B422}" name="Coluna20" headerRowDxfId="47" dataDxfId="46"/>
+    <tableColumn id="24" xr3:uid="{B0850B61-1B8F-418B-98C0-04AB09902DE3}" name="Coluna19" headerRowDxfId="45" dataDxfId="44"/>
+    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="43" dataDxfId="42"/>
+    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="41" dataDxfId="40"/>
+    <tableColumn id="6" xr3:uid="{8E7C1DDF-1846-4221-9B0E-C7E4CC7EA057}" name="Coluna9" headerRowDxfId="39" dataDxfId="38"/>
+    <tableColumn id="7" xr3:uid="{3D7A485C-E68B-4D3B-888E-DCFC8EAEE60D}" name="Coluna10" headerRowDxfId="37" dataDxfId="36"/>
+    <tableColumn id="16" xr3:uid="{FECF52FB-CC27-4CA6-B622-AF9F7DB3B554}" name="Coluna11" headerRowDxfId="35" dataDxfId="34"/>
+    <tableColumn id="17" xr3:uid="{D79F8B63-2EF5-45DD-9134-450A005B41F4}" name="Coluna12" headerRowDxfId="33" dataDxfId="32"/>
+    <tableColumn id="18" xr3:uid="{DAFF39A1-0FA6-4AF0-A3B6-380882A29861}" name="Coluna13" headerRowDxfId="31" dataDxfId="30"/>
+    <tableColumn id="19" xr3:uid="{87AE1228-C62F-45E2-A7B1-A0914F89FBE3}" name="Coluna14" headerRowDxfId="29" dataDxfId="28"/>
+    <tableColumn id="20" xr3:uid="{85EAA474-6B84-4EF5-95FF-852AF2C5EA5E}" name="Coluna15" headerRowDxfId="27" dataDxfId="26"/>
+    <tableColumn id="21" xr3:uid="{5B15C019-4680-4877-A95B-F683BA0C59DD}" name="Coluna16" headerRowDxfId="25" dataDxfId="24"/>
+    <tableColumn id="22" xr3:uid="{5C11667F-4365-4FD8-A625-69FCEAC4D24C}" name="Coluna17" headerRowDxfId="23" dataDxfId="22"/>
+    <tableColumn id="23" xr3:uid="{38F8B48D-5280-437C-BB95-24A464DAF74A}" name="Coluna18" headerRowDxfId="21" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -4784,7 +4779,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46148.387493402777</v>
+        <v>46148.570963773149</v>
       </c>
       <c r="C18" s="48" t="s">
         <v>436</v>
@@ -6639,18 +6634,18 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A19">
-    <cfRule type="cellIs" dxfId="20" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="19" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA1:AA19">
-    <cfRule type="cellIs" dxfId="15" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6800,7 +6795,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6845,7 +6840,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6867,9 +6862,9 @@
     <col min="6" max="6" width="4" style="40" customWidth="1"/>
     <col min="7" max="7" width="6.83203125" style="40" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="3.5" style="40" customWidth="1"/>
-    <col min="9" max="9" width="24.33203125" style="40" customWidth="1"/>
+    <col min="9" max="9" width="7.1640625" style="40" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="5" style="40" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19" style="40" customWidth="1"/>
+    <col min="11" max="11" width="20.1640625" style="40" customWidth="1"/>
     <col min="12" max="12" width="5.6640625" style="40" customWidth="1"/>
     <col min="13" max="13" width="36" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="17" width="8.83203125" style="40" customWidth="1"/>
@@ -6970,22 +6965,22 @@
         <v>372</v>
       </c>
       <c r="F2" s="51" t="s">
-        <v>364</v>
+        <v>191</v>
       </c>
       <c r="G2" s="52" t="s">
-        <v>441</v>
+        <v>191</v>
       </c>
       <c r="H2" s="51" t="s">
         <v>366</v>
       </c>
       <c r="I2" s="52" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="J2" s="51" t="s">
         <v>426</v>
       </c>
       <c r="K2" s="52" t="s">
-        <v>425</v>
+        <v>537</v>
       </c>
       <c r="L2" s="38" t="s">
         <v>1</v>
@@ -7046,17 +7041,17 @@
       <c r="G3" s="41" t="s">
         <v>365</v>
       </c>
-      <c r="H3" s="38" t="s">
+      <c r="H3" s="51" t="s">
         <v>366</v>
       </c>
       <c r="I3" s="52" t="s">
-        <v>529</v>
-      </c>
-      <c r="J3" s="38" t="s">
+        <v>536</v>
+      </c>
+      <c r="J3" s="51" t="s">
         <v>426</v>
       </c>
       <c r="K3" s="52" t="s">
-        <v>425</v>
+        <v>537</v>
       </c>
       <c r="L3" s="38" t="s">
         <v>1</v>
@@ -7117,17 +7112,17 @@
       <c r="G4" s="41" t="s">
         <v>365</v>
       </c>
-      <c r="H4" s="38" t="s">
+      <c r="H4" s="51" t="s">
         <v>366</v>
       </c>
       <c r="I4" s="52" t="s">
-        <v>529</v>
-      </c>
-      <c r="J4" s="38" t="s">
+        <v>536</v>
+      </c>
+      <c r="J4" s="51" t="s">
         <v>426</v>
       </c>
       <c r="K4" s="52" t="s">
-        <v>425</v>
+        <v>537</v>
       </c>
       <c r="L4" s="38" t="s">
         <v>1</v>
@@ -7198,7 +7193,7 @@
         <v>426</v>
       </c>
       <c r="K5" s="39" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="L5" s="38" t="s">
         <v>1</v>
@@ -7269,7 +7264,7 @@
         <v>426</v>
       </c>
       <c r="K6" s="39" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="L6" s="38" t="s">
         <v>1</v>
@@ -7340,7 +7335,7 @@
         <v>426</v>
       </c>
       <c r="K7" s="39" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="L7" s="38" t="s">
         <v>1</v>
@@ -7411,7 +7406,7 @@
         <v>426</v>
       </c>
       <c r="K8" s="39" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="L8" s="38" t="s">
         <v>1</v>
@@ -7482,7 +7477,7 @@
         <v>426</v>
       </c>
       <c r="K9" s="39" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="L9" s="38" t="s">
         <v>1</v>
@@ -7553,7 +7548,7 @@
         <v>426</v>
       </c>
       <c r="K10" s="39" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="L10" s="38" t="s">
         <v>1</v>
@@ -7624,7 +7619,7 @@
         <v>426</v>
       </c>
       <c r="K11" s="39" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="L11" s="38" t="s">
         <v>1</v>
@@ -7695,7 +7690,7 @@
         <v>426</v>
       </c>
       <c r="K12" s="39" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="L12" s="38" t="s">
         <v>1</v>
@@ -7766,7 +7761,7 @@
         <v>426</v>
       </c>
       <c r="K13" s="39" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="L13" s="38" t="s">
         <v>1</v>
@@ -7837,7 +7832,7 @@
         <v>426</v>
       </c>
       <c r="K14" s="39" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="L14" s="38" t="s">
         <v>1</v>
@@ -7908,7 +7903,7 @@
         <v>426</v>
       </c>
       <c r="K15" s="39" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="L15" s="38" t="s">
         <v>1</v>
@@ -7979,7 +7974,7 @@
         <v>426</v>
       </c>
       <c r="K16" s="39" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="L16" s="38" t="s">
         <v>1</v>
@@ -8050,7 +8045,7 @@
         <v>426</v>
       </c>
       <c r="K17" s="39" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="L17" s="38" t="s">
         <v>1</v>
@@ -8121,7 +8116,7 @@
         <v>426</v>
       </c>
       <c r="K18" s="39" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="L18" s="38" t="s">
         <v>1</v>
@@ -8192,7 +8187,7 @@
         <v>426</v>
       </c>
       <c r="K19" s="39" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="L19" s="38" t="s">
         <v>1</v>
@@ -8263,7 +8258,7 @@
         <v>426</v>
       </c>
       <c r="K20" s="39" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="L20" s="38" t="s">
         <v>1</v>
@@ -8334,7 +8329,7 @@
         <v>426</v>
       </c>
       <c r="K21" s="39" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="L21" s="38" t="s">
         <v>1</v>
@@ -8405,7 +8400,7 @@
         <v>426</v>
       </c>
       <c r="K22" s="39" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="L22" s="38" t="s">
         <v>1</v>
@@ -8476,7 +8471,7 @@
         <v>426</v>
       </c>
       <c r="K23" s="39" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="L23" s="38" t="s">
         <v>1</v>
@@ -8547,7 +8542,7 @@
         <v>426</v>
       </c>
       <c r="K24" s="39" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="L24" s="38" t="s">
         <v>1</v>
@@ -8618,7 +8613,7 @@
         <v>426</v>
       </c>
       <c r="K25" s="39" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="L25" s="38" t="s">
         <v>1</v>
@@ -8689,7 +8684,7 @@
         <v>426</v>
       </c>
       <c r="K26" s="39" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="L26" s="38" t="s">
         <v>1</v>
@@ -8760,7 +8755,7 @@
         <v>426</v>
       </c>
       <c r="K27" s="39" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="L27" s="38" t="s">
         <v>1</v>
@@ -8831,7 +8826,7 @@
         <v>426</v>
       </c>
       <c r="K28" s="39" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="L28" s="38" t="s">
         <v>1</v>
@@ -8902,7 +8897,7 @@
         <v>426</v>
       </c>
       <c r="K29" s="39" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="L29" s="38" t="s">
         <v>1</v>
@@ -8973,7 +8968,7 @@
         <v>426</v>
       </c>
       <c r="K30" s="39" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="L30" s="38" t="s">
         <v>1</v>
@@ -9044,7 +9039,7 @@
         <v>426</v>
       </c>
       <c r="K31" s="39" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="L31" s="38" t="s">
         <v>1</v>
@@ -9115,7 +9110,7 @@
         <v>426</v>
       </c>
       <c r="K32" s="39" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="L32" s="38" t="s">
         <v>1</v>
@@ -9186,7 +9181,7 @@
         <v>426</v>
       </c>
       <c r="K33" s="39" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="L33" s="38" t="s">
         <v>1</v>
@@ -9257,7 +9252,7 @@
         <v>426</v>
       </c>
       <c r="K34" s="39" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="L34" s="38" t="s">
         <v>1</v>
@@ -9328,7 +9323,7 @@
         <v>426</v>
       </c>
       <c r="K35" s="39" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="L35" s="38" t="s">
         <v>1</v>
@@ -9399,7 +9394,7 @@
         <v>426</v>
       </c>
       <c r="K36" s="39" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="L36" s="38" t="s">
         <v>1</v>
@@ -9470,7 +9465,7 @@
         <v>426</v>
       </c>
       <c r="K37" s="39" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="L37" s="38" t="s">
         <v>1</v>
@@ -9541,7 +9536,7 @@
         <v>426</v>
       </c>
       <c r="K38" s="39" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="L38" s="38" t="s">
         <v>1</v>
@@ -9612,7 +9607,7 @@
         <v>426</v>
       </c>
       <c r="K39" s="39" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="L39" s="38" t="s">
         <v>1</v>
@@ -9683,7 +9678,7 @@
         <v>426</v>
       </c>
       <c r="K40" s="39" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="L40" s="38" t="s">
         <v>1</v>
@@ -9754,7 +9749,7 @@
         <v>426</v>
       </c>
       <c r="K41" s="39" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="L41" s="38" t="s">
         <v>1</v>
@@ -9825,7 +9820,7 @@
         <v>426</v>
       </c>
       <c r="K42" s="39" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="L42" s="38" t="s">
         <v>1</v>
@@ -9896,7 +9891,7 @@
         <v>426</v>
       </c>
       <c r="K43" s="39" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="L43" s="38" t="s">
         <v>1</v>
@@ -9967,7 +9962,7 @@
         <v>426</v>
       </c>
       <c r="K44" s="39" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="L44" s="38" t="s">
         <v>1</v>
@@ -10038,7 +10033,7 @@
         <v>426</v>
       </c>
       <c r="K45" s="39" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="L45" s="38" t="s">
         <v>1</v>
@@ -10109,7 +10104,7 @@
         <v>426</v>
       </c>
       <c r="K46" s="39" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="L46" s="38" t="s">
         <v>1</v>
@@ -10180,7 +10175,7 @@
         <v>426</v>
       </c>
       <c r="K47" s="39" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="L47" s="38" t="s">
         <v>1</v>
@@ -10251,7 +10246,7 @@
         <v>426</v>
       </c>
       <c r="K48" s="39" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="L48" s="38" t="s">
         <v>1</v>
@@ -10322,7 +10317,7 @@
         <v>426</v>
       </c>
       <c r="K49" s="39" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="L49" s="38" t="s">
         <v>1</v>
@@ -10393,7 +10388,7 @@
         <v>426</v>
       </c>
       <c r="K50" s="39" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="L50" s="38" t="s">
         <v>1</v>
@@ -10464,7 +10459,7 @@
         <v>426</v>
       </c>
       <c r="K51" s="39" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="L51" s="38" t="s">
         <v>1</v>
@@ -12452,7 +12447,7 @@
         <v>426</v>
       </c>
       <c r="K79" s="39" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="L79" s="38" t="s">
         <v>1</v>
@@ -12523,7 +12518,7 @@
         <v>426</v>
       </c>
       <c r="K80" s="39" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="L80" s="38" t="s">
         <v>1</v>
@@ -12594,7 +12589,7 @@
         <v>426</v>
       </c>
       <c r="K81" s="39" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="L81" s="38" t="s">
         <v>1</v>
@@ -12665,7 +12660,7 @@
         <v>426</v>
       </c>
       <c r="K82" s="39" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="L82" s="38" t="s">
         <v>1</v>
@@ -12736,7 +12731,7 @@
         <v>426</v>
       </c>
       <c r="K83" s="39" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="L83" s="38" t="s">
         <v>1</v>
@@ -12807,7 +12802,7 @@
         <v>426</v>
       </c>
       <c r="K84" s="39" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="L84" s="38" t="s">
         <v>1</v>
@@ -12878,7 +12873,7 @@
         <v>426</v>
       </c>
       <c r="K85" s="39" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="L85" s="38" t="s">
         <v>1</v>
@@ -12949,7 +12944,7 @@
         <v>426</v>
       </c>
       <c r="K86" s="39" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="L86" s="38" t="s">
         <v>1</v>
@@ -13020,7 +13015,7 @@
         <v>426</v>
       </c>
       <c r="K87" s="39" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="L87" s="38" t="s">
         <v>1</v>
@@ -13091,7 +13086,7 @@
         <v>426</v>
       </c>
       <c r="K88" s="39" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="L88" s="38" t="s">
         <v>1</v>
@@ -13162,7 +13157,7 @@
         <v>426</v>
       </c>
       <c r="K89" s="39" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="L89" s="38" t="s">
         <v>1</v>
@@ -13233,7 +13228,7 @@
         <v>426</v>
       </c>
       <c r="K90" s="39" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="L90" s="38" t="s">
         <v>1</v>
@@ -13304,7 +13299,7 @@
         <v>426</v>
       </c>
       <c r="K91" s="39" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="L91" s="38" t="s">
         <v>1</v>
@@ -13375,7 +13370,7 @@
         <v>426</v>
       </c>
       <c r="K92" s="39" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="L92" s="38" t="s">
         <v>1</v>
@@ -13446,7 +13441,7 @@
         <v>426</v>
       </c>
       <c r="K93" s="39" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="L93" s="38" t="s">
         <v>1</v>
@@ -13517,7 +13512,7 @@
         <v>426</v>
       </c>
       <c r="K94" s="39" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="L94" s="38" t="s">
         <v>1</v>
@@ -13588,7 +13583,7 @@
         <v>426</v>
       </c>
       <c r="K95" s="39" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="L95" s="38" t="s">
         <v>1</v>
@@ -13659,7 +13654,7 @@
         <v>426</v>
       </c>
       <c r="K96" s="39" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="L96" s="38" t="s">
         <v>1</v>
@@ -13730,7 +13725,7 @@
         <v>426</v>
       </c>
       <c r="K97" s="39" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="L97" s="38" t="s">
         <v>1</v>
@@ -13801,7 +13796,7 @@
         <v>426</v>
       </c>
       <c r="K98" s="39" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="L98" s="38" t="s">
         <v>1</v>
@@ -13872,7 +13867,7 @@
         <v>426</v>
       </c>
       <c r="K99" s="39" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="L99" s="38" t="s">
         <v>1</v>
@@ -13943,7 +13938,7 @@
         <v>426</v>
       </c>
       <c r="K100" s="39" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="L100" s="38" t="s">
         <v>1</v>
@@ -14014,7 +14009,7 @@
         <v>426</v>
       </c>
       <c r="K101" s="39" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="L101" s="38" t="s">
         <v>1</v>
@@ -14085,7 +14080,7 @@
         <v>426</v>
       </c>
       <c r="K102" s="39" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="L102" s="38" t="s">
         <v>1</v>
@@ -14156,7 +14151,7 @@
         <v>426</v>
       </c>
       <c r="K103" s="39" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="L103" s="38" t="s">
         <v>1</v>
@@ -14227,7 +14222,7 @@
         <v>426</v>
       </c>
       <c r="K104" s="39" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="L104" s="38" t="s">
         <v>1</v>
@@ -14298,7 +14293,7 @@
         <v>426</v>
       </c>
       <c r="K105" s="39" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="L105" s="38" t="s">
         <v>1</v>
@@ -14369,7 +14364,7 @@
         <v>426</v>
       </c>
       <c r="K106" s="39" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="L106" s="38" t="s">
         <v>1</v>
@@ -14440,7 +14435,7 @@
         <v>426</v>
       </c>
       <c r="K107" s="39" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="L107" s="38" t="s">
         <v>1</v>
@@ -14511,7 +14506,7 @@
         <v>426</v>
       </c>
       <c r="K108" s="39" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L108" s="38" t="s">
         <v>1</v>
@@ -14582,7 +14577,7 @@
         <v>426</v>
       </c>
       <c r="K109" s="39" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L109" s="38" t="s">
         <v>1</v>
@@ -14653,7 +14648,7 @@
         <v>426</v>
       </c>
       <c r="K110" s="39" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L110" s="38" t="s">
         <v>1</v>
@@ -14724,7 +14719,7 @@
         <v>426</v>
       </c>
       <c r="K111" s="39" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L111" s="38" t="s">
         <v>1</v>
@@ -14795,7 +14790,7 @@
         <v>426</v>
       </c>
       <c r="K112" s="39" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L112" s="38" t="s">
         <v>1</v>
@@ -14866,7 +14861,7 @@
         <v>426</v>
       </c>
       <c r="K113" s="39" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L113" s="38" t="s">
         <v>1</v>
@@ -14937,7 +14932,7 @@
         <v>426</v>
       </c>
       <c r="K114" s="39" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L114" s="38" t="s">
         <v>1</v>
@@ -15008,7 +15003,7 @@
         <v>426</v>
       </c>
       <c r="K115" s="39" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L115" s="38" t="s">
         <v>1</v>
@@ -15079,7 +15074,7 @@
         <v>426</v>
       </c>
       <c r="K116" s="39" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L116" s="38" t="s">
         <v>1</v>
@@ -15150,7 +15145,7 @@
         <v>426</v>
       </c>
       <c r="K117" s="39" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L117" s="38" t="s">
         <v>1</v>
@@ -15221,7 +15216,7 @@
         <v>426</v>
       </c>
       <c r="K118" s="39" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L118" s="38" t="s">
         <v>1</v>
@@ -15292,7 +15287,7 @@
         <v>426</v>
       </c>
       <c r="K119" s="39" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L119" s="38" t="s">
         <v>1</v>
@@ -15363,7 +15358,7 @@
         <v>426</v>
       </c>
       <c r="K120" s="39" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L120" s="38" t="s">
         <v>1</v>
@@ -15434,7 +15429,7 @@
         <v>426</v>
       </c>
       <c r="K121" s="39" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L121" s="38" t="s">
         <v>1</v>
@@ -15505,7 +15500,7 @@
         <v>426</v>
       </c>
       <c r="K122" s="39" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L122" s="38" t="s">
         <v>1</v>
@@ -15576,7 +15571,7 @@
         <v>426</v>
       </c>
       <c r="K123" s="39" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L123" s="38" t="s">
         <v>1</v>
@@ -15647,7 +15642,7 @@
         <v>426</v>
       </c>
       <c r="K124" s="39" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L124" s="38" t="s">
         <v>1</v>
@@ -15718,7 +15713,7 @@
         <v>426</v>
       </c>
       <c r="K125" s="39" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L125" s="38" t="s">
         <v>1</v>
@@ -15789,7 +15784,7 @@
         <v>426</v>
       </c>
       <c r="K126" s="39" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L126" s="38" t="s">
         <v>1</v>
@@ -15860,7 +15855,7 @@
         <v>426</v>
       </c>
       <c r="K127" s="39" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L127" s="38" t="s">
         <v>1</v>
@@ -15931,7 +15926,7 @@
         <v>426</v>
       </c>
       <c r="K128" s="39" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L128" s="38" t="s">
         <v>1</v>
@@ -16002,7 +15997,7 @@
         <v>426</v>
       </c>
       <c r="K129" s="39" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L129" s="38" t="s">
         <v>1</v>
@@ -16073,7 +16068,7 @@
         <v>426</v>
       </c>
       <c r="K130" s="39" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L130" s="38" t="s">
         <v>1</v>
@@ -16144,7 +16139,7 @@
         <v>426</v>
       </c>
       <c r="K131" s="39" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L131" s="38" t="s">
         <v>1</v>
@@ -16215,7 +16210,7 @@
         <v>426</v>
       </c>
       <c r="K132" s="39" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L132" s="38" t="s">
         <v>1</v>
@@ -16286,7 +16281,7 @@
         <v>426</v>
       </c>
       <c r="K133" s="39" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L133" s="38" t="s">
         <v>1</v>
@@ -16357,7 +16352,7 @@
         <v>426</v>
       </c>
       <c r="K134" s="39" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L134" s="38" t="s">
         <v>1</v>
@@ -16428,7 +16423,7 @@
         <v>426</v>
       </c>
       <c r="K135" s="39" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L135" s="38" t="s">
         <v>1</v>
@@ -16499,7 +16494,7 @@
         <v>426</v>
       </c>
       <c r="K136" s="39" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L136" s="38" t="s">
         <v>1</v>
@@ -16570,7 +16565,7 @@
         <v>426</v>
       </c>
       <c r="K137" s="39" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L137" s="38" t="s">
         <v>1</v>
@@ -16641,7 +16636,7 @@
         <v>426</v>
       </c>
       <c r="K138" s="39" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="L138" s="38" t="s">
         <v>1</v>
@@ -16712,7 +16707,7 @@
         <v>426</v>
       </c>
       <c r="K139" s="39" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="L139" s="38" t="s">
         <v>1</v>
@@ -16783,7 +16778,7 @@
         <v>426</v>
       </c>
       <c r="K140" s="39" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="L140" s="38" t="s">
         <v>1</v>
@@ -16854,7 +16849,7 @@
         <v>426</v>
       </c>
       <c r="K141" s="39" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="L141" s="38" t="s">
         <v>1</v>
@@ -16925,7 +16920,7 @@
         <v>426</v>
       </c>
       <c r="K142" s="39" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="L142" s="38" t="s">
         <v>1</v>
@@ -16996,7 +16991,7 @@
         <v>426</v>
       </c>
       <c r="K143" s="39" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="L143" s="38" t="s">
         <v>1</v>
@@ -17067,7 +17062,7 @@
         <v>426</v>
       </c>
       <c r="K144" s="39" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="L144" s="38" t="s">
         <v>1</v>
@@ -17138,7 +17133,7 @@
         <v>426</v>
       </c>
       <c r="K145" s="39" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="L145" s="38" t="s">
         <v>1</v>
@@ -17209,7 +17204,7 @@
         <v>426</v>
       </c>
       <c r="K146" s="39" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="L146" s="38" t="s">
         <v>1</v>
@@ -17280,7 +17275,7 @@
         <v>426</v>
       </c>
       <c r="K147" s="39" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="L147" s="38" t="s">
         <v>1</v>
@@ -17351,7 +17346,7 @@
         <v>426</v>
       </c>
       <c r="K148" s="39" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="L148" s="38" t="s">
         <v>1</v>
@@ -17422,7 +17417,7 @@
         <v>426</v>
       </c>
       <c r="K149" s="39" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="L149" s="38" t="s">
         <v>1</v>
@@ -17493,7 +17488,7 @@
         <v>426</v>
       </c>
       <c r="K150" s="39" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="L150" s="38" t="s">
         <v>1</v>
@@ -17564,7 +17559,7 @@
         <v>426</v>
       </c>
       <c r="K151" s="39" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="L151" s="38" t="s">
         <v>1</v>
@@ -17635,7 +17630,7 @@
         <v>426</v>
       </c>
       <c r="K152" s="39" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="L152" s="38" t="s">
         <v>1</v>
@@ -17706,7 +17701,7 @@
         <v>426</v>
       </c>
       <c r="K153" s="39" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="L153" s="38" t="s">
         <v>1</v>
@@ -17777,7 +17772,7 @@
         <v>426</v>
       </c>
       <c r="K154" s="39" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="L154" s="38" t="s">
         <v>1</v>
@@ -17848,7 +17843,7 @@
         <v>426</v>
       </c>
       <c r="K155" s="39" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="L155" s="38" t="s">
         <v>1</v>
@@ -17919,7 +17914,7 @@
         <v>426</v>
       </c>
       <c r="K156" s="39" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="L156" s="38" t="s">
         <v>1</v>
@@ -17990,7 +17985,7 @@
         <v>426</v>
       </c>
       <c r="K157" s="39" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="L157" s="38" t="s">
         <v>1</v>
@@ -18061,7 +18056,7 @@
         <v>426</v>
       </c>
       <c r="K158" s="39" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="L158" s="38" t="s">
         <v>1</v>
@@ -18132,7 +18127,7 @@
         <v>426</v>
       </c>
       <c r="K159" s="39" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="L159" s="38" t="s">
         <v>1</v>
@@ -18203,7 +18198,7 @@
         <v>426</v>
       </c>
       <c r="K160" s="39" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="L160" s="38" t="s">
         <v>1</v>
@@ -18274,7 +18269,7 @@
         <v>426</v>
       </c>
       <c r="K161" s="39" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="L161" s="38" t="s">
         <v>1</v>
@@ -18345,7 +18340,7 @@
         <v>426</v>
       </c>
       <c r="K162" s="39" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="L162" s="38" t="s">
         <v>1</v>
@@ -18416,7 +18411,7 @@
         <v>426</v>
       </c>
       <c r="K163" s="39" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="L163" s="38" t="s">
         <v>1</v>
@@ -18487,7 +18482,7 @@
         <v>426</v>
       </c>
       <c r="K164" s="39" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="L164" s="38" t="s">
         <v>1</v>
@@ -18558,7 +18553,7 @@
         <v>426</v>
       </c>
       <c r="K165" s="39" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="L165" s="38" t="s">
         <v>1</v>
@@ -18629,7 +18624,7 @@
         <v>426</v>
       </c>
       <c r="K166" s="39" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="L166" s="38" t="s">
         <v>1</v>
@@ -18700,7 +18695,7 @@
         <v>426</v>
       </c>
       <c r="K167" s="39" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="L167" s="38" t="s">
         <v>1</v>
@@ -18771,7 +18766,7 @@
         <v>426</v>
       </c>
       <c r="K168" s="39" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="L168" s="38" t="s">
         <v>1</v>
@@ -18842,7 +18837,7 @@
         <v>426</v>
       </c>
       <c r="K169" s="39" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="L169" s="42" t="s">
         <v>1</v>
@@ -18884,60 +18879,60 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="12" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1">
-    <cfRule type="cellIs" dxfId="11" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1">
-    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="10" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J1">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1">
-    <cfRule type="cellIs" dxfId="8" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="16" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P1">
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:W1048576">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1">
-    <cfRule type="cellIs" dxfId="2" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V1">
-    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J1">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_15965_1F.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_1F.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{305B7F90-21B7-4136-B778-33FFA5F5B01C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -2276,92 +2276,6 @@
     <dxf>
       <font>
         <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="6"/>
-        <color auto="1"/>
-        <name val="Arial Nova Cond Light"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFEF2CB"/>
-          <bgColor rgb="FFFFDE75"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="6"/>
-        <color auto="1"/>
-        <name val="Arial Nova Cond"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
         <i/>
         <strike val="0"/>
         <color theme="0"/>
@@ -2373,6 +2287,14 @@
         <i/>
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
       </font>
     </dxf>
     <dxf>
@@ -2520,84 +2442,6 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="6"/>
-        <color auto="1"/>
-        <name val="Arial Nova Cond Light"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFEF2CB"/>
-          <bgColor rgb="FFFFDE75"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="6"/>
-        <color auto="1"/>
-        <name val="Arial Nova Cond"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -4112,6 +3956,162 @@
         <vertAlign val="baseline"/>
         <sz val="6"/>
         <color auto="1"/>
+        <name val="Arial Nova Cond Light"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEF2CB"/>
+          <bgColor rgb="FFFFDE75"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="6"/>
+        <color auto="1"/>
+        <name val="Arial Nova Cond"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="6"/>
+        <color auto="1"/>
+        <name val="Arial Nova Cond Light"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEF2CB"/>
+          <bgColor rgb="FFFFDE75"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="6"/>
+        <color auto="1"/>
+        <name val="Arial Nova Cond"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="6"/>
+        <color auto="1"/>
         <name val="Arial Nova Cond"/>
         <family val="2"/>
         <scheme val="none"/>
@@ -4418,28 +4418,28 @@
     <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="70" dataDxfId="69"/>
     <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="68" dataDxfId="67"/>
     <tableColumn id="3" xr3:uid="{38346B1D-47C6-4B44-A19C-766D16435669}" name="Classe" headerRowDxfId="66" dataDxfId="65"/>
-    <tableColumn id="5" xr3:uid="{AAB64158-D6DA-4E9F-AC47-A0274997AD5C}" name="Coluna8" headerRowDxfId="2" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{9F1772E8-67AD-410D-A17F-F21B8080770D}" name="Coluna7" headerRowDxfId="24" dataDxfId="23"/>
-    <tableColumn id="9" xr3:uid="{9B194C8C-85D6-4BE2-B1AE-E11E335186F0}" name="Coluna6" headerRowDxfId="64" dataDxfId="63"/>
-    <tableColumn id="8" xr3:uid="{6F1A2D13-ED4B-47DE-AFA9-D11431CAA734}" name="Coluna5" headerRowDxfId="62" dataDxfId="61"/>
-    <tableColumn id="15" xr3:uid="{0C0DAD0A-A76E-4555-A1F1-F78A8F1BE2C2}" name="Coluna4" headerRowDxfId="60" dataDxfId="59"/>
-    <tableColumn id="14" xr3:uid="{C073F03F-8B8F-474F-AF29-E26DD9C1B19A}" name="Coluna3" headerRowDxfId="58" dataDxfId="57"/>
-    <tableColumn id="11" xr3:uid="{AE04A63A-3540-4CF3-9D9A-59CD3577B22C}" name="Coluna2" headerRowDxfId="56" dataDxfId="55"/>
-    <tableColumn id="10" xr3:uid="{F50D06F5-DC15-417E-BE0C-A36478AC8A38}" name="Coluna1" headerRowDxfId="54" dataDxfId="53"/>
-    <tableColumn id="25" xr3:uid="{FF2B42B8-007D-4B78-A1E6-70321A25B422}" name="Coluna20" headerRowDxfId="52" dataDxfId="51"/>
-    <tableColumn id="24" xr3:uid="{B0850B61-1B8F-418B-98C0-04AB09902DE3}" name="Coluna19" headerRowDxfId="50" dataDxfId="49"/>
-    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="48" dataDxfId="47"/>
-    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="46" dataDxfId="45"/>
-    <tableColumn id="6" xr3:uid="{8E7C1DDF-1846-4221-9B0E-C7E4CC7EA057}" name="Coluna9" headerRowDxfId="44" dataDxfId="43"/>
-    <tableColumn id="7" xr3:uid="{3D7A485C-E68B-4D3B-888E-DCFC8EAEE60D}" name="Coluna10" headerRowDxfId="42" dataDxfId="41"/>
-    <tableColumn id="16" xr3:uid="{FECF52FB-CC27-4CA6-B622-AF9F7DB3B554}" name="Coluna11" headerRowDxfId="40" dataDxfId="39"/>
-    <tableColumn id="17" xr3:uid="{D79F8B63-2EF5-45DD-9134-450A005B41F4}" name="Coluna12" headerRowDxfId="38" dataDxfId="37"/>
-    <tableColumn id="18" xr3:uid="{DAFF39A1-0FA6-4AF0-A3B6-380882A29861}" name="Coluna13" headerRowDxfId="36" dataDxfId="35"/>
-    <tableColumn id="19" xr3:uid="{87AE1228-C62F-45E2-A7B1-A0914F89FBE3}" name="Coluna14" headerRowDxfId="34" dataDxfId="33"/>
-    <tableColumn id="20" xr3:uid="{85EAA474-6B84-4EF5-95FF-852AF2C5EA5E}" name="Coluna15" headerRowDxfId="32" dataDxfId="31"/>
-    <tableColumn id="21" xr3:uid="{5B15C019-4680-4877-A95B-F683BA0C59DD}" name="Coluna16" headerRowDxfId="30" dataDxfId="29"/>
-    <tableColumn id="22" xr3:uid="{5C11667F-4365-4FD8-A625-69FCEAC4D24C}" name="Coluna17" headerRowDxfId="28" dataDxfId="27"/>
-    <tableColumn id="23" xr3:uid="{38F8B48D-5280-437C-BB95-24A464DAF74A}" name="Coluna18" headerRowDxfId="26" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{AAB64158-D6DA-4E9F-AC47-A0274997AD5C}" name="Coluna8" headerRowDxfId="64" dataDxfId="63"/>
+    <tableColumn id="4" xr3:uid="{9F1772E8-67AD-410D-A17F-F21B8080770D}" name="Coluna7" headerRowDxfId="62" dataDxfId="61"/>
+    <tableColumn id="9" xr3:uid="{9B194C8C-85D6-4BE2-B1AE-E11E335186F0}" name="Coluna6" headerRowDxfId="60" dataDxfId="59"/>
+    <tableColumn id="8" xr3:uid="{6F1A2D13-ED4B-47DE-AFA9-D11431CAA734}" name="Coluna5" headerRowDxfId="58" dataDxfId="57"/>
+    <tableColumn id="15" xr3:uid="{0C0DAD0A-A76E-4555-A1F1-F78A8F1BE2C2}" name="Coluna4" headerRowDxfId="56" dataDxfId="55"/>
+    <tableColumn id="14" xr3:uid="{C073F03F-8B8F-474F-AF29-E26DD9C1B19A}" name="Coluna3" headerRowDxfId="54" dataDxfId="53"/>
+    <tableColumn id="11" xr3:uid="{AE04A63A-3540-4CF3-9D9A-59CD3577B22C}" name="Coluna2" headerRowDxfId="52" dataDxfId="51"/>
+    <tableColumn id="10" xr3:uid="{F50D06F5-DC15-417E-BE0C-A36478AC8A38}" name="Coluna1" headerRowDxfId="50" dataDxfId="49"/>
+    <tableColumn id="25" xr3:uid="{FF2B42B8-007D-4B78-A1E6-70321A25B422}" name="Coluna20" headerRowDxfId="48" dataDxfId="47"/>
+    <tableColumn id="24" xr3:uid="{B0850B61-1B8F-418B-98C0-04AB09902DE3}" name="Coluna19" headerRowDxfId="46" dataDxfId="45"/>
+    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="44" dataDxfId="43"/>
+    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="42" dataDxfId="41"/>
+    <tableColumn id="6" xr3:uid="{8E7C1DDF-1846-4221-9B0E-C7E4CC7EA057}" name="Coluna9" headerRowDxfId="40" dataDxfId="39"/>
+    <tableColumn id="7" xr3:uid="{3D7A485C-E68B-4D3B-888E-DCFC8EAEE60D}" name="Coluna10" headerRowDxfId="38" dataDxfId="37"/>
+    <tableColumn id="16" xr3:uid="{FECF52FB-CC27-4CA6-B622-AF9F7DB3B554}" name="Coluna11" headerRowDxfId="36" dataDxfId="35"/>
+    <tableColumn id="17" xr3:uid="{D79F8B63-2EF5-45DD-9134-450A005B41F4}" name="Coluna12" headerRowDxfId="34" dataDxfId="33"/>
+    <tableColumn id="18" xr3:uid="{DAFF39A1-0FA6-4AF0-A3B6-380882A29861}" name="Coluna13" headerRowDxfId="32" dataDxfId="31"/>
+    <tableColumn id="19" xr3:uid="{87AE1228-C62F-45E2-A7B1-A0914F89FBE3}" name="Coluna14" headerRowDxfId="30" dataDxfId="29"/>
+    <tableColumn id="20" xr3:uid="{85EAA474-6B84-4EF5-95FF-852AF2C5EA5E}" name="Coluna15" headerRowDxfId="28" dataDxfId="27"/>
+    <tableColumn id="21" xr3:uid="{5B15C019-4680-4877-A95B-F683BA0C59DD}" name="Coluna16" headerRowDxfId="26" dataDxfId="25"/>
+    <tableColumn id="22" xr3:uid="{5C11667F-4365-4FD8-A625-69FCEAC4D24C}" name="Coluna17" headerRowDxfId="24" dataDxfId="23"/>
+    <tableColumn id="23" xr3:uid="{38F8B48D-5280-437C-BB95-24A464DAF74A}" name="Coluna18" headerRowDxfId="22" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -4764,14 +4764,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B000FC7-022F-4B0D-BBFB-289DF5E27855}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="65.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.69921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.69921875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -4782,7 +4782,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="49" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" s="49" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>177</v>
       </c>
@@ -4793,7 +4793,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="49" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" s="49" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>178</v>
       </c>
@@ -4804,7 +4804,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="49" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" s="49" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -4815,7 +4815,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="49" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" s="49" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -4827,7 +4827,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="6" spans="1:3" s="49" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" s="49" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
@@ -4839,7 +4839,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="7" spans="1:3" s="49" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" s="49" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
@@ -4850,7 +4850,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="49" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" s="49" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="45" t="s">
         <v>9</v>
       </c>
@@ -4861,7 +4861,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="9" spans="1:3" s="49" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" s="49" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>179</v>
       </c>
@@ -4872,7 +4872,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="10" spans="1:3" s="49" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" s="49" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>181</v>
       </c>
@@ -4883,7 +4883,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="11" spans="1:3" s="49" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" s="49" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>182</v>
       </c>
@@ -4894,7 +4894,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="12" spans="1:3" s="49" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" s="49" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>10</v>
       </c>
@@ -4905,7 +4905,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="13" spans="1:3" s="49" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" s="49" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>183</v>
       </c>
@@ -4916,7 +4916,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="14" spans="1:3" s="49" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" s="49" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>184</v>
       </c>
@@ -4927,7 +4927,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="15" spans="1:3" s="49" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" s="49" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>185</v>
       </c>
@@ -4938,7 +4938,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="16" spans="1:3" s="49" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" s="49" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>186</v>
       </c>
@@ -4949,7 +4949,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="17" spans="1:3" s="49" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" s="49" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>12</v>
       </c>
@@ -4960,19 +4960,19 @@
         <v>436</v>
       </c>
     </row>
-    <row r="18" spans="1:3" s="49" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" s="49" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>187</v>
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46148.629739814816</v>
+        <v>46157.68362210648</v>
       </c>
       <c r="C18" s="48" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="49" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" s="49" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>447</v>
       </c>
@@ -4983,7 +4983,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="49" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" s="49" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="45" t="s">
         <v>440</v>
       </c>
@@ -4995,7 +4995,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="21" spans="1:3" s="49" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" s="49" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="45" t="s">
         <v>448</v>
       </c>
@@ -5007,7 +5007,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="22" spans="1:3" s="49" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" s="49" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>176</v>
       </c>
@@ -5018,7 +5018,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="23" spans="1:3" s="49" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" s="49" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>188</v>
       </c>
@@ -5029,7 +5029,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="49" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" s="49" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>195</v>
       </c>
@@ -5040,7 +5040,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="25" spans="1:3" s="49" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" s="49" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>197</v>
       </c>
@@ -5051,7 +5051,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="26" spans="1:3" s="49" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" s="49" customFormat="1" ht="7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="45" t="s">
         <v>432</v>
       </c>
@@ -5071,34 +5071,34 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F75533AB-3BC5-4EED-85BC-780B8F4A6EA8}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA19"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.83203125" style="35" customWidth="1"/>
+    <col min="2" max="2" width="6.796875" style="35" customWidth="1"/>
     <col min="3" max="3" width="7" style="35" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.83203125" style="35" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.33203125" style="35" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.33203125" style="35" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="8.83203125" style="35" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="75.83203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="55.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.796875" style="35" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.296875" style="35" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.296875" style="35" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="8.796875" style="35" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.19921875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.296875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.296875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="75.796875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="55.19921875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="6" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="7" customWidth="1"/>
-    <col min="20" max="20" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.796875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.296875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="10" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.6640625" customWidth="1"/>
-    <col min="24" max="24" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.69921875" customWidth="1"/>
+    <col min="24" max="24" width="9.19921875" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="8.5" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="6" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="79.33203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="79.296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="57.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" ht="30.9" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>374</v>
       </c>
@@ -5181,7 +5181,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="59">
         <v>2</v>
       </c>
@@ -5272,7 +5272,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="59">
         <v>3</v>
       </c>
@@ -5363,7 +5363,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="59">
         <v>4</v>
       </c>
@@ -5454,7 +5454,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="59">
         <v>5</v>
       </c>
@@ -5545,7 +5545,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="59">
         <v>6</v>
       </c>
@@ -5636,7 +5636,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="59">
         <v>7</v>
       </c>
@@ -5727,7 +5727,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="59">
         <v>8</v>
       </c>
@@ -5818,7 +5818,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="59">
         <v>9</v>
       </c>
@@ -5909,7 +5909,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="59">
         <v>10</v>
       </c>
@@ -6000,7 +6000,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="59">
         <v>11</v>
       </c>
@@ -6091,7 +6091,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="59">
         <v>12</v>
       </c>
@@ -6182,7 +6182,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="59">
         <v>13</v>
       </c>
@@ -6273,7 +6273,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="59">
         <v>14</v>
       </c>
@@ -6364,7 +6364,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="59">
         <v>15</v>
       </c>
@@ -6455,7 +6455,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="59">
         <v>16</v>
       </c>
@@ -6546,7 +6546,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="59">
         <v>17</v>
       </c>
@@ -6637,7 +6637,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="59">
         <v>18</v>
       </c>
@@ -6728,7 +6728,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="59">
         <v>19</v>
       </c>
@@ -6821,18 +6821,18 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A19">
-    <cfRule type="cellIs" dxfId="22" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="21" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA1:AA19">
-    <cfRule type="cellIs" dxfId="17" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6844,13 +6844,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99A4D5B2-E607-43E1-969D-E9BC12588F0D}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="21" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="21" width="7.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" ht="15.45" x14ac:dyDescent="0.3">
       <c r="A1" s="28" t="s">
         <v>375</v>
       </c>
@@ -6915,7 +6915,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="28">
         <v>2</v>
       </c>
@@ -6982,7 +6982,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6997,13 +6997,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50BE4DF8-DB25-47BD-BFAE-132A16409236}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="13.83203125" customWidth="1"/>
+    <col min="2" max="3" width="13.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="31">
         <v>1</v>
       </c>
@@ -7014,7 +7014,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -7027,7 +7027,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7039,34 +7039,34 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B79BA5E7-BFBD-4AC9-B36C-B9776AA17B75}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:Y169"/>
-  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.33203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="6.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="7.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.69921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.296875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="6.69921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.19921875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="7.69921875" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="4.5" style="40" customWidth="1"/>
     <col min="7" max="7" width="9" style="40" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="4" style="40" customWidth="1"/>
-    <col min="9" max="9" width="6.83203125" style="40" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.796875" style="40" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="3.5" style="40" customWidth="1"/>
-    <col min="11" max="11" width="7.1640625" style="40" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.19921875" style="40" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="5" style="40" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.1640625" style="40" customWidth="1"/>
-    <col min="14" max="14" width="5.6640625" style="40" customWidth="1"/>
+    <col min="13" max="13" width="20.19921875" style="40" customWidth="1"/>
+    <col min="14" max="14" width="5.69921875" style="40" customWidth="1"/>
     <col min="15" max="15" width="36" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="19" width="8.83203125" style="40" customWidth="1"/>
+    <col min="16" max="19" width="8.796875" style="40" customWidth="1"/>
     <col min="20" max="20" width="5" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.69921875" style="2" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="5" style="2" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="5.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.69921875" style="2" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="5" style="2" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="5.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="5.69921875" style="2" bestFit="1" customWidth="1"/>
     <col min="26" max="16384" width="11.5" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>189</v>
       </c>
@@ -7143,7 +7143,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8">
         <v>2</v>
       </c>
@@ -7220,7 +7220,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
         <v>3</v>
       </c>
@@ -7297,7 +7297,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
         <v>4</v>
       </c>
@@ -7374,7 +7374,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
         <v>5</v>
       </c>
@@ -7451,7 +7451,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
         <v>6</v>
       </c>
@@ -7528,7 +7528,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8">
         <v>7</v>
       </c>
@@ -7605,7 +7605,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <v>8</v>
       </c>
@@ -7682,7 +7682,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
         <v>9</v>
       </c>
@@ -7759,7 +7759,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
         <v>10</v>
       </c>
@@ -7836,7 +7836,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8">
         <v>11</v>
       </c>
@@ -7913,7 +7913,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
         <v>12</v>
       </c>
@@ -7990,7 +7990,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
         <v>13</v>
       </c>
@@ -8067,7 +8067,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
         <v>14</v>
       </c>
@@ -8144,7 +8144,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
         <v>15</v>
       </c>
@@ -8221,7 +8221,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
         <v>16</v>
       </c>
@@ -8298,7 +8298,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="17" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
         <v>17</v>
       </c>
@@ -8375,7 +8375,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="8">
         <v>18</v>
       </c>
@@ -8452,7 +8452,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="8">
         <v>19</v>
       </c>
@@ -8529,7 +8529,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <v>20</v>
       </c>
@@ -8606,7 +8606,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8">
         <v>21</v>
       </c>
@@ -8683,7 +8683,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
         <v>22</v>
       </c>
@@ -8760,7 +8760,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8">
         <v>23</v>
       </c>
@@ -8837,7 +8837,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
         <v>24</v>
       </c>
@@ -8914,7 +8914,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8">
         <v>25</v>
       </c>
@@ -8991,7 +8991,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="8">
         <v>26</v>
       </c>
@@ -9068,7 +9068,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="27" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="8">
         <v>27</v>
       </c>
@@ -9145,7 +9145,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="28" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="8">
         <v>28</v>
       </c>
@@ -9222,7 +9222,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="29" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="8">
         <v>29</v>
       </c>
@@ -9299,7 +9299,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="30" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="8">
         <v>30</v>
       </c>
@@ -9376,7 +9376,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="31" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="8">
         <v>31</v>
       </c>
@@ -9453,7 +9453,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="32" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="8">
         <v>32</v>
       </c>
@@ -9530,7 +9530,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="33" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="8">
         <v>33</v>
       </c>
@@ -9607,7 +9607,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="34" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="8">
         <v>34</v>
       </c>
@@ -9684,7 +9684,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="35" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="8">
         <v>35</v>
       </c>
@@ -9761,7 +9761,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="36" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="8">
         <v>36</v>
       </c>
@@ -9838,7 +9838,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="37" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="8">
         <v>37</v>
       </c>
@@ -9915,7 +9915,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="38" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="8">
         <v>38</v>
       </c>
@@ -9992,7 +9992,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="39" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="8">
         <v>39</v>
       </c>
@@ -10069,7 +10069,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="40" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="8">
         <v>40</v>
       </c>
@@ -10146,7 +10146,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="41" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="8">
         <v>41</v>
       </c>
@@ -10223,7 +10223,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="42" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="8">
         <v>42</v>
       </c>
@@ -10300,7 +10300,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="43" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="8">
         <v>43</v>
       </c>
@@ -10377,7 +10377,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="44" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="8">
         <v>44</v>
       </c>
@@ -10454,7 +10454,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="45" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="8">
         <v>45</v>
       </c>
@@ -10531,7 +10531,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="46" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="8">
         <v>46</v>
       </c>
@@ -10608,7 +10608,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="47" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="8">
         <v>47</v>
       </c>
@@ -10685,7 +10685,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="48" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="8">
         <v>48</v>
       </c>
@@ -10762,7 +10762,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="49" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="8">
         <v>49</v>
       </c>
@@ -10839,7 +10839,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="50" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="8">
         <v>50</v>
       </c>
@@ -10916,7 +10916,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="51" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="8">
         <v>51</v>
       </c>
@@ -10993,7 +10993,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="52" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="8">
         <v>52</v>
       </c>
@@ -11070,7 +11070,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="53" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="8">
         <v>53</v>
       </c>
@@ -11147,7 +11147,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="54" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="8">
         <v>54</v>
       </c>
@@ -11224,7 +11224,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="55" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="8">
         <v>55</v>
       </c>
@@ -11301,7 +11301,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="56" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="8">
         <v>56</v>
       </c>
@@ -11378,7 +11378,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="57" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="8">
         <v>57</v>
       </c>
@@ -11455,7 +11455,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="58" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="8">
         <v>58</v>
       </c>
@@ -11532,7 +11532,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="59" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="8">
         <v>59</v>
       </c>
@@ -11609,7 +11609,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="60" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="8">
         <v>60</v>
       </c>
@@ -11686,7 +11686,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="61" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="8">
         <v>61</v>
       </c>
@@ -11763,7 +11763,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="62" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="8">
         <v>62</v>
       </c>
@@ -11840,7 +11840,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="63" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="8">
         <v>63</v>
       </c>
@@ -11917,7 +11917,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="64" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="8">
         <v>64</v>
       </c>
@@ -11994,7 +11994,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="65" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="8">
         <v>65</v>
       </c>
@@ -12071,7 +12071,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="66" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="8">
         <v>66</v>
       </c>
@@ -12148,7 +12148,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="67" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="8">
         <v>67</v>
       </c>
@@ -12225,7 +12225,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="68" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="8">
         <v>68</v>
       </c>
@@ -12302,7 +12302,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="69" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="8">
         <v>69</v>
       </c>
@@ -12379,7 +12379,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="70" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="8">
         <v>70</v>
       </c>
@@ -12456,7 +12456,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="71" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="8">
         <v>71</v>
       </c>
@@ -12533,7 +12533,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="72" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="8">
         <v>72</v>
       </c>
@@ -12610,7 +12610,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="73" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="8">
         <v>73</v>
       </c>
@@ -12687,7 +12687,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="74" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="8">
         <v>74</v>
       </c>
@@ -12764,7 +12764,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="75" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="8">
         <v>75</v>
       </c>
@@ -12841,7 +12841,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="76" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="8">
         <v>76</v>
       </c>
@@ -12918,7 +12918,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="77" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="8">
         <v>77</v>
       </c>
@@ -12995,7 +12995,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="78" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="8">
         <v>78</v>
       </c>
@@ -13072,7 +13072,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="79" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="8">
         <v>79</v>
       </c>
@@ -13149,7 +13149,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="80" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="8">
         <v>80</v>
       </c>
@@ -13226,7 +13226,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="81" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="8">
         <v>81</v>
       </c>
@@ -13303,7 +13303,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="82" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="8">
         <v>82</v>
       </c>
@@ -13380,7 +13380,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="83" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="8">
         <v>83</v>
       </c>
@@ -13457,7 +13457,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="84" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="8">
         <v>84</v>
       </c>
@@ -13534,7 +13534,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="85" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="8">
         <v>85</v>
       </c>
@@ -13611,7 +13611,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="86" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="8">
         <v>86</v>
       </c>
@@ -13688,7 +13688,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="87" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="8">
         <v>87</v>
       </c>
@@ -13765,7 +13765,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="88" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="8">
         <v>88</v>
       </c>
@@ -13842,7 +13842,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="89" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="8">
         <v>89</v>
       </c>
@@ -13919,7 +13919,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="90" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="8">
         <v>90</v>
       </c>
@@ -13996,7 +13996,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="91" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="8">
         <v>91</v>
       </c>
@@ -14073,7 +14073,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="92" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="8">
         <v>92</v>
       </c>
@@ -14150,7 +14150,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="93" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="8">
         <v>93</v>
       </c>
@@ -14227,7 +14227,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="94" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="8">
         <v>94</v>
       </c>
@@ -14304,7 +14304,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="95" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="8">
         <v>95</v>
       </c>
@@ -14381,7 +14381,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="96" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="8">
         <v>96</v>
       </c>
@@ -14458,7 +14458,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="97" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="8">
         <v>97</v>
       </c>
@@ -14535,7 +14535,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="98" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="8">
         <v>98</v>
       </c>
@@ -14612,7 +14612,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="99" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="8">
         <v>99</v>
       </c>
@@ -14689,7 +14689,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="100" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="8">
         <v>100</v>
       </c>
@@ -14766,7 +14766,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="101" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="8">
         <v>101</v>
       </c>
@@ -14843,7 +14843,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="102" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="8">
         <v>102</v>
       </c>
@@ -14920,7 +14920,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="103" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="8">
         <v>103</v>
       </c>
@@ -14997,7 +14997,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="104" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="8">
         <v>104</v>
       </c>
@@ -15074,7 +15074,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="105" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="8">
         <v>105</v>
       </c>
@@ -15151,7 +15151,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="106" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="8">
         <v>106</v>
       </c>
@@ -15228,7 +15228,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="107" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="8">
         <v>107</v>
       </c>
@@ -15305,7 +15305,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="108" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="8">
         <v>108</v>
       </c>
@@ -15382,7 +15382,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="109" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="8">
         <v>109</v>
       </c>
@@ -15459,7 +15459,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="110" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="8">
         <v>110</v>
       </c>
@@ -15536,7 +15536,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="111" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="8">
         <v>111</v>
       </c>
@@ -15613,7 +15613,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="112" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="8">
         <v>112</v>
       </c>
@@ -15690,7 +15690,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="113" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="8">
         <v>113</v>
       </c>
@@ -15767,7 +15767,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="114" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="8">
         <v>114</v>
       </c>
@@ -15844,7 +15844,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="115" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="8">
         <v>115</v>
       </c>
@@ -15921,7 +15921,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="116" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="8">
         <v>116</v>
       </c>
@@ -15998,7 +15998,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="117" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="8">
         <v>117</v>
       </c>
@@ -16075,7 +16075,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="118" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="8">
         <v>118</v>
       </c>
@@ -16152,7 +16152,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="119" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="8">
         <v>119</v>
       </c>
@@ -16229,7 +16229,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="120" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="8">
         <v>120</v>
       </c>
@@ -16306,7 +16306,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="121" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="8">
         <v>121</v>
       </c>
@@ -16383,7 +16383,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="122" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="8">
         <v>122</v>
       </c>
@@ -16460,7 +16460,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="123" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="8">
         <v>123</v>
       </c>
@@ -16537,7 +16537,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="124" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="8">
         <v>124</v>
       </c>
@@ -16614,7 +16614,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="125" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="8">
         <v>125</v>
       </c>
@@ -16691,7 +16691,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="126" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="8">
         <v>126</v>
       </c>
@@ -16768,7 +16768,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="127" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="8">
         <v>127</v>
       </c>
@@ -16845,7 +16845,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="128" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="8">
         <v>128</v>
       </c>
@@ -16922,7 +16922,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="129" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="8">
         <v>129</v>
       </c>
@@ -16999,7 +16999,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="130" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="8">
         <v>130</v>
       </c>
@@ -17076,7 +17076,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="131" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="8">
         <v>131</v>
       </c>
@@ -17153,7 +17153,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="132" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="8">
         <v>132</v>
       </c>
@@ -17230,7 +17230,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="133" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="8">
         <v>133</v>
       </c>
@@ -17307,7 +17307,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="134" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="8">
         <v>134</v>
       </c>
@@ -17384,7 +17384,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="135" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="8">
         <v>135</v>
       </c>
@@ -17461,7 +17461,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="136" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="8">
         <v>136</v>
       </c>
@@ -17538,7 +17538,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="137" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="8">
         <v>137</v>
       </c>
@@ -17615,7 +17615,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="138" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="8">
         <v>138</v>
       </c>
@@ -17692,7 +17692,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="139" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="8">
         <v>139</v>
       </c>
@@ -17769,7 +17769,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="140" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="8">
         <v>140</v>
       </c>
@@ -17846,7 +17846,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="141" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="8">
         <v>141</v>
       </c>
@@ -17923,7 +17923,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="142" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="8">
         <v>142</v>
       </c>
@@ -18000,7 +18000,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="143" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="8">
         <v>143</v>
       </c>
@@ -18077,7 +18077,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="144" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="8">
         <v>144</v>
       </c>
@@ -18154,7 +18154,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="145" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="8">
         <v>145</v>
       </c>
@@ -18231,7 +18231,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="146" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="8">
         <v>146</v>
       </c>
@@ -18308,7 +18308,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="147" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="8">
         <v>147</v>
       </c>
@@ -18385,7 +18385,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="148" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="8">
         <v>148</v>
       </c>
@@ -18462,7 +18462,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="149" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="8">
         <v>149</v>
       </c>
@@ -18539,7 +18539,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="150" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="8">
         <v>150</v>
       </c>
@@ -18616,7 +18616,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="151" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="8">
         <v>151</v>
       </c>
@@ -18693,7 +18693,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="152" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="8">
         <v>152</v>
       </c>
@@ -18770,7 +18770,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="153" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="8">
         <v>153</v>
       </c>
@@ -18847,7 +18847,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="154" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="8">
         <v>154</v>
       </c>
@@ -18924,7 +18924,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="155" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="8">
         <v>155</v>
       </c>
@@ -19001,7 +19001,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="156" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="8">
         <v>156</v>
       </c>
@@ -19078,7 +19078,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="157" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="8">
         <v>157</v>
       </c>
@@ -19155,7 +19155,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="158" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="8">
         <v>158</v>
       </c>
@@ -19232,7 +19232,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="159" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="8">
         <v>159</v>
       </c>
@@ -19309,7 +19309,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="160" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="8">
         <v>160</v>
       </c>
@@ -19386,7 +19386,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="161" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="8">
         <v>161</v>
       </c>
@@ -19463,7 +19463,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="162" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="8">
         <v>162</v>
       </c>
@@ -19540,7 +19540,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="163" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="8">
         <v>163</v>
       </c>
@@ -19617,7 +19617,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="164" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="8">
         <v>164</v>
       </c>
@@ -19694,7 +19694,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="165" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="8">
         <v>165</v>
       </c>
@@ -19771,7 +19771,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="166" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="8">
         <v>166</v>
       </c>
@@ -19848,7 +19848,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="167" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="8">
         <v>167</v>
       </c>
@@ -19925,7 +19925,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="168" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="8">
         <v>168</v>
       </c>
@@ -20002,7 +20002,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="169" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="8">
         <v>169</v>
       </c>
@@ -20082,65 +20082,65 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1">
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="cellIs" dxfId="13" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="13" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1">
-    <cfRule type="cellIs" dxfId="12" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1">
-    <cfRule type="cellIs" dxfId="11" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1">
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="cellIs" dxfId="9" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="17" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P1">
-    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="9" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1">
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1:Y1048576">
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V1">
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1">
-    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D1">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_15965_1F.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_1F.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AB264D6-1B96-4C65-944F-9440B7B343E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B1663FC-853F-48EE-A03A-0A1BF6E4E2D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4654" uniqueCount="565">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4654" uniqueCount="571">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -1449,54 +1449,33 @@
     <t>No.Projeto</t>
   </si>
   <si>
-    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Definição do Projeto.</t>
-  </si>
-  <si>
-    <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1.</t>
-  </si>
-  <si>
     <t>Interdisciplinar</t>
   </si>
   <si>
-    <t>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</t>
-  </si>
-  <si>
     <t>Requerida</t>
   </si>
   <si>
     <t>Requisito.Espacial</t>
   </si>
   <si>
-    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos Espaciais para o Projeto.</t>
-  </si>
-  <si>
     <t>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</t>
   </si>
   <si>
     <t>Requisito.Mobiliário</t>
   </si>
   <si>
-    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos Mobiliários para o Projeto.</t>
-  </si>
-  <si>
     <t>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</t>
   </si>
   <si>
     <t>Requisito.Equipamento</t>
   </si>
   <si>
-    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos Equipamentos para o Projeto.</t>
-  </si>
-  <si>
     <t>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</t>
   </si>
   <si>
     <t>Requisito.Sistemas</t>
   </si>
   <si>
-    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos de Sistemas Prediais para o Projeto.</t>
-  </si>
-  <si>
     <t>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</t>
   </si>
   <si>
@@ -1786,6 +1765,45 @@
   </si>
   <si>
     <t>NBR.F.Operacional</t>
+  </si>
+  <si>
+    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Definições do Projeto.</t>
+  </si>
+  <si>
+    <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1. Definiciones del Proyecto.</t>
+  </si>
+  <si>
+    <t>Defines an information container in accordance with the NBR 19650-1 standard. Project Definitions.</t>
+  </si>
+  <si>
+    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requisitos Espaciais do Projeto.</t>
+  </si>
+  <si>
+    <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1. Requisitos Espaciales del Proyecto.</t>
+  </si>
+  <si>
+    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requisitos Mobiliários do Projeto.</t>
+  </si>
+  <si>
+    <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1. Requisitos de Mobiliarios del Proyecto.</t>
+  </si>
+  <si>
+    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requisitos Equipamentos do Projeto.</t>
+  </si>
+  <si>
+    <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1. Requisitos de Equipamiento del Proyecto.</t>
+  </si>
+  <si>
+    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requisitos de Sistemas Prediais do Projeto.</t>
+  </si>
+  <si>
+    <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1. Requisitos de Instalaciones del Proyecto.</t>
+  </si>
+  <si>
+    <t>"Parte 3 da NBR 15.965"</t>
+  </si>
+  <si>
+    <t>"Fases do ciclo de vida da edificação"</t>
   </si>
 </sst>
 </file>
@@ -2342,7 +2360,63 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{9B49B867-F029-4368-B154-870C7BE57F68}"/>
   </cellStyles>
-  <dxfs count="82">
+  <dxfs count="85">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2515,30 +2589,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2584,84 +2634,6 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="6"/>
-        <color auto="1"/>
-        <name val="Arial Nova Cond Light"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFEF2CB"/>
-          <bgColor rgb="FFFFDE75"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="6"/>
-        <color auto="1"/>
-        <name val="Arial Nova Cond"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -4331,6 +4303,84 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="6"/>
+        <color auto="1"/>
+        <name val="Arial Nova Cond Light"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEF2CB"/>
+          <bgColor rgb="FFFFDE75"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="6"/>
+        <color auto="1"/>
+        <name val="Arial Nova Cond"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="6"/>
         <color rgb="FF000000"/>
         <name val="Arial Nova Cond"/>
         <family val="2"/>
@@ -4555,33 +4605,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:Y169" headerRowCount="0" totalsRowShown="0" headerRowDxfId="81" headerRowBorderDxfId="80" tableBorderDxfId="79" totalsRowBorderDxfId="78">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:Y169" headerRowCount="0" totalsRowShown="0" headerRowDxfId="84" headerRowBorderDxfId="83" tableBorderDxfId="82" totalsRowBorderDxfId="81">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="77" dataDxfId="76"/>
-    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="75" dataDxfId="74"/>
-    <tableColumn id="26" xr3:uid="{C91353D4-2D80-49C8-8738-A06C8033990C}" name="Coluna21" headerRowDxfId="29" dataDxfId="28"/>
-    <tableColumn id="5" xr3:uid="{AAB64158-D6DA-4E9F-AC47-A0274997AD5C}" name="Coluna8" headerRowDxfId="73" dataDxfId="72"/>
-    <tableColumn id="4" xr3:uid="{9F1772E8-67AD-410D-A17F-F21B8080770D}" name="Coluna7" headerRowDxfId="71" dataDxfId="70"/>
-    <tableColumn id="9" xr3:uid="{9B194C8C-85D6-4BE2-B1AE-E11E335186F0}" name="Coluna6" headerRowDxfId="69" dataDxfId="68"/>
-    <tableColumn id="8" xr3:uid="{6F1A2D13-ED4B-47DE-AFA9-D11431CAA734}" name="Coluna5" headerRowDxfId="67" dataDxfId="66"/>
-    <tableColumn id="15" xr3:uid="{0C0DAD0A-A76E-4555-A1F1-F78A8F1BE2C2}" name="Coluna4" headerRowDxfId="65" dataDxfId="64"/>
-    <tableColumn id="14" xr3:uid="{C073F03F-8B8F-474F-AF29-E26DD9C1B19A}" name="Coluna3" headerRowDxfId="63" dataDxfId="62"/>
-    <tableColumn id="11" xr3:uid="{AE04A63A-3540-4CF3-9D9A-59CD3577B22C}" name="Coluna2" headerRowDxfId="61" dataDxfId="60"/>
-    <tableColumn id="10" xr3:uid="{F50D06F5-DC15-417E-BE0C-A36478AC8A38}" name="Coluna1" headerRowDxfId="59" dataDxfId="58"/>
-    <tableColumn id="25" xr3:uid="{FF2B42B8-007D-4B78-A1E6-70321A25B422}" name="Coluna20" headerRowDxfId="57" dataDxfId="56"/>
-    <tableColumn id="24" xr3:uid="{B0850B61-1B8F-418B-98C0-04AB09902DE3}" name="Coluna19" headerRowDxfId="55" dataDxfId="54"/>
-    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="53" dataDxfId="52"/>
-    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="51" dataDxfId="50"/>
-    <tableColumn id="6" xr3:uid="{8E7C1DDF-1846-4221-9B0E-C7E4CC7EA057}" name="Coluna9" headerRowDxfId="49" dataDxfId="48"/>
-    <tableColumn id="7" xr3:uid="{3D7A485C-E68B-4D3B-888E-DCFC8EAEE60D}" name="Coluna10" headerRowDxfId="47" dataDxfId="46"/>
-    <tableColumn id="16" xr3:uid="{FECF52FB-CC27-4CA6-B622-AF9F7DB3B554}" name="Coluna11" headerRowDxfId="45" dataDxfId="44"/>
-    <tableColumn id="17" xr3:uid="{D79F8B63-2EF5-45DD-9134-450A005B41F4}" name="Coluna12" headerRowDxfId="43" dataDxfId="42"/>
-    <tableColumn id="18" xr3:uid="{DAFF39A1-0FA6-4AF0-A3B6-380882A29861}" name="Coluna13" headerRowDxfId="41" dataDxfId="40"/>
-    <tableColumn id="19" xr3:uid="{87AE1228-C62F-45E2-A7B1-A0914F89FBE3}" name="Coluna14" headerRowDxfId="39" dataDxfId="38"/>
-    <tableColumn id="20" xr3:uid="{85EAA474-6B84-4EF5-95FF-852AF2C5EA5E}" name="Coluna15" headerRowDxfId="37" dataDxfId="36"/>
-    <tableColumn id="21" xr3:uid="{5B15C019-4680-4877-A95B-F683BA0C59DD}" name="Coluna16" headerRowDxfId="35" dataDxfId="34"/>
-    <tableColumn id="22" xr3:uid="{5C11667F-4365-4FD8-A625-69FCEAC4D24C}" name="Coluna17" headerRowDxfId="33" dataDxfId="32"/>
-    <tableColumn id="23" xr3:uid="{38F8B48D-5280-437C-BB95-24A464DAF74A}" name="Coluna18" headerRowDxfId="31" dataDxfId="30"/>
+    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="80" dataDxfId="79"/>
+    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="78" dataDxfId="77"/>
+    <tableColumn id="26" xr3:uid="{C91353D4-2D80-49C8-8738-A06C8033990C}" name="Coluna21" headerRowDxfId="76" dataDxfId="75"/>
+    <tableColumn id="5" xr3:uid="{AAB64158-D6DA-4E9F-AC47-A0274997AD5C}" name="Coluna8" headerRowDxfId="74" dataDxfId="73"/>
+    <tableColumn id="4" xr3:uid="{9F1772E8-67AD-410D-A17F-F21B8080770D}" name="Coluna7" headerRowDxfId="72" dataDxfId="71"/>
+    <tableColumn id="9" xr3:uid="{9B194C8C-85D6-4BE2-B1AE-E11E335186F0}" name="Coluna6" headerRowDxfId="70" dataDxfId="69"/>
+    <tableColumn id="8" xr3:uid="{6F1A2D13-ED4B-47DE-AFA9-D11431CAA734}" name="Coluna5" headerRowDxfId="68" dataDxfId="67"/>
+    <tableColumn id="15" xr3:uid="{0C0DAD0A-A76E-4555-A1F1-F78A8F1BE2C2}" name="Coluna4" headerRowDxfId="66" dataDxfId="65"/>
+    <tableColumn id="14" xr3:uid="{C073F03F-8B8F-474F-AF29-E26DD9C1B19A}" name="Coluna3" headerRowDxfId="64" dataDxfId="63"/>
+    <tableColumn id="11" xr3:uid="{AE04A63A-3540-4CF3-9D9A-59CD3577B22C}" name="Coluna2" headerRowDxfId="62" dataDxfId="61"/>
+    <tableColumn id="10" xr3:uid="{F50D06F5-DC15-417E-BE0C-A36478AC8A38}" name="Coluna1" headerRowDxfId="60" dataDxfId="59"/>
+    <tableColumn id="25" xr3:uid="{FF2B42B8-007D-4B78-A1E6-70321A25B422}" name="Coluna20" headerRowDxfId="58" dataDxfId="57"/>
+    <tableColumn id="24" xr3:uid="{B0850B61-1B8F-418B-98C0-04AB09902DE3}" name="Coluna19" headerRowDxfId="56" dataDxfId="55"/>
+    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="54" dataDxfId="53"/>
+    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="52" dataDxfId="51"/>
+    <tableColumn id="6" xr3:uid="{8E7C1DDF-1846-4221-9B0E-C7E4CC7EA057}" name="Coluna9" headerRowDxfId="50" dataDxfId="49"/>
+    <tableColumn id="7" xr3:uid="{3D7A485C-E68B-4D3B-888E-DCFC8EAEE60D}" name="Coluna10" headerRowDxfId="48" dataDxfId="47"/>
+    <tableColumn id="16" xr3:uid="{FECF52FB-CC27-4CA6-B622-AF9F7DB3B554}" name="Coluna11" headerRowDxfId="46" dataDxfId="45"/>
+    <tableColumn id="17" xr3:uid="{D79F8B63-2EF5-45DD-9134-450A005B41F4}" name="Coluna12" headerRowDxfId="44" dataDxfId="43"/>
+    <tableColumn id="18" xr3:uid="{DAFF39A1-0FA6-4AF0-A3B6-380882A29861}" name="Coluna13" headerRowDxfId="42" dataDxfId="41"/>
+    <tableColumn id="19" xr3:uid="{87AE1228-C62F-45E2-A7B1-A0914F89FBE3}" name="Coluna14" headerRowDxfId="40" dataDxfId="39"/>
+    <tableColumn id="20" xr3:uid="{85EAA474-6B84-4EF5-95FF-852AF2C5EA5E}" name="Coluna15" headerRowDxfId="38" dataDxfId="37"/>
+    <tableColumn id="21" xr3:uid="{5B15C019-4680-4877-A95B-F683BA0C59DD}" name="Coluna16" headerRowDxfId="36" dataDxfId="35"/>
+    <tableColumn id="22" xr3:uid="{5C11667F-4365-4FD8-A625-69FCEAC4D24C}" name="Coluna17" headerRowDxfId="34" dataDxfId="33"/>
+    <tableColumn id="23" xr3:uid="{38F8B48D-5280-437C-BB95-24A464DAF74A}" name="Coluna18" headerRowDxfId="32" dataDxfId="31"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -5108,7 +5158,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46165.609699768516</v>
+        <v>46167.411050810188</v>
       </c>
       <c r="C18" s="48" t="s">
         <v>434</v>
@@ -5323,7 +5373,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="59">
         <v>2</v>
       </c>
@@ -5358,7 +5408,7 @@
         <v>191</v>
       </c>
       <c r="L2" s="63" t="str">
-        <f t="shared" ref="L2:N17" si="0">CONCATENATE("", C2)</f>
+        <f t="shared" ref="L2:M6" si="0">CONCATENATE("", C2)</f>
         <v>Contêiner</v>
       </c>
       <c r="M2" s="63" t="str">
@@ -5374,10 +5424,10 @@
         <v>No Projeto</v>
       </c>
       <c r="P2" s="44" t="s">
-        <v>452</v>
+        <v>558</v>
       </c>
       <c r="Q2" s="44" t="s">
-        <v>453</v>
+        <v>559</v>
       </c>
       <c r="R2" s="64" t="s">
         <v>191</v>
@@ -5395,10 +5445,10 @@
         <v>Definida</v>
       </c>
       <c r="V2" s="44" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="W2" s="66" t="str">
-        <f t="shared" ref="W2:W27" si="3">CONCATENATE("Key.ABNT.",A2)</f>
+        <f t="shared" ref="W2:W6" si="3">CONCATENATE("Key.ABNT.",A2)</f>
         <v>Key.ABNT.2</v>
       </c>
       <c r="X2" s="44" t="s">
@@ -5411,10 +5461,10 @@
         <v>191</v>
       </c>
       <c r="AA2" s="44" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="59">
         <v>3</v>
       </c>
@@ -5428,10 +5478,10 @@
         <v>449</v>
       </c>
       <c r="E3" s="60" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="F3" s="61" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="G3" s="62" t="s">
         <v>191</v>
@@ -5465,10 +5515,10 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="44" t="s">
-        <v>458</v>
+        <v>561</v>
       </c>
       <c r="Q3" s="44" t="s">
-        <v>453</v>
+        <v>562</v>
       </c>
       <c r="R3" s="64" t="s">
         <v>191</v>
@@ -5486,7 +5536,7 @@
         <v>Requerida</v>
       </c>
       <c r="V3" s="44" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="W3" s="66" t="str">
         <f t="shared" si="3"/>
@@ -5502,10 +5552,10 @@
         <v>191</v>
       </c>
       <c r="AA3" s="44" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="59">
         <v>4</v>
       </c>
@@ -5519,10 +5569,10 @@
         <v>449</v>
       </c>
       <c r="E4" s="60" t="s">
+        <v>453</v>
+      </c>
+      <c r="F4" s="61" t="s">
         <v>456</v>
-      </c>
-      <c r="F4" s="61" t="s">
-        <v>460</v>
       </c>
       <c r="G4" s="62" t="s">
         <v>191</v>
@@ -5556,10 +5606,10 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="44" t="s">
-        <v>461</v>
+        <v>563</v>
       </c>
       <c r="Q4" s="44" t="s">
-        <v>453</v>
+        <v>564</v>
       </c>
       <c r="R4" s="64" t="s">
         <v>191</v>
@@ -5577,7 +5627,7 @@
         <v>Requerida</v>
       </c>
       <c r="V4" s="44" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="W4" s="66" t="str">
         <f t="shared" si="3"/>
@@ -5593,10 +5643,10 @@
         <v>191</v>
       </c>
       <c r="AA4" s="44" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="59">
         <v>5</v>
       </c>
@@ -5610,10 +5660,10 @@
         <v>449</v>
       </c>
       <c r="E5" s="60" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="F5" s="61" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="G5" s="62" t="s">
         <v>191</v>
@@ -5647,10 +5697,10 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="44" t="s">
-        <v>464</v>
+        <v>565</v>
       </c>
       <c r="Q5" s="44" t="s">
-        <v>453</v>
+        <v>566</v>
       </c>
       <c r="R5" s="64" t="s">
         <v>191</v>
@@ -5668,7 +5718,7 @@
         <v>Requerida</v>
       </c>
       <c r="V5" s="44" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="W5" s="66" t="str">
         <f t="shared" si="3"/>
@@ -5684,10 +5734,10 @@
         <v>191</v>
       </c>
       <c r="AA5" s="44" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="59">
         <v>6</v>
       </c>
@@ -5701,10 +5751,10 @@
         <v>449</v>
       </c>
       <c r="E6" s="60" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="F6" s="61" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="G6" s="62" t="s">
         <v>191</v>
@@ -5738,10 +5788,10 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="44" t="s">
-        <v>467</v>
+        <v>567</v>
       </c>
       <c r="Q6" s="44" t="s">
-        <v>453</v>
+        <v>568</v>
       </c>
       <c r="R6" s="64" t="s">
         <v>191</v>
@@ -5759,7 +5809,7 @@
         <v>Requerida</v>
       </c>
       <c r="V6" s="44" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="W6" s="66" t="str">
         <f t="shared" si="3"/>
@@ -5775,7 +5825,7 @@
         <v>191</v>
       </c>
       <c r="AA6" s="44" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
     </row>
     <row r="7" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5792,10 +5842,10 @@
         <v>397</v>
       </c>
       <c r="E7" s="34" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="G7" s="37" t="s">
         <v>191</v>
@@ -5813,47 +5863,47 @@
         <v>191</v>
       </c>
       <c r="L7" s="63" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="L7:N17" si="4">CONCATENATE("", C7)</f>
         <v>Norma</v>
       </c>
       <c r="M7" s="63" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>ABNT</v>
       </c>
       <c r="N7" s="63" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>NBR.Parte</v>
       </c>
       <c r="O7" s="63" t="str">
-        <f t="shared" ref="O7:P27" si="4">F7</f>
+        <f t="shared" ref="O7:O27" si="5">F7</f>
         <v>NBR.0M</v>
       </c>
       <c r="P7" s="63" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="Q7" s="63" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="R7" s="64" t="s">
         <v>191</v>
       </c>
       <c r="S7" s="65" t="str">
-        <f t="shared" ref="S7:U22" si="5">SUBSTITUTE(C7, "_", " ")</f>
+        <f t="shared" ref="S7:U22" si="6">SUBSTITUTE(C7, "_", " ")</f>
         <v>Norma</v>
       </c>
       <c r="T7" s="65" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
       <c r="U7" s="63" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
       <c r="V7" s="44" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="W7" s="66" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="W7:W27" si="7">CONCATENATE("Key.ABNT.",A7)</f>
         <v>Key.ABNT.7</v>
       </c>
       <c r="X7" s="44" t="s">
@@ -5863,10 +5913,10 @@
         <v>191</v>
       </c>
       <c r="Z7" s="44" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="AA7" s="67" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5883,10 +5933,10 @@
         <v>397</v>
       </c>
       <c r="E8" s="34" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="F8" s="27" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="G8" s="37" t="s">
         <v>191</v>
@@ -5904,47 +5954,47 @@
         <v>191</v>
       </c>
       <c r="L8" s="63" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>Norma</v>
       </c>
       <c r="M8" s="63" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>ABNT</v>
       </c>
       <c r="N8" s="63" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>NBR.Parte</v>
       </c>
       <c r="O8" s="63" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.0P</v>
       </c>
       <c r="P8" s="63" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="Q8" s="63" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="R8" s="64" t="s">
         <v>191</v>
       </c>
       <c r="S8" s="65" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Norma</v>
       </c>
       <c r="T8" s="65" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
       <c r="U8" s="63" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
       <c r="V8" s="44" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="W8" s="66" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>Key.ABNT.8</v>
       </c>
       <c r="X8" s="44" t="s">
@@ -5954,10 +6004,10 @@
         <v>191</v>
       </c>
       <c r="Z8" s="44" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="AA8" s="67" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -5974,10 +6024,10 @@
         <v>397</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="G9" s="37" t="s">
         <v>191</v>
@@ -5995,47 +6045,47 @@
         <v>191</v>
       </c>
       <c r="L9" s="63" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>Norma</v>
       </c>
       <c r="M9" s="63" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>ABNT</v>
       </c>
       <c r="N9" s="63" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>NBR.Parte</v>
       </c>
       <c r="O9" s="63" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.1D</v>
       </c>
       <c r="P9" s="63" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="Q9" s="63" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="R9" s="64" t="s">
         <v>191</v>
       </c>
       <c r="S9" s="65" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Norma</v>
       </c>
       <c r="T9" s="65" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
       <c r="U9" s="63" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
       <c r="V9" s="44" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="W9" s="66" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>Key.ABNT.9</v>
       </c>
       <c r="X9" s="44" t="s">
@@ -6045,10 +6095,10 @@
         <v>191</v>
       </c>
       <c r="Z9" s="44" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="AA9" s="67" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6065,10 +6115,10 @@
         <v>397</v>
       </c>
       <c r="E10" s="34" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="F10" s="27" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="G10" s="37" t="s">
         <v>191</v>
@@ -6086,47 +6136,47 @@
         <v>191</v>
       </c>
       <c r="L10" s="63" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>Norma</v>
       </c>
       <c r="M10" s="63" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>ABNT</v>
       </c>
       <c r="N10" s="63" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>NBR.Parte</v>
       </c>
       <c r="O10" s="63" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.1F</v>
       </c>
       <c r="P10" s="63" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="Q10" s="63" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="R10" s="64" t="s">
         <v>191</v>
       </c>
       <c r="S10" s="65" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Norma</v>
       </c>
       <c r="T10" s="65" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
       <c r="U10" s="63" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
       <c r="V10" s="44" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="W10" s="66" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>Key.ABNT.10</v>
       </c>
       <c r="X10" s="44" t="s">
@@ -6139,7 +6189,7 @@
         <v>369</v>
       </c>
       <c r="AA10" s="67" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6156,10 +6206,10 @@
         <v>397</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="G11" s="37" t="s">
         <v>191</v>
@@ -6177,47 +6227,47 @@
         <v>191</v>
       </c>
       <c r="L11" s="63" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>Norma</v>
       </c>
       <c r="M11" s="63" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>ABNT</v>
       </c>
       <c r="N11" s="63" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>NBR.Parte</v>
       </c>
       <c r="O11" s="63" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.1S</v>
       </c>
       <c r="P11" s="63" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="Q11" s="63" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="R11" s="64" t="s">
         <v>191</v>
       </c>
       <c r="S11" s="65" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Norma</v>
       </c>
       <c r="T11" s="65" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
       <c r="U11" s="63" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
       <c r="V11" s="44" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="W11" s="66" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>Key.ABNT.11</v>
       </c>
       <c r="X11" s="44" t="s">
@@ -6227,10 +6277,10 @@
         <v>191</v>
       </c>
       <c r="Z11" s="44" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="AA11" s="67" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6247,10 +6297,10 @@
         <v>397</v>
       </c>
       <c r="E12" s="34" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="F12" s="27" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="G12" s="37" t="s">
         <v>191</v>
@@ -6268,47 +6318,47 @@
         <v>191</v>
       </c>
       <c r="L12" s="63" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>Norma</v>
       </c>
       <c r="M12" s="63" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>ABNT</v>
       </c>
       <c r="N12" s="63" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>NBR.Parte</v>
       </c>
       <c r="O12" s="63" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.2C</v>
       </c>
       <c r="P12" s="63" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="Q12" s="63" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="R12" s="64" t="s">
         <v>191</v>
       </c>
       <c r="S12" s="65" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Norma</v>
       </c>
       <c r="T12" s="65" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
       <c r="U12" s="63" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
       <c r="V12" s="44" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="W12" s="66" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>Key.ABNT.12</v>
       </c>
       <c r="X12" s="44" t="s">
@@ -6318,10 +6368,10 @@
         <v>191</v>
       </c>
       <c r="Z12" s="44" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="AA12" s="67" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6338,11 +6388,11 @@
         <v>397</v>
       </c>
       <c r="E13" s="34" t="s">
+        <v>517</v>
+      </c>
+      <c r="F13" s="27" t="s">
         <v>524</v>
       </c>
-      <c r="F13" s="27" t="s">
-        <v>531</v>
-      </c>
       <c r="G13" s="37" t="s">
         <v>191</v>
       </c>
@@ -6359,47 +6409,47 @@
         <v>191</v>
       </c>
       <c r="L13" s="63" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>Norma</v>
       </c>
       <c r="M13" s="63" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>ABNT</v>
       </c>
       <c r="N13" s="63" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>NBR.Parte</v>
       </c>
       <c r="O13" s="63" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.2N</v>
       </c>
       <c r="P13" s="63" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="Q13" s="63" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="R13" s="64" t="s">
         <v>191</v>
       </c>
       <c r="S13" s="65" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Norma</v>
       </c>
       <c r="T13" s="65" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
       <c r="U13" s="63" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
       <c r="V13" s="44" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="W13" s="66" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>Key.ABNT.13</v>
       </c>
       <c r="X13" s="44" t="s">
@@ -6409,10 +6459,10 @@
         <v>191</v>
       </c>
       <c r="Z13" s="44" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="AA13" s="67" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
     </row>
     <row r="14" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6429,10 +6479,10 @@
         <v>397</v>
       </c>
       <c r="E14" s="34" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="F14" s="27" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="G14" s="37" t="s">
         <v>191</v>
@@ -6450,47 +6500,47 @@
         <v>191</v>
       </c>
       <c r="L14" s="63" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>Norma</v>
       </c>
       <c r="M14" s="63" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>ABNT</v>
       </c>
       <c r="N14" s="63" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>NBR.Parte</v>
       </c>
       <c r="O14" s="63" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.2Q</v>
       </c>
       <c r="P14" s="63" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="Q14" s="63" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="R14" s="64" t="s">
         <v>191</v>
       </c>
       <c r="S14" s="65" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Norma</v>
       </c>
       <c r="T14" s="65" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
       <c r="U14" s="63" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
       <c r="V14" s="44" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="W14" s="66" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>Key.ABNT.14</v>
       </c>
       <c r="X14" s="44" t="s">
@@ -6500,10 +6550,10 @@
         <v>191</v>
       </c>
       <c r="Z14" s="44" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="AA14" s="67" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6520,10 +6570,10 @@
         <v>397</v>
       </c>
       <c r="E15" s="34" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="F15" s="27" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="G15" s="37" t="s">
         <v>191</v>
@@ -6541,47 +6591,47 @@
         <v>191</v>
       </c>
       <c r="L15" s="63" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>Norma</v>
       </c>
       <c r="M15" s="63" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>ABNT</v>
       </c>
       <c r="N15" s="63" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>NBR.Parte</v>
       </c>
       <c r="O15" s="63" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.3E</v>
       </c>
       <c r="P15" s="63" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="Q15" s="63" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="R15" s="64" t="s">
         <v>191</v>
       </c>
       <c r="S15" s="65" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Norma</v>
       </c>
       <c r="T15" s="65" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
       <c r="U15" s="63" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
       <c r="V15" s="44" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="W15" s="66" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>Key.ABNT.15</v>
       </c>
       <c r="X15" s="44" t="s">
@@ -6591,10 +6641,10 @@
         <v>191</v>
       </c>
       <c r="Z15" s="44" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="AA15" s="67" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6611,10 +6661,10 @@
         <v>397</v>
       </c>
       <c r="E16" s="34" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="F16" s="27" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="G16" s="37" t="s">
         <v>191</v>
@@ -6632,47 +6682,47 @@
         <v>191</v>
       </c>
       <c r="L16" s="63" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>Norma</v>
       </c>
       <c r="M16" s="63" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>ABNT</v>
       </c>
       <c r="N16" s="63" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>NBR.Parte</v>
       </c>
       <c r="O16" s="63" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.3R</v>
       </c>
       <c r="P16" s="63" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="Q16" s="63" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="R16" s="64" t="s">
         <v>191</v>
       </c>
       <c r="S16" s="65" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Norma</v>
       </c>
       <c r="T16" s="65" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
       <c r="U16" s="63" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
       <c r="V16" s="44" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="W16" s="66" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>Key.ABNT.16</v>
       </c>
       <c r="X16" s="44" t="s">
@@ -6682,10 +6732,10 @@
         <v>191</v>
       </c>
       <c r="Z16" s="44" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="AA16" s="67" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
     </row>
     <row r="17" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6702,10 +6752,10 @@
         <v>397</v>
       </c>
       <c r="E17" s="34" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="F17" s="27" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="G17" s="37" t="s">
         <v>191</v>
@@ -6723,47 +6773,47 @@
         <v>191</v>
       </c>
       <c r="L17" s="63" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>Norma</v>
       </c>
       <c r="M17" s="63" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>ABNT</v>
       </c>
       <c r="N17" s="63" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>NBR.Parte</v>
       </c>
       <c r="O17" s="63" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.4A</v>
       </c>
       <c r="P17" s="63" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="Q17" s="63" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="R17" s="64" t="s">
         <v>191</v>
       </c>
       <c r="S17" s="65" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Norma</v>
       </c>
       <c r="T17" s="65" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
       <c r="U17" s="63" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
       <c r="V17" s="44" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="W17" s="66" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>Key.ABNT.17</v>
       </c>
       <c r="X17" s="44" t="s">
@@ -6773,10 +6823,10 @@
         <v>191</v>
       </c>
       <c r="Z17" s="44" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="AA17" s="67" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
     </row>
     <row r="18" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6793,10 +6843,10 @@
         <v>397</v>
       </c>
       <c r="E18" s="34" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="F18" s="27" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="G18" s="37" t="s">
         <v>191</v>
@@ -6814,47 +6864,47 @@
         <v>191</v>
       </c>
       <c r="L18" s="63" t="str">
-        <f t="shared" ref="L18:N27" si="6">CONCATENATE("", C18)</f>
+        <f t="shared" ref="L18:N27" si="8">CONCATENATE("", C18)</f>
         <v>Norma</v>
       </c>
       <c r="M18" s="63" t="str">
+        <f t="shared" si="8"/>
+        <v>ABNT</v>
+      </c>
+      <c r="N18" s="63" t="str">
+        <f t="shared" si="8"/>
+        <v>NBR.Parte</v>
+      </c>
+      <c r="O18" s="63" t="str">
+        <f t="shared" si="5"/>
+        <v>NBR.4U</v>
+      </c>
+      <c r="P18" s="63" t="s">
+        <v>499</v>
+      </c>
+      <c r="Q18" s="63" t="s">
+        <v>500</v>
+      </c>
+      <c r="R18" s="64" t="s">
+        <v>191</v>
+      </c>
+      <c r="S18" s="65" t="str">
+        <f t="shared" si="6"/>
+        <v>Norma</v>
+      </c>
+      <c r="T18" s="65" t="str">
         <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
-      <c r="N18" s="63" t="str">
+      <c r="U18" s="63" t="str">
         <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="O18" s="63" t="str">
-        <f t="shared" si="4"/>
-        <v>NBR.4U</v>
-      </c>
-      <c r="P18" s="63" t="s">
-        <v>506</v>
-      </c>
-      <c r="Q18" s="63" t="s">
-        <v>507</v>
-      </c>
-      <c r="R18" s="64" t="s">
-        <v>191</v>
-      </c>
-      <c r="S18" s="65" t="str">
-        <f t="shared" si="5"/>
-        <v>Norma</v>
-      </c>
-      <c r="T18" s="65" t="str">
-        <f t="shared" si="5"/>
-        <v>ABNT</v>
-      </c>
-      <c r="U18" s="63" t="str">
-        <f t="shared" si="5"/>
-        <v>NBR.Parte</v>
-      </c>
       <c r="V18" s="44" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="W18" s="66" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>Key.ABNT.18</v>
       </c>
       <c r="X18" s="44" t="s">
@@ -6864,10 +6914,10 @@
         <v>191</v>
       </c>
       <c r="Z18" s="44" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="AA18" s="67" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6884,10 +6934,10 @@
         <v>397</v>
       </c>
       <c r="E19" s="34" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="F19" s="27" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="G19" s="37" t="s">
         <v>191</v>
@@ -6905,47 +6955,47 @@
         <v>191</v>
       </c>
       <c r="L19" s="63" t="str">
+        <f t="shared" si="8"/>
+        <v>Norma</v>
+      </c>
+      <c r="M19" s="63" t="str">
+        <f t="shared" si="8"/>
+        <v>ABNT</v>
+      </c>
+      <c r="N19" s="63" t="str">
+        <f t="shared" si="8"/>
+        <v>NBR.Parte</v>
+      </c>
+      <c r="O19" s="63" t="str">
+        <f t="shared" si="5"/>
+        <v>NBR.5I</v>
+      </c>
+      <c r="P19" s="63" t="s">
+        <v>503</v>
+      </c>
+      <c r="Q19" s="63" t="s">
+        <v>504</v>
+      </c>
+      <c r="R19" s="64" t="s">
+        <v>191</v>
+      </c>
+      <c r="S19" s="65" t="str">
         <f t="shared" si="6"/>
         <v>Norma</v>
       </c>
-      <c r="M19" s="63" t="str">
+      <c r="T19" s="65" t="str">
         <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
-      <c r="N19" s="63" t="str">
+      <c r="U19" s="63" t="str">
         <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="O19" s="63" t="str">
-        <f t="shared" si="4"/>
-        <v>NBR.5I</v>
-      </c>
-      <c r="P19" s="63" t="s">
-        <v>510</v>
-      </c>
-      <c r="Q19" s="63" t="s">
-        <v>511</v>
-      </c>
-      <c r="R19" s="64" t="s">
-        <v>191</v>
-      </c>
-      <c r="S19" s="65" t="str">
-        <f t="shared" si="5"/>
-        <v>Norma</v>
-      </c>
-      <c r="T19" s="65" t="str">
-        <f t="shared" si="5"/>
-        <v>ABNT</v>
-      </c>
-      <c r="U19" s="63" t="str">
-        <f t="shared" si="5"/>
-        <v>NBR.Parte</v>
-      </c>
       <c r="V19" s="44" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="W19" s="66" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>Key.ABNT.19</v>
       </c>
       <c r="X19" s="44" t="s">
@@ -6955,10 +7005,10 @@
         <v>191</v>
       </c>
       <c r="Z19" s="44" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="AA19" s="67" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
     </row>
     <row r="20" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6969,50 +7019,50 @@
         <v>420</v>
       </c>
       <c r="C20" s="34" t="s">
+        <v>531</v>
+      </c>
+      <c r="D20" s="34" t="s">
+        <v>532</v>
+      </c>
+      <c r="E20" s="34" t="s">
         <v>538</v>
       </c>
-      <c r="D20" s="34" t="s">
+      <c r="F20" s="12" t="s">
+        <v>533</v>
+      </c>
+      <c r="G20" s="62" t="s">
+        <v>191</v>
+      </c>
+      <c r="H20" s="62" t="s">
+        <v>191</v>
+      </c>
+      <c r="I20" s="62" t="s">
+        <v>191</v>
+      </c>
+      <c r="J20" s="62" t="s">
+        <v>191</v>
+      </c>
+      <c r="K20" s="62" t="s">
+        <v>191</v>
+      </c>
+      <c r="L20" s="63" t="str">
+        <f t="shared" si="8"/>
+        <v>NBR.Tema</v>
+      </c>
+      <c r="M20" s="63" t="str">
+        <f t="shared" si="8"/>
+        <v>NBR.Subtema</v>
+      </c>
+      <c r="N20" s="63" t="str">
+        <f t="shared" si="8"/>
+        <v>NBR.Fases</v>
+      </c>
+      <c r="O20" s="63" t="str">
+        <f t="shared" si="5"/>
+        <v>NBR.F.Programação</v>
+      </c>
+      <c r="P20" s="44" t="s">
         <v>539</v>
-      </c>
-      <c r="E20" s="34" t="s">
-        <v>545</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>540</v>
-      </c>
-      <c r="G20" s="62" t="s">
-        <v>191</v>
-      </c>
-      <c r="H20" s="62" t="s">
-        <v>191</v>
-      </c>
-      <c r="I20" s="62" t="s">
-        <v>191</v>
-      </c>
-      <c r="J20" s="62" t="s">
-        <v>191</v>
-      </c>
-      <c r="K20" s="62" t="s">
-        <v>191</v>
-      </c>
-      <c r="L20" s="63" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.Tema</v>
-      </c>
-      <c r="M20" s="63" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.Subtema</v>
-      </c>
-      <c r="N20" s="63" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.Fases</v>
-      </c>
-      <c r="O20" s="63" t="str">
-        <f t="shared" si="4"/>
-        <v>NBR.F.Programação</v>
-      </c>
-      <c r="P20" s="44" t="s">
-        <v>546</v>
       </c>
       <c r="Q20" s="44" t="str">
         <f>_xlfn.TRANSLATE(P20,"pt","es")</f>
@@ -7022,22 +7072,22 @@
         <v>191</v>
       </c>
       <c r="S20" s="65" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>NBR.Tema</v>
       </c>
       <c r="T20" s="65" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>NBR.Subtema</v>
       </c>
       <c r="U20" s="63" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>NBR.Fases</v>
       </c>
       <c r="V20" s="44" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="W20" s="66" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>Key.ABNT.20</v>
       </c>
       <c r="X20" s="44" t="s">
@@ -7047,7 +7097,7 @@
         <v>191</v>
       </c>
       <c r="Z20" s="65" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="AA20" s="44" t="str">
         <f>_xlfn.TRANSLATE(P20,"pt","en")</f>
@@ -7062,16 +7112,16 @@
         <v>420</v>
       </c>
       <c r="C21" s="34" t="s">
+        <v>531</v>
+      </c>
+      <c r="D21" s="34" t="s">
+        <v>532</v>
+      </c>
+      <c r="E21" s="34" t="s">
         <v>538</v>
       </c>
-      <c r="D21" s="34" t="s">
-        <v>539</v>
-      </c>
-      <c r="E21" s="34" t="s">
-        <v>545</v>
-      </c>
       <c r="F21" s="12" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="G21" s="37" t="s">
         <v>191</v>
@@ -7089,48 +7139,48 @@
         <v>191</v>
       </c>
       <c r="L21" s="63" t="str">
+        <f t="shared" si="8"/>
+        <v>NBR.Tema</v>
+      </c>
+      <c r="M21" s="63" t="str">
+        <f t="shared" si="8"/>
+        <v>NBR.Subtema</v>
+      </c>
+      <c r="N21" s="63" t="str">
+        <f t="shared" si="8"/>
+        <v>NBR.Fases</v>
+      </c>
+      <c r="O21" s="63" t="str">
+        <f t="shared" si="5"/>
+        <v>NBR.F.Estudo.Preliminar</v>
+      </c>
+      <c r="P21" s="63" t="s">
+        <v>546</v>
+      </c>
+      <c r="Q21" s="44" t="str">
+        <f t="shared" ref="Q21:Q27" si="9">_xlfn.TRANSLATE(P21,"pt","es")</f>
+        <v>Fase de Estudios Preliminares</v>
+      </c>
+      <c r="R21" s="64" t="s">
+        <v>191</v>
+      </c>
+      <c r="S21" s="65" t="str">
         <f t="shared" si="6"/>
         <v>NBR.Tema</v>
       </c>
-      <c r="M21" s="63" t="str">
+      <c r="T21" s="65" t="str">
         <f t="shared" si="6"/>
         <v>NBR.Subtema</v>
       </c>
-      <c r="N21" s="63" t="str">
+      <c r="U21" s="63" t="str">
         <f t="shared" si="6"/>
         <v>NBR.Fases</v>
       </c>
-      <c r="O21" s="63" t="str">
-        <f t="shared" si="4"/>
-        <v>NBR.F.Estudo.Preliminar</v>
-      </c>
-      <c r="P21" s="63" t="s">
-        <v>553</v>
-      </c>
-      <c r="Q21" s="44" t="str">
-        <f t="shared" ref="Q21:Q27" si="7">_xlfn.TRANSLATE(P21,"pt","es")</f>
-        <v>Fase de Estudios Preliminares</v>
-      </c>
-      <c r="R21" s="64" t="s">
-        <v>191</v>
-      </c>
-      <c r="S21" s="65" t="str">
-        <f t="shared" si="5"/>
-        <v>NBR.Tema</v>
-      </c>
-      <c r="T21" s="65" t="str">
-        <f t="shared" si="5"/>
-        <v>NBR.Subtema</v>
-      </c>
-      <c r="U21" s="63" t="str">
-        <f t="shared" si="5"/>
-        <v>NBR.Fases</v>
-      </c>
       <c r="V21" s="44" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="W21" s="66" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>Key.ABNT.21</v>
       </c>
       <c r="X21" s="44" t="s">
@@ -7140,10 +7190,10 @@
         <v>191</v>
       </c>
       <c r="Z21" s="65" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="AA21" s="44" t="str">
-        <f t="shared" ref="AA21:AA27" si="8">_xlfn.TRANSLATE(P21,"pt","en")</f>
+        <f t="shared" ref="AA21:AA27" si="10">_xlfn.TRANSLATE(P21,"pt","en")</f>
         <v>Preliminary Studies Phase</v>
       </c>
     </row>
@@ -7155,16 +7205,16 @@
         <v>420</v>
       </c>
       <c r="C22" s="34" t="s">
+        <v>531</v>
+      </c>
+      <c r="D22" s="34" t="s">
+        <v>532</v>
+      </c>
+      <c r="E22" s="34" t="s">
         <v>538</v>
       </c>
-      <c r="D22" s="34" t="s">
-        <v>539</v>
-      </c>
-      <c r="E22" s="34" t="s">
-        <v>545</v>
-      </c>
       <c r="F22" s="12" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="G22" s="37" t="s">
         <v>191</v>
@@ -7182,48 +7232,48 @@
         <v>191</v>
       </c>
       <c r="L22" s="63" t="str">
+        <f t="shared" si="8"/>
+        <v>NBR.Tema</v>
+      </c>
+      <c r="M22" s="63" t="str">
+        <f t="shared" si="8"/>
+        <v>NBR.Subtema</v>
+      </c>
+      <c r="N22" s="63" t="str">
+        <f t="shared" si="8"/>
+        <v>NBR.Fases</v>
+      </c>
+      <c r="O22" s="63" t="str">
+        <f t="shared" si="5"/>
+        <v>NBR.F.Projetual</v>
+      </c>
+      <c r="P22" s="63" t="s">
+        <v>540</v>
+      </c>
+      <c r="Q22" s="44" t="str">
+        <f t="shared" si="9"/>
+        <v>Fase del proyecto</v>
+      </c>
+      <c r="R22" s="64" t="s">
+        <v>191</v>
+      </c>
+      <c r="S22" s="65" t="str">
         <f t="shared" si="6"/>
         <v>NBR.Tema</v>
       </c>
-      <c r="M22" s="63" t="str">
+      <c r="T22" s="65" t="str">
         <f t="shared" si="6"/>
         <v>NBR.Subtema</v>
       </c>
-      <c r="N22" s="63" t="str">
+      <c r="U22" s="63" t="str">
         <f t="shared" si="6"/>
         <v>NBR.Fases</v>
       </c>
-      <c r="O22" s="63" t="str">
-        <f t="shared" si="4"/>
-        <v>NBR.F.Projetual</v>
-      </c>
-      <c r="P22" s="63" t="s">
-        <v>547</v>
-      </c>
-      <c r="Q22" s="44" t="str">
+      <c r="V22" s="44" t="s">
+        <v>452</v>
+      </c>
+      <c r="W22" s="66" t="str">
         <f t="shared" si="7"/>
-        <v>Fase del proyecto</v>
-      </c>
-      <c r="R22" s="64" t="s">
-        <v>191</v>
-      </c>
-      <c r="S22" s="65" t="str">
-        <f t="shared" si="5"/>
-        <v>NBR.Tema</v>
-      </c>
-      <c r="T22" s="65" t="str">
-        <f t="shared" si="5"/>
-        <v>NBR.Subtema</v>
-      </c>
-      <c r="U22" s="63" t="str">
-        <f t="shared" si="5"/>
-        <v>NBR.Fases</v>
-      </c>
-      <c r="V22" s="44" t="s">
-        <v>454</v>
-      </c>
-      <c r="W22" s="66" t="str">
-        <f t="shared" si="3"/>
         <v>Key.ABNT.22</v>
       </c>
       <c r="X22" s="44" t="s">
@@ -7233,10 +7283,10 @@
         <v>191</v>
       </c>
       <c r="Z22" s="65" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="AA22" s="44" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Project Phase</v>
       </c>
     </row>
@@ -7248,75 +7298,75 @@
         <v>420</v>
       </c>
       <c r="C23" s="34" t="s">
+        <v>531</v>
+      </c>
+      <c r="D23" s="34" t="s">
+        <v>532</v>
+      </c>
+      <c r="E23" s="34" t="s">
         <v>538</v>
       </c>
-      <c r="D23" s="34" t="s">
-        <v>539</v>
-      </c>
-      <c r="E23" s="34" t="s">
+      <c r="F23" s="12" t="s">
+        <v>556</v>
+      </c>
+      <c r="G23" s="37" t="s">
+        <v>191</v>
+      </c>
+      <c r="H23" s="37" t="s">
+        <v>191</v>
+      </c>
+      <c r="I23" s="37" t="s">
+        <v>191</v>
+      </c>
+      <c r="J23" s="37" t="s">
+        <v>191</v>
+      </c>
+      <c r="K23" s="37" t="s">
+        <v>191</v>
+      </c>
+      <c r="L23" s="63" t="str">
+        <f t="shared" si="8"/>
+        <v>NBR.Tema</v>
+      </c>
+      <c r="M23" s="63" t="str">
+        <f t="shared" si="8"/>
+        <v>NBR.Subtema</v>
+      </c>
+      <c r="N23" s="63" t="str">
+        <f t="shared" si="8"/>
+        <v>NBR.Fases</v>
+      </c>
+      <c r="O23" s="63" t="str">
+        <f t="shared" si="5"/>
+        <v>NBR.F.Licitação</v>
+      </c>
+      <c r="P23" s="63" t="s">
         <v>545</v>
       </c>
-      <c r="F23" s="12" t="s">
-        <v>563</v>
-      </c>
-      <c r="G23" s="37" t="s">
-        <v>191</v>
-      </c>
-      <c r="H23" s="37" t="s">
-        <v>191</v>
-      </c>
-      <c r="I23" s="37" t="s">
-        <v>191</v>
-      </c>
-      <c r="J23" s="37" t="s">
-        <v>191</v>
-      </c>
-      <c r="K23" s="37" t="s">
-        <v>191</v>
-      </c>
-      <c r="L23" s="63" t="str">
-        <f t="shared" si="6"/>
+      <c r="Q23" s="44" t="str">
+        <f t="shared" si="9"/>
+        <v>Fase de subasta</v>
+      </c>
+      <c r="R23" s="64" t="s">
+        <v>191</v>
+      </c>
+      <c r="S23" s="65" t="str">
+        <f t="shared" ref="S23:U27" si="11">SUBSTITUTE(C23, "_", " ")</f>
         <v>NBR.Tema</v>
       </c>
-      <c r="M23" s="63" t="str">
-        <f t="shared" si="6"/>
+      <c r="T23" s="65" t="str">
+        <f t="shared" si="11"/>
         <v>NBR.Subtema</v>
       </c>
-      <c r="N23" s="63" t="str">
-        <f t="shared" si="6"/>
+      <c r="U23" s="63" t="str">
+        <f t="shared" si="11"/>
         <v>NBR.Fases</v>
       </c>
-      <c r="O23" s="63" t="str">
-        <f t="shared" si="4"/>
-        <v>NBR.F.Licitação</v>
-      </c>
-      <c r="P23" s="63" t="s">
-        <v>552</v>
-      </c>
-      <c r="Q23" s="44" t="str">
+      <c r="V23" s="44" t="s">
+        <v>452</v>
+      </c>
+      <c r="W23" s="66" t="str">
         <f t="shared" si="7"/>
-        <v>Fase de subasta</v>
-      </c>
-      <c r="R23" s="64" t="s">
-        <v>191</v>
-      </c>
-      <c r="S23" s="65" t="str">
-        <f t="shared" ref="S23:U27" si="9">SUBSTITUTE(C23, "_", " ")</f>
-        <v>NBR.Tema</v>
-      </c>
-      <c r="T23" s="65" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Subtema</v>
-      </c>
-      <c r="U23" s="63" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Fases</v>
-      </c>
-      <c r="V23" s="44" t="s">
-        <v>454</v>
-      </c>
-      <c r="W23" s="66" t="str">
-        <f t="shared" si="3"/>
         <v>Key.ABNT.23</v>
       </c>
       <c r="X23" s="44" t="s">
@@ -7326,10 +7376,10 @@
         <v>191</v>
       </c>
       <c r="Z23" s="65" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="AA23" s="44" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bidding Phase</v>
       </c>
     </row>
@@ -7341,16 +7391,16 @@
         <v>420</v>
       </c>
       <c r="C24" s="34" t="s">
+        <v>531</v>
+      </c>
+      <c r="D24" s="34" t="s">
+        <v>532</v>
+      </c>
+      <c r="E24" s="34" t="s">
         <v>538</v>
       </c>
-      <c r="D24" s="34" t="s">
-        <v>539</v>
-      </c>
-      <c r="E24" s="34" t="s">
-        <v>545</v>
-      </c>
       <c r="F24" s="12" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="G24" s="37" t="s">
         <v>191</v>
@@ -7368,48 +7418,48 @@
         <v>191</v>
       </c>
       <c r="L24" s="63" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.Tema</v>
       </c>
       <c r="M24" s="63" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.Subtema</v>
       </c>
       <c r="N24" s="63" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.Fases</v>
       </c>
       <c r="O24" s="63" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.F.Construtiva</v>
       </c>
       <c r="P24" s="63" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="Q24" s="44" t="str">
+        <f t="shared" si="9"/>
+        <v>Fase de construcción</v>
+      </c>
+      <c r="R24" s="64" t="s">
+        <v>191</v>
+      </c>
+      <c r="S24" s="65" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Tema</v>
+      </c>
+      <c r="T24" s="65" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Subtema</v>
+      </c>
+      <c r="U24" s="63" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Fases</v>
+      </c>
+      <c r="V24" s="44" t="s">
+        <v>452</v>
+      </c>
+      <c r="W24" s="66" t="str">
         <f t="shared" si="7"/>
-        <v>Fase de construcción</v>
-      </c>
-      <c r="R24" s="64" t="s">
-        <v>191</v>
-      </c>
-      <c r="S24" s="65" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Tema</v>
-      </c>
-      <c r="T24" s="65" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Subtema</v>
-      </c>
-      <c r="U24" s="63" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Fases</v>
-      </c>
-      <c r="V24" s="44" t="s">
-        <v>454</v>
-      </c>
-      <c r="W24" s="66" t="str">
-        <f t="shared" si="3"/>
         <v>Key.ABNT.24</v>
       </c>
       <c r="X24" s="44" t="s">
@@ -7419,10 +7469,10 @@
         <v>191</v>
       </c>
       <c r="Z24" s="65" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
       <c r="AA24" s="44" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Construction Phase</v>
       </c>
     </row>
@@ -7434,16 +7484,16 @@
         <v>420</v>
       </c>
       <c r="C25" s="34" t="s">
+        <v>531</v>
+      </c>
+      <c r="D25" s="34" t="s">
+        <v>532</v>
+      </c>
+      <c r="E25" s="34" t="s">
         <v>538</v>
       </c>
-      <c r="D25" s="34" t="s">
-        <v>539</v>
-      </c>
-      <c r="E25" s="34" t="s">
-        <v>545</v>
-      </c>
       <c r="F25" s="12" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="G25" s="37" t="s">
         <v>191</v>
@@ -7461,48 +7511,48 @@
         <v>191</v>
       </c>
       <c r="L25" s="63" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.Tema</v>
       </c>
       <c r="M25" s="63" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.Subtema</v>
       </c>
       <c r="N25" s="63" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.Fases</v>
       </c>
       <c r="O25" s="63" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.F.Comissionamento</v>
       </c>
       <c r="P25" s="63" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="Q25" s="44" t="str">
+        <f t="shared" si="9"/>
+        <v>Fase de puesta en servicio</v>
+      </c>
+      <c r="R25" s="64" t="s">
+        <v>191</v>
+      </c>
+      <c r="S25" s="65" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Tema</v>
+      </c>
+      <c r="T25" s="65" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Subtema</v>
+      </c>
+      <c r="U25" s="63" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Fases</v>
+      </c>
+      <c r="V25" s="44" t="s">
+        <v>452</v>
+      </c>
+      <c r="W25" s="66" t="str">
         <f t="shared" si="7"/>
-        <v>Fase de puesta en servicio</v>
-      </c>
-      <c r="R25" s="64" t="s">
-        <v>191</v>
-      </c>
-      <c r="S25" s="65" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Tema</v>
-      </c>
-      <c r="T25" s="65" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Subtema</v>
-      </c>
-      <c r="U25" s="63" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Fases</v>
-      </c>
-      <c r="V25" s="44" t="s">
-        <v>454</v>
-      </c>
-      <c r="W25" s="66" t="str">
-        <f t="shared" si="3"/>
         <v>Key.ABNT.25</v>
       </c>
       <c r="X25" s="44" t="s">
@@ -7512,10 +7562,10 @@
         <v>191</v>
       </c>
       <c r="Z25" s="65" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="AA25" s="44" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Commissioning Phase</v>
       </c>
     </row>
@@ -7527,16 +7577,16 @@
         <v>420</v>
       </c>
       <c r="C26" s="34" t="s">
+        <v>531</v>
+      </c>
+      <c r="D26" s="34" t="s">
+        <v>532</v>
+      </c>
+      <c r="E26" s="34" t="s">
         <v>538</v>
       </c>
-      <c r="D26" s="34" t="s">
-        <v>539</v>
-      </c>
-      <c r="E26" s="34" t="s">
-        <v>545</v>
-      </c>
       <c r="F26" s="12" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="G26" s="37" t="s">
         <v>191</v>
@@ -7554,48 +7604,48 @@
         <v>191</v>
       </c>
       <c r="L26" s="63" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.Tema</v>
       </c>
       <c r="M26" s="63" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.Subtema</v>
       </c>
       <c r="N26" s="63" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.Fases</v>
       </c>
       <c r="O26" s="63" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.F.Operacional</v>
       </c>
       <c r="P26" s="63" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="Q26" s="44" t="str">
+        <f t="shared" si="9"/>
+        <v>Fase de Operación</v>
+      </c>
+      <c r="R26" s="64" t="s">
+        <v>191</v>
+      </c>
+      <c r="S26" s="65" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Tema</v>
+      </c>
+      <c r="T26" s="65" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Subtema</v>
+      </c>
+      <c r="U26" s="63" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Fases</v>
+      </c>
+      <c r="V26" s="44" t="s">
+        <v>452</v>
+      </c>
+      <c r="W26" s="66" t="str">
         <f t="shared" si="7"/>
-        <v>Fase de Operación</v>
-      </c>
-      <c r="R26" s="64" t="s">
-        <v>191</v>
-      </c>
-      <c r="S26" s="65" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Tema</v>
-      </c>
-      <c r="T26" s="65" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Subtema</v>
-      </c>
-      <c r="U26" s="63" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Fases</v>
-      </c>
-      <c r="V26" s="44" t="s">
-        <v>454</v>
-      </c>
-      <c r="W26" s="66" t="str">
-        <f t="shared" si="3"/>
         <v>Key.ABNT.26</v>
       </c>
       <c r="X26" s="44" t="s">
@@ -7605,10 +7655,10 @@
         <v>191</v>
       </c>
       <c r="Z26" s="65" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
       <c r="AA26" s="44" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Operation Phase</v>
       </c>
     </row>
@@ -7620,16 +7670,16 @@
         <v>420</v>
       </c>
       <c r="C27" s="34" t="s">
+        <v>531</v>
+      </c>
+      <c r="D27" s="34" t="s">
+        <v>532</v>
+      </c>
+      <c r="E27" s="34" t="s">
         <v>538</v>
       </c>
-      <c r="D27" s="34" t="s">
-        <v>539</v>
-      </c>
-      <c r="E27" s="34" t="s">
-        <v>545</v>
-      </c>
       <c r="F27" s="12" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="G27" s="37" t="s">
         <v>191</v>
@@ -7647,48 +7697,48 @@
         <v>191</v>
       </c>
       <c r="L27" s="63" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.Tema</v>
       </c>
       <c r="M27" s="63" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.Subtema</v>
       </c>
       <c r="N27" s="63" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.Fases</v>
       </c>
       <c r="O27" s="63" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.F.Fechamento.Demolição</v>
       </c>
       <c r="P27" s="63" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="Q27" s="44" t="str">
+        <f t="shared" si="9"/>
+        <v>Fase de cierre y demolición</v>
+      </c>
+      <c r="R27" s="64" t="s">
+        <v>191</v>
+      </c>
+      <c r="S27" s="65" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Tema</v>
+      </c>
+      <c r="T27" s="65" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Subtema</v>
+      </c>
+      <c r="U27" s="63" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Fases</v>
+      </c>
+      <c r="V27" s="44" t="s">
+        <v>452</v>
+      </c>
+      <c r="W27" s="66" t="str">
         <f t="shared" si="7"/>
-        <v>Fase de cierre y demolición</v>
-      </c>
-      <c r="R27" s="64" t="s">
-        <v>191</v>
-      </c>
-      <c r="S27" s="65" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Tema</v>
-      </c>
-      <c r="T27" s="65" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Subtema</v>
-      </c>
-      <c r="U27" s="63" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Fases</v>
-      </c>
-      <c r="V27" s="44" t="s">
-        <v>454</v>
-      </c>
-      <c r="W27" s="66" t="str">
-        <f t="shared" si="3"/>
         <v>Key.ABNT.27</v>
       </c>
       <c r="X27" s="44" t="s">
@@ -7698,48 +7748,43 @@
         <v>191</v>
       </c>
       <c r="Z27" s="65" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="AA27" s="44" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Closure and Demolition Phase</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A7:A27">
+    <cfRule type="cellIs" dxfId="30" priority="9" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F20">
+    <cfRule type="duplicateValues" dxfId="25" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA1 AA7:AA27">
+    <cfRule type="cellIs" dxfId="21" priority="7" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A2:A6">
-    <cfRule type="cellIs" dxfId="27" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="26" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA1:AA6">
-    <cfRule type="cellIs" dxfId="22" priority="13" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A7:A27">
-    <cfRule type="cellIs" dxfId="21" priority="6" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA7:AA19">
-    <cfRule type="cellIs" dxfId="20" priority="7" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F20">
-    <cfRule type="duplicateValues" dxfId="19" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA20:AA27">
-    <cfRule type="cellIs" dxfId="15" priority="5" operator="equal">
+  <conditionalFormatting sqref="AA2:AA6">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7889,7 +7934,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7934,7 +7979,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8082,13 +8127,13 @@
         <v>366</v>
       </c>
       <c r="K2" s="52" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="L2" s="51" t="s">
         <v>424</v>
       </c>
       <c r="M2" s="52" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="N2" s="38" t="s">
         <v>1</v>
@@ -8135,10 +8180,10 @@
         <v>371</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="D3" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E3" s="69" t="s">
         <v>367</v>
@@ -8159,13 +8204,13 @@
         <v>366</v>
       </c>
       <c r="K3" s="52" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="L3" s="51" t="s">
         <v>424</v>
       </c>
       <c r="M3" s="52" t="s">
-        <v>522</v>
+        <v>569</v>
       </c>
       <c r="N3" s="38" t="s">
         <v>1</v>
@@ -8212,10 +8257,10 @@
         <v>369</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="D4" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E4" s="69" t="s">
         <v>371</v>
@@ -8236,13 +8281,13 @@
         <v>366</v>
       </c>
       <c r="K4" s="52" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="L4" s="51" t="s">
         <v>424</v>
       </c>
       <c r="M4" s="52" t="s">
-        <v>522</v>
+        <v>570</v>
       </c>
       <c r="N4" s="38" t="s">
         <v>1</v>
@@ -8289,10 +8334,10 @@
         <v>199</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="D5" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E5" s="69" t="s">
         <v>371</v>
@@ -8319,7 +8364,7 @@
         <v>424</v>
       </c>
       <c r="M5" s="39" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="N5" s="38" t="s">
         <v>1</v>
@@ -8366,10 +8411,10 @@
         <v>200</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="D6" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E6" s="69" t="s">
         <v>371</v>
@@ -8396,7 +8441,7 @@
         <v>424</v>
       </c>
       <c r="M6" s="39" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="N6" s="38" t="s">
         <v>1</v>
@@ -8443,10 +8488,10 @@
         <v>201</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="D7" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E7" s="69" t="s">
         <v>371</v>
@@ -8473,7 +8518,7 @@
         <v>424</v>
       </c>
       <c r="M7" s="39" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="N7" s="38" t="s">
         <v>1</v>
@@ -8520,10 +8565,10 @@
         <v>202</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="D8" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E8" s="69" t="s">
         <v>371</v>
@@ -8550,7 +8595,7 @@
         <v>424</v>
       </c>
       <c r="M8" s="39" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="N8" s="38" t="s">
         <v>1</v>
@@ -8597,10 +8642,10 @@
         <v>203</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="D9" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E9" s="69" t="s">
         <v>371</v>
@@ -8627,7 +8672,7 @@
         <v>424</v>
       </c>
       <c r="M9" s="39" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="N9" s="38" t="s">
         <v>1</v>
@@ -8674,10 +8719,10 @@
         <v>204</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="D10" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E10" s="69" t="s">
         <v>371</v>
@@ -8704,7 +8749,7 @@
         <v>424</v>
       </c>
       <c r="M10" s="39" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="N10" s="38" t="s">
         <v>1</v>
@@ -8751,10 +8796,10 @@
         <v>205</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="D11" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E11" s="69" t="s">
         <v>371</v>
@@ -8781,7 +8826,7 @@
         <v>424</v>
       </c>
       <c r="M11" s="39" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="N11" s="38" t="s">
         <v>1</v>
@@ -8828,10 +8873,10 @@
         <v>206</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="D12" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E12" s="69" t="s">
         <v>371</v>
@@ -8858,7 +8903,7 @@
         <v>424</v>
       </c>
       <c r="M12" s="39" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="N12" s="38" t="s">
         <v>1</v>
@@ -8905,10 +8950,10 @@
         <v>207</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="D13" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E13" s="69" t="s">
         <v>371</v>
@@ -8935,7 +8980,7 @@
         <v>424</v>
       </c>
       <c r="M13" s="39" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="N13" s="38" t="s">
         <v>1</v>
@@ -8982,10 +9027,10 @@
         <v>208</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="D14" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E14" s="69" t="s">
         <v>371</v>
@@ -9012,7 +9057,7 @@
         <v>424</v>
       </c>
       <c r="M14" s="39" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="N14" s="38" t="s">
         <v>1</v>
@@ -9059,10 +9104,10 @@
         <v>209</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="D15" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E15" s="69" t="s">
         <v>371</v>
@@ -9089,7 +9134,7 @@
         <v>424</v>
       </c>
       <c r="M15" s="39" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="N15" s="38" t="s">
         <v>1</v>
@@ -9136,10 +9181,10 @@
         <v>210</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="D16" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E16" s="69" t="s">
         <v>371</v>
@@ -9166,7 +9211,7 @@
         <v>424</v>
       </c>
       <c r="M16" s="39" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="N16" s="38" t="s">
         <v>1</v>
@@ -9213,10 +9258,10 @@
         <v>211</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="D17" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E17" s="69" t="s">
         <v>371</v>
@@ -9243,7 +9288,7 @@
         <v>424</v>
       </c>
       <c r="M17" s="39" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="N17" s="38" t="s">
         <v>1</v>
@@ -9290,10 +9335,10 @@
         <v>212</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="D18" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E18" s="69" t="s">
         <v>371</v>
@@ -9320,7 +9365,7 @@
         <v>424</v>
       </c>
       <c r="M18" s="39" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="N18" s="38" t="s">
         <v>1</v>
@@ -9367,10 +9412,10 @@
         <v>213</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="D19" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E19" s="69" t="s">
         <v>371</v>
@@ -9397,7 +9442,7 @@
         <v>424</v>
       </c>
       <c r="M19" s="39" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="N19" s="38" t="s">
         <v>1</v>
@@ -9444,10 +9489,10 @@
         <v>214</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="D20" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E20" s="69" t="s">
         <v>371</v>
@@ -9474,7 +9519,7 @@
         <v>424</v>
       </c>
       <c r="M20" s="39" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="N20" s="38" t="s">
         <v>1</v>
@@ -9521,10 +9566,10 @@
         <v>215</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="D21" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E21" s="69" t="s">
         <v>371</v>
@@ -9551,7 +9596,7 @@
         <v>424</v>
       </c>
       <c r="M21" s="39" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="N21" s="38" t="s">
         <v>1</v>
@@ -9598,10 +9643,10 @@
         <v>216</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="D22" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E22" s="69" t="s">
         <v>371</v>
@@ -9628,7 +9673,7 @@
         <v>424</v>
       </c>
       <c r="M22" s="39" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="N22" s="38" t="s">
         <v>1</v>
@@ -9675,10 +9720,10 @@
         <v>217</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="D23" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E23" s="69" t="s">
         <v>371</v>
@@ -9705,7 +9750,7 @@
         <v>424</v>
       </c>
       <c r="M23" s="39" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="N23" s="38" t="s">
         <v>1</v>
@@ -9752,10 +9797,10 @@
         <v>218</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="D24" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E24" s="69" t="s">
         <v>371</v>
@@ -9782,7 +9827,7 @@
         <v>424</v>
       </c>
       <c r="M24" s="39" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="N24" s="38" t="s">
         <v>1</v>
@@ -9829,10 +9874,10 @@
         <v>219</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="D25" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E25" s="69" t="s">
         <v>371</v>
@@ -9859,7 +9904,7 @@
         <v>424</v>
       </c>
       <c r="M25" s="39" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="N25" s="38" t="s">
         <v>1</v>
@@ -9906,10 +9951,10 @@
         <v>220</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="D26" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E26" s="69" t="s">
         <v>371</v>
@@ -9936,7 +9981,7 @@
         <v>424</v>
       </c>
       <c r="M26" s="39" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="N26" s="38" t="s">
         <v>1</v>
@@ -9983,10 +10028,10 @@
         <v>221</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="D27" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E27" s="69" t="s">
         <v>371</v>
@@ -10013,7 +10058,7 @@
         <v>424</v>
       </c>
       <c r="M27" s="39" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="N27" s="38" t="s">
         <v>1</v>
@@ -10060,10 +10105,10 @@
         <v>222</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="D28" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E28" s="69" t="s">
         <v>371</v>
@@ -10090,7 +10135,7 @@
         <v>424</v>
       </c>
       <c r="M28" s="39" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="N28" s="38" t="s">
         <v>1</v>
@@ -10137,10 +10182,10 @@
         <v>223</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="D29" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E29" s="69" t="s">
         <v>371</v>
@@ -10167,7 +10212,7 @@
         <v>424</v>
       </c>
       <c r="M29" s="39" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="N29" s="38" t="s">
         <v>1</v>
@@ -10214,10 +10259,10 @@
         <v>224</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="D30" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E30" s="69" t="s">
         <v>371</v>
@@ -10244,7 +10289,7 @@
         <v>424</v>
       </c>
       <c r="M30" s="39" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="N30" s="38" t="s">
         <v>1</v>
@@ -10291,10 +10336,10 @@
         <v>225</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="D31" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E31" s="69" t="s">
         <v>371</v>
@@ -10321,7 +10366,7 @@
         <v>424</v>
       </c>
       <c r="M31" s="39" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="N31" s="38" t="s">
         <v>1</v>
@@ -10368,10 +10413,10 @@
         <v>226</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="D32" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E32" s="69" t="s">
         <v>371</v>
@@ -10398,7 +10443,7 @@
         <v>424</v>
       </c>
       <c r="M32" s="39" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="N32" s="38" t="s">
         <v>1</v>
@@ -10445,10 +10490,10 @@
         <v>227</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="D33" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E33" s="69" t="s">
         <v>371</v>
@@ -10475,7 +10520,7 @@
         <v>424</v>
       </c>
       <c r="M33" s="39" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="N33" s="38" t="s">
         <v>1</v>
@@ -10522,10 +10567,10 @@
         <v>228</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="D34" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E34" s="69" t="s">
         <v>371</v>
@@ -10552,7 +10597,7 @@
         <v>424</v>
       </c>
       <c r="M34" s="39" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="N34" s="38" t="s">
         <v>1</v>
@@ -10599,10 +10644,10 @@
         <v>229</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="D35" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E35" s="69" t="s">
         <v>371</v>
@@ -10629,7 +10674,7 @@
         <v>424</v>
       </c>
       <c r="M35" s="39" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="N35" s="38" t="s">
         <v>1</v>
@@ -10676,10 +10721,10 @@
         <v>230</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="D36" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E36" s="69" t="s">
         <v>371</v>
@@ -10706,7 +10751,7 @@
         <v>424</v>
       </c>
       <c r="M36" s="39" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="N36" s="38" t="s">
         <v>1</v>
@@ -10753,10 +10798,10 @@
         <v>231</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="D37" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E37" s="69" t="s">
         <v>371</v>
@@ -10783,7 +10828,7 @@
         <v>424</v>
       </c>
       <c r="M37" s="39" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="N37" s="38" t="s">
         <v>1</v>
@@ -10830,10 +10875,10 @@
         <v>232</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="D38" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E38" s="69" t="s">
         <v>371</v>
@@ -10860,7 +10905,7 @@
         <v>424</v>
       </c>
       <c r="M38" s="39" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="N38" s="38" t="s">
         <v>1</v>
@@ -10907,10 +10952,10 @@
         <v>233</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="D39" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E39" s="69" t="s">
         <v>371</v>
@@ -10937,7 +10982,7 @@
         <v>424</v>
       </c>
       <c r="M39" s="39" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="N39" s="38" t="s">
         <v>1</v>
@@ -10984,10 +11029,10 @@
         <v>234</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="D40" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E40" s="69" t="s">
         <v>371</v>
@@ -11014,7 +11059,7 @@
         <v>424</v>
       </c>
       <c r="M40" s="39" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="N40" s="38" t="s">
         <v>1</v>
@@ -11061,10 +11106,10 @@
         <v>235</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="D41" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E41" s="69" t="s">
         <v>371</v>
@@ -11091,7 +11136,7 @@
         <v>424</v>
       </c>
       <c r="M41" s="39" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="N41" s="38" t="s">
         <v>1</v>
@@ -11138,10 +11183,10 @@
         <v>236</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="D42" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E42" s="69" t="s">
         <v>371</v>
@@ -11168,7 +11213,7 @@
         <v>424</v>
       </c>
       <c r="M42" s="39" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="N42" s="38" t="s">
         <v>1</v>
@@ -11215,10 +11260,10 @@
         <v>237</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="D43" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E43" s="69" t="s">
         <v>371</v>
@@ -11245,7 +11290,7 @@
         <v>424</v>
       </c>
       <c r="M43" s="39" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="N43" s="38" t="s">
         <v>1</v>
@@ -11292,10 +11337,10 @@
         <v>238</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="D44" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E44" s="69" t="s">
         <v>371</v>
@@ -11322,7 +11367,7 @@
         <v>424</v>
       </c>
       <c r="M44" s="39" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="N44" s="38" t="s">
         <v>1</v>
@@ -11369,10 +11414,10 @@
         <v>239</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="D45" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E45" s="69" t="s">
         <v>371</v>
@@ -11399,7 +11444,7 @@
         <v>424</v>
       </c>
       <c r="M45" s="39" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="N45" s="38" t="s">
         <v>1</v>
@@ -11446,10 +11491,10 @@
         <v>240</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="D46" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E46" s="69" t="s">
         <v>371</v>
@@ -11476,7 +11521,7 @@
         <v>424</v>
       </c>
       <c r="M46" s="39" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="N46" s="38" t="s">
         <v>1</v>
@@ -11523,10 +11568,10 @@
         <v>241</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="D47" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E47" s="69" t="s">
         <v>371</v>
@@ -11553,7 +11598,7 @@
         <v>424</v>
       </c>
       <c r="M47" s="39" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="N47" s="38" t="s">
         <v>1</v>
@@ -11600,10 +11645,10 @@
         <v>242</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="D48" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E48" s="69" t="s">
         <v>371</v>
@@ -11630,7 +11675,7 @@
         <v>424</v>
       </c>
       <c r="M48" s="39" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="N48" s="38" t="s">
         <v>1</v>
@@ -11677,10 +11722,10 @@
         <v>243</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="D49" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E49" s="69" t="s">
         <v>371</v>
@@ -11707,7 +11752,7 @@
         <v>424</v>
       </c>
       <c r="M49" s="39" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="N49" s="38" t="s">
         <v>1</v>
@@ -11754,10 +11799,10 @@
         <v>244</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="D50" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E50" s="69" t="s">
         <v>371</v>
@@ -11784,7 +11829,7 @@
         <v>424</v>
       </c>
       <c r="M50" s="39" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="N50" s="38" t="s">
         <v>1</v>
@@ -11831,10 +11876,10 @@
         <v>245</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="D51" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E51" s="69" t="s">
         <v>371</v>
@@ -11861,7 +11906,7 @@
         <v>424</v>
       </c>
       <c r="M51" s="39" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="N51" s="38" t="s">
         <v>1</v>
@@ -11908,10 +11953,10 @@
         <v>246</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="D52" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E52" s="69" t="s">
         <v>371</v>
@@ -11985,10 +12030,10 @@
         <v>247</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="D53" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E53" s="69" t="s">
         <v>371</v>
@@ -12062,10 +12107,10 @@
         <v>248</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="D54" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E54" s="69" t="s">
         <v>371</v>
@@ -12139,10 +12184,10 @@
         <v>249</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="D55" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E55" s="69" t="s">
         <v>371</v>
@@ -12216,10 +12261,10 @@
         <v>250</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="D56" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E56" s="69" t="s">
         <v>371</v>
@@ -12293,10 +12338,10 @@
         <v>251</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="D57" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E57" s="69" t="s">
         <v>371</v>
@@ -12370,10 +12415,10 @@
         <v>252</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="D58" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E58" s="69" t="s">
         <v>371</v>
@@ -12447,10 +12492,10 @@
         <v>253</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="D59" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E59" s="69" t="s">
         <v>371</v>
@@ -12524,10 +12569,10 @@
         <v>254</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="D60" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E60" s="69" t="s">
         <v>371</v>
@@ -12601,10 +12646,10 @@
         <v>255</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="D61" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E61" s="69" t="s">
         <v>371</v>
@@ -12678,10 +12723,10 @@
         <v>256</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="D62" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E62" s="69" t="s">
         <v>371</v>
@@ -12755,10 +12800,10 @@
         <v>257</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="D63" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E63" s="69" t="s">
         <v>371</v>
@@ -12832,10 +12877,10 @@
         <v>258</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="D64" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E64" s="69" t="s">
         <v>371</v>
@@ -12909,10 +12954,10 @@
         <v>259</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="D65" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E65" s="69" t="s">
         <v>371</v>
@@ -12986,10 +13031,10 @@
         <v>260</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="D66" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E66" s="69" t="s">
         <v>371</v>
@@ -13063,10 +13108,10 @@
         <v>261</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="D67" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E67" s="69" t="s">
         <v>371</v>
@@ -13140,10 +13185,10 @@
         <v>262</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="D68" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E68" s="69" t="s">
         <v>371</v>
@@ -13217,10 +13262,10 @@
         <v>263</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="D69" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E69" s="69" t="s">
         <v>371</v>
@@ -13294,10 +13339,10 @@
         <v>264</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="D70" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E70" s="69" t="s">
         <v>371</v>
@@ -13371,10 +13416,10 @@
         <v>265</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="D71" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E71" s="69" t="s">
         <v>371</v>
@@ -13448,10 +13493,10 @@
         <v>266</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="D72" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E72" s="69" t="s">
         <v>371</v>
@@ -13525,10 +13570,10 @@
         <v>267</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="D73" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E73" s="69" t="s">
         <v>371</v>
@@ -13602,10 +13647,10 @@
         <v>268</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="D74" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E74" s="69" t="s">
         <v>371</v>
@@ -13679,10 +13724,10 @@
         <v>269</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="D75" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E75" s="69" t="s">
         <v>371</v>
@@ -13756,10 +13801,10 @@
         <v>270</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="D76" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E76" s="69" t="s">
         <v>371</v>
@@ -13833,10 +13878,10 @@
         <v>271</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="D77" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E77" s="69" t="s">
         <v>371</v>
@@ -13910,10 +13955,10 @@
         <v>272</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="D78" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E78" s="69" t="s">
         <v>371</v>
@@ -13987,10 +14032,10 @@
         <v>273</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="D79" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E79" s="69" t="s">
         <v>371</v>
@@ -14017,7 +14062,7 @@
         <v>424</v>
       </c>
       <c r="M79" s="39" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="N79" s="38" t="s">
         <v>1</v>
@@ -14064,10 +14109,10 @@
         <v>274</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="D80" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E80" s="69" t="s">
         <v>371</v>
@@ -14094,7 +14139,7 @@
         <v>424</v>
       </c>
       <c r="M80" s="39" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="N80" s="38" t="s">
         <v>1</v>
@@ -14141,10 +14186,10 @@
         <v>275</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="D81" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E81" s="69" t="s">
         <v>371</v>
@@ -14171,7 +14216,7 @@
         <v>424</v>
       </c>
       <c r="M81" s="39" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="N81" s="38" t="s">
         <v>1</v>
@@ -14218,10 +14263,10 @@
         <v>276</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="D82" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E82" s="69" t="s">
         <v>371</v>
@@ -14248,7 +14293,7 @@
         <v>424</v>
       </c>
       <c r="M82" s="39" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="N82" s="38" t="s">
         <v>1</v>
@@ -14295,10 +14340,10 @@
         <v>277</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="D83" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E83" s="69" t="s">
         <v>371</v>
@@ -14325,7 +14370,7 @@
         <v>424</v>
       </c>
       <c r="M83" s="39" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="N83" s="38" t="s">
         <v>1</v>
@@ -14372,10 +14417,10 @@
         <v>278</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="D84" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E84" s="69" t="s">
         <v>371</v>
@@ -14402,7 +14447,7 @@
         <v>424</v>
       </c>
       <c r="M84" s="39" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="N84" s="38" t="s">
         <v>1</v>
@@ -14449,10 +14494,10 @@
         <v>279</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="D85" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E85" s="69" t="s">
         <v>371</v>
@@ -14479,7 +14524,7 @@
         <v>424</v>
       </c>
       <c r="M85" s="39" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="N85" s="38" t="s">
         <v>1</v>
@@ -14526,10 +14571,10 @@
         <v>280</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="D86" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E86" s="69" t="s">
         <v>371</v>
@@ -14556,7 +14601,7 @@
         <v>424</v>
       </c>
       <c r="M86" s="39" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="N86" s="38" t="s">
         <v>1</v>
@@ -14603,10 +14648,10 @@
         <v>281</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="D87" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E87" s="69" t="s">
         <v>371</v>
@@ -14633,7 +14678,7 @@
         <v>424</v>
       </c>
       <c r="M87" s="39" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="N87" s="38" t="s">
         <v>1</v>
@@ -14680,10 +14725,10 @@
         <v>282</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="D88" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E88" s="69" t="s">
         <v>371</v>
@@ -14710,7 +14755,7 @@
         <v>424</v>
       </c>
       <c r="M88" s="39" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="N88" s="38" t="s">
         <v>1</v>
@@ -14757,10 +14802,10 @@
         <v>283</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="D89" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E89" s="69" t="s">
         <v>371</v>
@@ -14787,7 +14832,7 @@
         <v>424</v>
       </c>
       <c r="M89" s="39" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="N89" s="38" t="s">
         <v>1</v>
@@ -14834,10 +14879,10 @@
         <v>284</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="D90" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E90" s="69" t="s">
         <v>371</v>
@@ -14864,7 +14909,7 @@
         <v>424</v>
       </c>
       <c r="M90" s="39" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="N90" s="38" t="s">
         <v>1</v>
@@ -14911,10 +14956,10 @@
         <v>285</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="D91" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E91" s="69" t="s">
         <v>371</v>
@@ -14941,7 +14986,7 @@
         <v>424</v>
       </c>
       <c r="M91" s="39" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="N91" s="38" t="s">
         <v>1</v>
@@ -14988,10 +15033,10 @@
         <v>286</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="D92" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E92" s="69" t="s">
         <v>371</v>
@@ -15018,7 +15063,7 @@
         <v>424</v>
       </c>
       <c r="M92" s="39" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="N92" s="38" t="s">
         <v>1</v>
@@ -15065,10 +15110,10 @@
         <v>287</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="D93" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E93" s="69" t="s">
         <v>371</v>
@@ -15095,7 +15140,7 @@
         <v>424</v>
       </c>
       <c r="M93" s="39" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="N93" s="38" t="s">
         <v>1</v>
@@ -15142,10 +15187,10 @@
         <v>288</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="D94" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E94" s="69" t="s">
         <v>371</v>
@@ -15172,7 +15217,7 @@
         <v>424</v>
       </c>
       <c r="M94" s="39" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="N94" s="38" t="s">
         <v>1</v>
@@ -15219,10 +15264,10 @@
         <v>289</v>
       </c>
       <c r="C95" s="12" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="D95" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E95" s="69" t="s">
         <v>371</v>
@@ -15249,7 +15294,7 @@
         <v>424</v>
       </c>
       <c r="M95" s="39" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="N95" s="38" t="s">
         <v>1</v>
@@ -15296,10 +15341,10 @@
         <v>290</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D96" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E96" s="69" t="s">
         <v>371</v>
@@ -15326,7 +15371,7 @@
         <v>424</v>
       </c>
       <c r="M96" s="39" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="N96" s="38" t="s">
         <v>1</v>
@@ -15373,10 +15418,10 @@
         <v>291</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D97" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E97" s="69" t="s">
         <v>371</v>
@@ -15403,7 +15448,7 @@
         <v>424</v>
       </c>
       <c r="M97" s="39" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="N97" s="38" t="s">
         <v>1</v>
@@ -15450,10 +15495,10 @@
         <v>292</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D98" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E98" s="69" t="s">
         <v>371</v>
@@ -15480,7 +15525,7 @@
         <v>424</v>
       </c>
       <c r="M98" s="39" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="N98" s="38" t="s">
         <v>1</v>
@@ -15527,10 +15572,10 @@
         <v>293</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D99" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E99" s="69" t="s">
         <v>371</v>
@@ -15557,7 +15602,7 @@
         <v>424</v>
       </c>
       <c r="M99" s="39" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="N99" s="38" t="s">
         <v>1</v>
@@ -15604,10 +15649,10 @@
         <v>294</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D100" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E100" s="69" t="s">
         <v>371</v>
@@ -15634,7 +15679,7 @@
         <v>424</v>
       </c>
       <c r="M100" s="39" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="N100" s="38" t="s">
         <v>1</v>
@@ -15681,10 +15726,10 @@
         <v>295</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D101" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E101" s="69" t="s">
         <v>371</v>
@@ -15711,7 +15756,7 @@
         <v>424</v>
       </c>
       <c r="M101" s="39" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="N101" s="38" t="s">
         <v>1</v>
@@ -15758,10 +15803,10 @@
         <v>296</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D102" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E102" s="69" t="s">
         <v>371</v>
@@ -15788,7 +15833,7 @@
         <v>424</v>
       </c>
       <c r="M102" s="39" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="N102" s="38" t="s">
         <v>1</v>
@@ -15835,10 +15880,10 @@
         <v>297</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D103" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E103" s="69" t="s">
         <v>371</v>
@@ -15865,7 +15910,7 @@
         <v>424</v>
       </c>
       <c r="M103" s="39" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="N103" s="38" t="s">
         <v>1</v>
@@ -15912,10 +15957,10 @@
         <v>298</v>
       </c>
       <c r="C104" s="12" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D104" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E104" s="69" t="s">
         <v>371</v>
@@ -15942,7 +15987,7 @@
         <v>424</v>
       </c>
       <c r="M104" s="39" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="N104" s="38" t="s">
         <v>1</v>
@@ -15989,10 +16034,10 @@
         <v>299</v>
       </c>
       <c r="C105" s="12" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D105" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E105" s="69" t="s">
         <v>371</v>
@@ -16019,7 +16064,7 @@
         <v>424</v>
       </c>
       <c r="M105" s="39" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="N105" s="38" t="s">
         <v>1</v>
@@ -16066,10 +16111,10 @@
         <v>300</v>
       </c>
       <c r="C106" s="12" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D106" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E106" s="69" t="s">
         <v>371</v>
@@ -16096,7 +16141,7 @@
         <v>424</v>
       </c>
       <c r="M106" s="39" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="N106" s="38" t="s">
         <v>1</v>
@@ -16143,10 +16188,10 @@
         <v>301</v>
       </c>
       <c r="C107" s="12" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D107" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E107" s="69" t="s">
         <v>371</v>
@@ -16173,7 +16218,7 @@
         <v>424</v>
       </c>
       <c r="M107" s="39" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="N107" s="38" t="s">
         <v>1</v>
@@ -16220,10 +16265,10 @@
         <v>302</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D108" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E108" s="69" t="s">
         <v>371</v>
@@ -16250,7 +16295,7 @@
         <v>424</v>
       </c>
       <c r="M108" s="39" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="N108" s="38" t="s">
         <v>1</v>
@@ -16297,10 +16342,10 @@
         <v>303</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D109" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E109" s="69" t="s">
         <v>371</v>
@@ -16327,7 +16372,7 @@
         <v>424</v>
       </c>
       <c r="M109" s="39" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="N109" s="38" t="s">
         <v>1</v>
@@ -16374,10 +16419,10 @@
         <v>304</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D110" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E110" s="69" t="s">
         <v>371</v>
@@ -16404,7 +16449,7 @@
         <v>424</v>
       </c>
       <c r="M110" s="39" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="N110" s="38" t="s">
         <v>1</v>
@@ -16451,10 +16496,10 @@
         <v>305</v>
       </c>
       <c r="C111" s="12" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D111" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E111" s="69" t="s">
         <v>371</v>
@@ -16481,7 +16526,7 @@
         <v>424</v>
       </c>
       <c r="M111" s="39" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="N111" s="38" t="s">
         <v>1</v>
@@ -16528,10 +16573,10 @@
         <v>306</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D112" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E112" s="69" t="s">
         <v>371</v>
@@ -16558,7 +16603,7 @@
         <v>424</v>
       </c>
       <c r="M112" s="39" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="N112" s="38" t="s">
         <v>1</v>
@@ -16605,10 +16650,10 @@
         <v>307</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D113" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E113" s="69" t="s">
         <v>371</v>
@@ -16635,7 +16680,7 @@
         <v>424</v>
       </c>
       <c r="M113" s="39" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="N113" s="38" t="s">
         <v>1</v>
@@ -16682,10 +16727,10 @@
         <v>308</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D114" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E114" s="69" t="s">
         <v>371</v>
@@ -16712,7 +16757,7 @@
         <v>424</v>
       </c>
       <c r="M114" s="39" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="N114" s="38" t="s">
         <v>1</v>
@@ -16759,10 +16804,10 @@
         <v>309</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D115" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E115" s="69" t="s">
         <v>371</v>
@@ -16789,7 +16834,7 @@
         <v>424</v>
       </c>
       <c r="M115" s="39" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="N115" s="38" t="s">
         <v>1</v>
@@ -16836,10 +16881,10 @@
         <v>310</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D116" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E116" s="69" t="s">
         <v>371</v>
@@ -16866,7 +16911,7 @@
         <v>424</v>
       </c>
       <c r="M116" s="39" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="N116" s="38" t="s">
         <v>1</v>
@@ -16913,10 +16958,10 @@
         <v>311</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D117" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E117" s="69" t="s">
         <v>371</v>
@@ -16943,7 +16988,7 @@
         <v>424</v>
       </c>
       <c r="M117" s="39" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="N117" s="38" t="s">
         <v>1</v>
@@ -16990,10 +17035,10 @@
         <v>312</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D118" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E118" s="69" t="s">
         <v>371</v>
@@ -17020,7 +17065,7 @@
         <v>424</v>
       </c>
       <c r="M118" s="39" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="N118" s="38" t="s">
         <v>1</v>
@@ -17067,10 +17112,10 @@
         <v>313</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D119" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E119" s="69" t="s">
         <v>371</v>
@@ -17097,7 +17142,7 @@
         <v>424</v>
       </c>
       <c r="M119" s="39" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="N119" s="38" t="s">
         <v>1</v>
@@ -17144,10 +17189,10 @@
         <v>314</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D120" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E120" s="69" t="s">
         <v>371</v>
@@ -17174,7 +17219,7 @@
         <v>424</v>
       </c>
       <c r="M120" s="39" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="N120" s="38" t="s">
         <v>1</v>
@@ -17221,10 +17266,10 @@
         <v>315</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D121" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E121" s="69" t="s">
         <v>371</v>
@@ -17251,7 +17296,7 @@
         <v>424</v>
       </c>
       <c r="M121" s="39" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="N121" s="38" t="s">
         <v>1</v>
@@ -17298,10 +17343,10 @@
         <v>316</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D122" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E122" s="69" t="s">
         <v>371</v>
@@ -17328,7 +17373,7 @@
         <v>424</v>
       </c>
       <c r="M122" s="39" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="N122" s="38" t="s">
         <v>1</v>
@@ -17375,10 +17420,10 @@
         <v>317</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D123" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E123" s="69" t="s">
         <v>371</v>
@@ -17405,7 +17450,7 @@
         <v>424</v>
       </c>
       <c r="M123" s="39" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="N123" s="38" t="s">
         <v>1</v>
@@ -17452,10 +17497,10 @@
         <v>318</v>
       </c>
       <c r="C124" s="12" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D124" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E124" s="69" t="s">
         <v>371</v>
@@ -17482,7 +17527,7 @@
         <v>424</v>
       </c>
       <c r="M124" s="39" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="N124" s="38" t="s">
         <v>1</v>
@@ -17529,10 +17574,10 @@
         <v>319</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D125" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E125" s="69" t="s">
         <v>371</v>
@@ -17559,7 +17604,7 @@
         <v>424</v>
       </c>
       <c r="M125" s="39" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="N125" s="38" t="s">
         <v>1</v>
@@ -17606,10 +17651,10 @@
         <v>320</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D126" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E126" s="69" t="s">
         <v>371</v>
@@ -17636,7 +17681,7 @@
         <v>424</v>
       </c>
       <c r="M126" s="39" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="N126" s="38" t="s">
         <v>1</v>
@@ -17683,10 +17728,10 @@
         <v>321</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D127" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E127" s="69" t="s">
         <v>371</v>
@@ -17713,7 +17758,7 @@
         <v>424</v>
       </c>
       <c r="M127" s="39" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="N127" s="38" t="s">
         <v>1</v>
@@ -17760,10 +17805,10 @@
         <v>322</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D128" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E128" s="69" t="s">
         <v>371</v>
@@ -17790,7 +17835,7 @@
         <v>424</v>
       </c>
       <c r="M128" s="39" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="N128" s="38" t="s">
         <v>1</v>
@@ -17837,10 +17882,10 @@
         <v>323</v>
       </c>
       <c r="C129" s="12" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D129" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E129" s="69" t="s">
         <v>371</v>
@@ -17867,7 +17912,7 @@
         <v>424</v>
       </c>
       <c r="M129" s="39" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="N129" s="38" t="s">
         <v>1</v>
@@ -17914,10 +17959,10 @@
         <v>324</v>
       </c>
       <c r="C130" s="12" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D130" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E130" s="69" t="s">
         <v>371</v>
@@ -17944,7 +17989,7 @@
         <v>424</v>
       </c>
       <c r="M130" s="39" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="N130" s="38" t="s">
         <v>1</v>
@@ -17991,10 +18036,10 @@
         <v>325</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D131" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E131" s="69" t="s">
         <v>371</v>
@@ -18021,7 +18066,7 @@
         <v>424</v>
       </c>
       <c r="M131" s="39" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="N131" s="38" t="s">
         <v>1</v>
@@ -18068,10 +18113,10 @@
         <v>326</v>
       </c>
       <c r="C132" s="12" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D132" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E132" s="69" t="s">
         <v>371</v>
@@ -18098,7 +18143,7 @@
         <v>424</v>
       </c>
       <c r="M132" s="39" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="N132" s="38" t="s">
         <v>1</v>
@@ -18145,10 +18190,10 @@
         <v>327</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D133" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E133" s="69" t="s">
         <v>371</v>
@@ -18175,7 +18220,7 @@
         <v>424</v>
       </c>
       <c r="M133" s="39" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="N133" s="38" t="s">
         <v>1</v>
@@ -18222,10 +18267,10 @@
         <v>328</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D134" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E134" s="69" t="s">
         <v>371</v>
@@ -18252,7 +18297,7 @@
         <v>424</v>
       </c>
       <c r="M134" s="39" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="N134" s="38" t="s">
         <v>1</v>
@@ -18299,10 +18344,10 @@
         <v>329</v>
       </c>
       <c r="C135" s="12" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D135" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E135" s="69" t="s">
         <v>371</v>
@@ -18329,7 +18374,7 @@
         <v>424</v>
       </c>
       <c r="M135" s="39" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="N135" s="38" t="s">
         <v>1</v>
@@ -18376,10 +18421,10 @@
         <v>330</v>
       </c>
       <c r="C136" s="12" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D136" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E136" s="69" t="s">
         <v>371</v>
@@ -18406,7 +18451,7 @@
         <v>424</v>
       </c>
       <c r="M136" s="39" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="N136" s="38" t="s">
         <v>1</v>
@@ -18453,10 +18498,10 @@
         <v>331</v>
       </c>
       <c r="C137" s="12" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D137" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E137" s="69" t="s">
         <v>371</v>
@@ -18483,7 +18528,7 @@
         <v>424</v>
       </c>
       <c r="M137" s="39" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="N137" s="38" t="s">
         <v>1</v>
@@ -18530,10 +18575,10 @@
         <v>332</v>
       </c>
       <c r="C138" s="12" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="D138" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E138" s="69" t="s">
         <v>371</v>
@@ -18560,7 +18605,7 @@
         <v>424</v>
       </c>
       <c r="M138" s="39" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="N138" s="38" t="s">
         <v>1</v>
@@ -18607,10 +18652,10 @@
         <v>333</v>
       </c>
       <c r="C139" s="12" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="D139" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E139" s="69" t="s">
         <v>371</v>
@@ -18637,7 +18682,7 @@
         <v>424</v>
       </c>
       <c r="M139" s="39" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="N139" s="38" t="s">
         <v>1</v>
@@ -18684,10 +18729,10 @@
         <v>334</v>
       </c>
       <c r="C140" s="12" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="D140" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E140" s="69" t="s">
         <v>371</v>
@@ -18714,7 +18759,7 @@
         <v>424</v>
       </c>
       <c r="M140" s="39" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="N140" s="38" t="s">
         <v>1</v>
@@ -18761,10 +18806,10 @@
         <v>335</v>
       </c>
       <c r="C141" s="12" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="D141" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E141" s="69" t="s">
         <v>371</v>
@@ -18791,7 +18836,7 @@
         <v>424</v>
       </c>
       <c r="M141" s="39" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="N141" s="38" t="s">
         <v>1</v>
@@ -18838,10 +18883,10 @@
         <v>336</v>
       </c>
       <c r="C142" s="12" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="D142" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E142" s="69" t="s">
         <v>371</v>
@@ -18868,7 +18913,7 @@
         <v>424</v>
       </c>
       <c r="M142" s="39" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="N142" s="38" t="s">
         <v>1</v>
@@ -18915,10 +18960,10 @@
         <v>337</v>
       </c>
       <c r="C143" s="12" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="D143" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E143" s="69" t="s">
         <v>371</v>
@@ -18945,7 +18990,7 @@
         <v>424</v>
       </c>
       <c r="M143" s="39" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="N143" s="38" t="s">
         <v>1</v>
@@ -18992,10 +19037,10 @@
         <v>338</v>
       </c>
       <c r="C144" s="12" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="D144" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E144" s="69" t="s">
         <v>371</v>
@@ -19022,7 +19067,7 @@
         <v>424</v>
       </c>
       <c r="M144" s="39" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="N144" s="38" t="s">
         <v>1</v>
@@ -19069,10 +19114,10 @@
         <v>339</v>
       </c>
       <c r="C145" s="12" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="D145" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E145" s="69" t="s">
         <v>371</v>
@@ -19099,7 +19144,7 @@
         <v>424</v>
       </c>
       <c r="M145" s="39" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="N145" s="38" t="s">
         <v>1</v>
@@ -19146,10 +19191,10 @@
         <v>340</v>
       </c>
       <c r="C146" s="12" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="D146" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E146" s="69" t="s">
         <v>371</v>
@@ -19176,7 +19221,7 @@
         <v>424</v>
       </c>
       <c r="M146" s="39" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="N146" s="38" t="s">
         <v>1</v>
@@ -19223,10 +19268,10 @@
         <v>341</v>
       </c>
       <c r="C147" s="12" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="D147" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E147" s="69" t="s">
         <v>371</v>
@@ -19253,7 +19298,7 @@
         <v>424</v>
       </c>
       <c r="M147" s="39" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="N147" s="38" t="s">
         <v>1</v>
@@ -19300,10 +19345,10 @@
         <v>342</v>
       </c>
       <c r="C148" s="12" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="D148" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E148" s="69" t="s">
         <v>371</v>
@@ -19330,7 +19375,7 @@
         <v>424</v>
       </c>
       <c r="M148" s="39" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="N148" s="38" t="s">
         <v>1</v>
@@ -19377,10 +19422,10 @@
         <v>343</v>
       </c>
       <c r="C149" s="12" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="D149" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E149" s="69" t="s">
         <v>371</v>
@@ -19407,7 +19452,7 @@
         <v>424</v>
       </c>
       <c r="M149" s="39" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="N149" s="38" t="s">
         <v>1</v>
@@ -19454,10 +19499,10 @@
         <v>344</v>
       </c>
       <c r="C150" s="12" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="D150" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E150" s="69" t="s">
         <v>371</v>
@@ -19484,7 +19529,7 @@
         <v>424</v>
       </c>
       <c r="M150" s="39" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="N150" s="38" t="s">
         <v>1</v>
@@ -19531,10 +19576,10 @@
         <v>345</v>
       </c>
       <c r="C151" s="12" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="D151" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E151" s="69" t="s">
         <v>371</v>
@@ -19561,7 +19606,7 @@
         <v>424</v>
       </c>
       <c r="M151" s="39" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="N151" s="38" t="s">
         <v>1</v>
@@ -19608,10 +19653,10 @@
         <v>346</v>
       </c>
       <c r="C152" s="12" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="D152" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E152" s="69" t="s">
         <v>371</v>
@@ -19638,7 +19683,7 @@
         <v>424</v>
       </c>
       <c r="M152" s="39" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="N152" s="38" t="s">
         <v>1</v>
@@ -19685,10 +19730,10 @@
         <v>347</v>
       </c>
       <c r="C153" s="12" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="D153" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E153" s="69" t="s">
         <v>371</v>
@@ -19715,7 +19760,7 @@
         <v>424</v>
       </c>
       <c r="M153" s="39" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="N153" s="38" t="s">
         <v>1</v>
@@ -19762,10 +19807,10 @@
         <v>348</v>
       </c>
       <c r="C154" s="12" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="D154" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E154" s="69" t="s">
         <v>371</v>
@@ -19792,7 +19837,7 @@
         <v>424</v>
       </c>
       <c r="M154" s="39" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="N154" s="38" t="s">
         <v>1</v>
@@ -19839,10 +19884,10 @@
         <v>349</v>
       </c>
       <c r="C155" s="12" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="D155" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E155" s="69" t="s">
         <v>371</v>
@@ -19869,7 +19914,7 @@
         <v>424</v>
       </c>
       <c r="M155" s="39" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="N155" s="38" t="s">
         <v>1</v>
@@ -19916,10 +19961,10 @@
         <v>350</v>
       </c>
       <c r="C156" s="12" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="D156" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E156" s="69" t="s">
         <v>371</v>
@@ -19946,7 +19991,7 @@
         <v>424</v>
       </c>
       <c r="M156" s="39" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="N156" s="38" t="s">
         <v>1</v>
@@ -19993,10 +20038,10 @@
         <v>351</v>
       </c>
       <c r="C157" s="12" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="D157" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E157" s="69" t="s">
         <v>371</v>
@@ -20023,7 +20068,7 @@
         <v>424</v>
       </c>
       <c r="M157" s="39" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="N157" s="38" t="s">
         <v>1</v>
@@ -20070,10 +20115,10 @@
         <v>352</v>
       </c>
       <c r="C158" s="12" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="D158" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E158" s="69" t="s">
         <v>371</v>
@@ -20100,7 +20145,7 @@
         <v>424</v>
       </c>
       <c r="M158" s="39" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="N158" s="38" t="s">
         <v>1</v>
@@ -20147,10 +20192,10 @@
         <v>353</v>
       </c>
       <c r="C159" s="12" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="D159" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E159" s="69" t="s">
         <v>371</v>
@@ -20177,7 +20222,7 @@
         <v>424</v>
       </c>
       <c r="M159" s="39" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="N159" s="38" t="s">
         <v>1</v>
@@ -20224,10 +20269,10 @@
         <v>354</v>
       </c>
       <c r="C160" s="12" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="D160" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E160" s="69" t="s">
         <v>371</v>
@@ -20254,7 +20299,7 @@
         <v>424</v>
       </c>
       <c r="M160" s="39" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="N160" s="38" t="s">
         <v>1</v>
@@ -20301,10 +20346,10 @@
         <v>355</v>
       </c>
       <c r="C161" s="12" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="D161" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E161" s="69" t="s">
         <v>371</v>
@@ -20331,7 +20376,7 @@
         <v>424</v>
       </c>
       <c r="M161" s="39" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="N161" s="38" t="s">
         <v>1</v>
@@ -20378,10 +20423,10 @@
         <v>356</v>
       </c>
       <c r="C162" s="12" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="D162" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E162" s="69" t="s">
         <v>371</v>
@@ -20408,7 +20453,7 @@
         <v>424</v>
       </c>
       <c r="M162" s="39" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="N162" s="38" t="s">
         <v>1</v>
@@ -20455,10 +20500,10 @@
         <v>357</v>
       </c>
       <c r="C163" s="12" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="D163" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E163" s="69" t="s">
         <v>371</v>
@@ -20485,7 +20530,7 @@
         <v>424</v>
       </c>
       <c r="M163" s="39" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="N163" s="38" t="s">
         <v>1</v>
@@ -20532,10 +20577,10 @@
         <v>358</v>
       </c>
       <c r="C164" s="12" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="D164" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E164" s="69" t="s">
         <v>371</v>
@@ -20562,7 +20607,7 @@
         <v>424</v>
       </c>
       <c r="M164" s="39" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="N164" s="38" t="s">
         <v>1</v>
@@ -20609,10 +20654,10 @@
         <v>359</v>
       </c>
       <c r="C165" s="12" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="D165" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E165" s="69" t="s">
         <v>371</v>
@@ -20639,7 +20684,7 @@
         <v>424</v>
       </c>
       <c r="M165" s="39" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="N165" s="38" t="s">
         <v>1</v>
@@ -20686,10 +20731,10 @@
         <v>360</v>
       </c>
       <c r="C166" s="12" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="D166" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E166" s="69" t="s">
         <v>371</v>
@@ -20716,7 +20761,7 @@
         <v>424</v>
       </c>
       <c r="M166" s="39" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="N166" s="38" t="s">
         <v>1</v>
@@ -20763,10 +20808,10 @@
         <v>361</v>
       </c>
       <c r="C167" s="12" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="D167" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E167" s="69" t="s">
         <v>371</v>
@@ -20793,7 +20838,7 @@
         <v>424</v>
       </c>
       <c r="M167" s="39" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="N167" s="38" t="s">
         <v>1</v>
@@ -20840,10 +20885,10 @@
         <v>362</v>
       </c>
       <c r="C168" s="12" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="D168" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E168" s="69" t="s">
         <v>371</v>
@@ -20870,7 +20915,7 @@
         <v>424</v>
       </c>
       <c r="M168" s="39" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="N168" s="38" t="s">
         <v>1</v>
@@ -20917,10 +20962,10 @@
         <v>363</v>
       </c>
       <c r="C169" s="12" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="D169" s="68" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="E169" s="69" t="s">
         <v>371</v>
@@ -20947,7 +20992,7 @@
         <v>424</v>
       </c>
       <c r="M169" s="39" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="N169" s="42" t="s">
         <v>1</v>
@@ -20989,65 +21034,65 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="12" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1">
-    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="cellIs" dxfId="10" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="13" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1">
-    <cfRule type="cellIs" dxfId="9" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1">
-    <cfRule type="cellIs" dxfId="8" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1">
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="cellIs" dxfId="6" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="17" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P1">
-    <cfRule type="cellIs" dxfId="5" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="9" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="cellIs" dxfId="4" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1">
-    <cfRule type="cellIs" dxfId="3" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1:Y1048576">
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V1">
-    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1">
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_15965_1F.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_1F.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr codeName="EstaPastaDeTrabalho"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B1663FC-853F-48EE-A03A-0A1BF6E4E2D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -2360,63 +2360,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{9B49B867-F029-4368-B154-870C7BE57F68}"/>
   </cellStyles>
-  <dxfs count="85">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="79">
     <dxf>
       <font>
         <b val="0"/>
@@ -4605,33 +4549,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:Y169" headerRowCount="0" totalsRowShown="0" headerRowDxfId="84" headerRowBorderDxfId="83" tableBorderDxfId="82" totalsRowBorderDxfId="81">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:Y169" headerRowCount="0" totalsRowShown="0" headerRowDxfId="78" headerRowBorderDxfId="77" tableBorderDxfId="76" totalsRowBorderDxfId="75">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="80" dataDxfId="79"/>
-    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="78" dataDxfId="77"/>
-    <tableColumn id="26" xr3:uid="{C91353D4-2D80-49C8-8738-A06C8033990C}" name="Coluna21" headerRowDxfId="76" dataDxfId="75"/>
-    <tableColumn id="5" xr3:uid="{AAB64158-D6DA-4E9F-AC47-A0274997AD5C}" name="Coluna8" headerRowDxfId="74" dataDxfId="73"/>
-    <tableColumn id="4" xr3:uid="{9F1772E8-67AD-410D-A17F-F21B8080770D}" name="Coluna7" headerRowDxfId="72" dataDxfId="71"/>
-    <tableColumn id="9" xr3:uid="{9B194C8C-85D6-4BE2-B1AE-E11E335186F0}" name="Coluna6" headerRowDxfId="70" dataDxfId="69"/>
-    <tableColumn id="8" xr3:uid="{6F1A2D13-ED4B-47DE-AFA9-D11431CAA734}" name="Coluna5" headerRowDxfId="68" dataDxfId="67"/>
-    <tableColumn id="15" xr3:uid="{0C0DAD0A-A76E-4555-A1F1-F78A8F1BE2C2}" name="Coluna4" headerRowDxfId="66" dataDxfId="65"/>
-    <tableColumn id="14" xr3:uid="{C073F03F-8B8F-474F-AF29-E26DD9C1B19A}" name="Coluna3" headerRowDxfId="64" dataDxfId="63"/>
-    <tableColumn id="11" xr3:uid="{AE04A63A-3540-4CF3-9D9A-59CD3577B22C}" name="Coluna2" headerRowDxfId="62" dataDxfId="61"/>
-    <tableColumn id="10" xr3:uid="{F50D06F5-DC15-417E-BE0C-A36478AC8A38}" name="Coluna1" headerRowDxfId="60" dataDxfId="59"/>
-    <tableColumn id="25" xr3:uid="{FF2B42B8-007D-4B78-A1E6-70321A25B422}" name="Coluna20" headerRowDxfId="58" dataDxfId="57"/>
-    <tableColumn id="24" xr3:uid="{B0850B61-1B8F-418B-98C0-04AB09902DE3}" name="Coluna19" headerRowDxfId="56" dataDxfId="55"/>
-    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="54" dataDxfId="53"/>
-    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="52" dataDxfId="51"/>
-    <tableColumn id="6" xr3:uid="{8E7C1DDF-1846-4221-9B0E-C7E4CC7EA057}" name="Coluna9" headerRowDxfId="50" dataDxfId="49"/>
-    <tableColumn id="7" xr3:uid="{3D7A485C-E68B-4D3B-888E-DCFC8EAEE60D}" name="Coluna10" headerRowDxfId="48" dataDxfId="47"/>
-    <tableColumn id="16" xr3:uid="{FECF52FB-CC27-4CA6-B622-AF9F7DB3B554}" name="Coluna11" headerRowDxfId="46" dataDxfId="45"/>
-    <tableColumn id="17" xr3:uid="{D79F8B63-2EF5-45DD-9134-450A005B41F4}" name="Coluna12" headerRowDxfId="44" dataDxfId="43"/>
-    <tableColumn id="18" xr3:uid="{DAFF39A1-0FA6-4AF0-A3B6-380882A29861}" name="Coluna13" headerRowDxfId="42" dataDxfId="41"/>
-    <tableColumn id="19" xr3:uid="{87AE1228-C62F-45E2-A7B1-A0914F89FBE3}" name="Coluna14" headerRowDxfId="40" dataDxfId="39"/>
-    <tableColumn id="20" xr3:uid="{85EAA474-6B84-4EF5-95FF-852AF2C5EA5E}" name="Coluna15" headerRowDxfId="38" dataDxfId="37"/>
-    <tableColumn id="21" xr3:uid="{5B15C019-4680-4877-A95B-F683BA0C59DD}" name="Coluna16" headerRowDxfId="36" dataDxfId="35"/>
-    <tableColumn id="22" xr3:uid="{5C11667F-4365-4FD8-A625-69FCEAC4D24C}" name="Coluna17" headerRowDxfId="34" dataDxfId="33"/>
-    <tableColumn id="23" xr3:uid="{38F8B48D-5280-437C-BB95-24A464DAF74A}" name="Coluna18" headerRowDxfId="32" dataDxfId="31"/>
+    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="74" dataDxfId="73"/>
+    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="72" dataDxfId="71"/>
+    <tableColumn id="26" xr3:uid="{C91353D4-2D80-49C8-8738-A06C8033990C}" name="Coluna21" headerRowDxfId="70" dataDxfId="69"/>
+    <tableColumn id="5" xr3:uid="{AAB64158-D6DA-4E9F-AC47-A0274997AD5C}" name="Coluna8" headerRowDxfId="68" dataDxfId="67"/>
+    <tableColumn id="4" xr3:uid="{9F1772E8-67AD-410D-A17F-F21B8080770D}" name="Coluna7" headerRowDxfId="66" dataDxfId="65"/>
+    <tableColumn id="9" xr3:uid="{9B194C8C-85D6-4BE2-B1AE-E11E335186F0}" name="Coluna6" headerRowDxfId="64" dataDxfId="63"/>
+    <tableColumn id="8" xr3:uid="{6F1A2D13-ED4B-47DE-AFA9-D11431CAA734}" name="Coluna5" headerRowDxfId="62" dataDxfId="61"/>
+    <tableColumn id="15" xr3:uid="{0C0DAD0A-A76E-4555-A1F1-F78A8F1BE2C2}" name="Coluna4" headerRowDxfId="60" dataDxfId="59"/>
+    <tableColumn id="14" xr3:uid="{C073F03F-8B8F-474F-AF29-E26DD9C1B19A}" name="Coluna3" headerRowDxfId="58" dataDxfId="57"/>
+    <tableColumn id="11" xr3:uid="{AE04A63A-3540-4CF3-9D9A-59CD3577B22C}" name="Coluna2" headerRowDxfId="56" dataDxfId="55"/>
+    <tableColumn id="10" xr3:uid="{F50D06F5-DC15-417E-BE0C-A36478AC8A38}" name="Coluna1" headerRowDxfId="54" dataDxfId="53"/>
+    <tableColumn id="25" xr3:uid="{FF2B42B8-007D-4B78-A1E6-70321A25B422}" name="Coluna20" headerRowDxfId="52" dataDxfId="51"/>
+    <tableColumn id="24" xr3:uid="{B0850B61-1B8F-418B-98C0-04AB09902DE3}" name="Coluna19" headerRowDxfId="50" dataDxfId="49"/>
+    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="48" dataDxfId="47"/>
+    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="46" dataDxfId="45"/>
+    <tableColumn id="6" xr3:uid="{8E7C1DDF-1846-4221-9B0E-C7E4CC7EA057}" name="Coluna9" headerRowDxfId="44" dataDxfId="43"/>
+    <tableColumn id="7" xr3:uid="{3D7A485C-E68B-4D3B-888E-DCFC8EAEE60D}" name="Coluna10" headerRowDxfId="42" dataDxfId="41"/>
+    <tableColumn id="16" xr3:uid="{FECF52FB-CC27-4CA6-B622-AF9F7DB3B554}" name="Coluna11" headerRowDxfId="40" dataDxfId="39"/>
+    <tableColumn id="17" xr3:uid="{D79F8B63-2EF5-45DD-9134-450A005B41F4}" name="Coluna12" headerRowDxfId="38" dataDxfId="37"/>
+    <tableColumn id="18" xr3:uid="{DAFF39A1-0FA6-4AF0-A3B6-380882A29861}" name="Coluna13" headerRowDxfId="36" dataDxfId="35"/>
+    <tableColumn id="19" xr3:uid="{87AE1228-C62F-45E2-A7B1-A0914F89FBE3}" name="Coluna14" headerRowDxfId="34" dataDxfId="33"/>
+    <tableColumn id="20" xr3:uid="{85EAA474-6B84-4EF5-95FF-852AF2C5EA5E}" name="Coluna15" headerRowDxfId="32" dataDxfId="31"/>
+    <tableColumn id="21" xr3:uid="{5B15C019-4680-4877-A95B-F683BA0C59DD}" name="Coluna16" headerRowDxfId="30" dataDxfId="29"/>
+    <tableColumn id="22" xr3:uid="{5C11667F-4365-4FD8-A625-69FCEAC4D24C}" name="Coluna17" headerRowDxfId="28" dataDxfId="27"/>
+    <tableColumn id="23" xr3:uid="{38F8B48D-5280-437C-BB95-24A464DAF74A}" name="Coluna18" headerRowDxfId="26" dataDxfId="25"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -5158,7 +5102,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46167.411050810188</v>
+        <v>46214.34683865741</v>
       </c>
       <c r="C18" s="48" t="s">
         <v>434</v>
@@ -7756,35 +7700,25 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A7:A27">
-    <cfRule type="cellIs" dxfId="30" priority="9" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F20">
-    <cfRule type="duplicateValues" dxfId="25" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA1 AA7:AA27">
-    <cfRule type="cellIs" dxfId="21" priority="7" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A6">
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
+  <conditionalFormatting sqref="A2:A27">
+    <cfRule type="cellIs" dxfId="24" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA6">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+  <conditionalFormatting sqref="F20">
+    <cfRule type="duplicateValues" dxfId="19" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA1:AA27">
+    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7934,7 +7868,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7979,7 +7913,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21034,65 +20968,65 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="18" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1">
-    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="cellIs" dxfId="16" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="13" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1">
-    <cfRule type="cellIs" dxfId="15" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1">
-    <cfRule type="cellIs" dxfId="14" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1">
-    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="cellIs" dxfId="12" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="17" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P1">
-    <cfRule type="cellIs" dxfId="11" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="9" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="cellIs" dxfId="10" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1">
-    <cfRule type="cellIs" dxfId="9" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1:Y1048576">
-    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V1">
-    <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1">
-    <cfRule type="cellIs" dxfId="6" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_15965_1F.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_1F.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1EA0A39-C573-44B5-8450-9DFAC704FF23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E14563-A740-406A-B71B-2DA75BA5E350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4649" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4649" uniqueCount="561">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -1759,9 +1759,6 @@
   </si>
   <si>
     <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1.</t>
-  </si>
-  <si>
-    <t>Arquitetura</t>
   </si>
   <si>
     <t>[ 5I ]</t>
@@ -2327,63 +2324,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{9B49B867-F029-4368-B154-870C7BE57F68}"/>
   </cellStyles>
-  <dxfs count="85">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="79">
     <dxf>
       <font>
         <b val="0"/>
@@ -4572,33 +4513,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:Y169" headerRowCount="0" totalsRowShown="0" headerRowDxfId="84" headerRowBorderDxfId="83" tableBorderDxfId="82" totalsRowBorderDxfId="81">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:Y169" headerRowCount="0" totalsRowShown="0" headerRowDxfId="78" headerRowBorderDxfId="77" tableBorderDxfId="76" totalsRowBorderDxfId="75">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="80" dataDxfId="79"/>
-    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="78" dataDxfId="77"/>
-    <tableColumn id="26" xr3:uid="{C91353D4-2D80-49C8-8738-A06C8033990C}" name="Coluna21" headerRowDxfId="76" dataDxfId="75"/>
-    <tableColumn id="5" xr3:uid="{AAB64158-D6DA-4E9F-AC47-A0274997AD5C}" name="Coluna8" headerRowDxfId="74" dataDxfId="73"/>
-    <tableColumn id="4" xr3:uid="{9F1772E8-67AD-410D-A17F-F21B8080770D}" name="Coluna7" headerRowDxfId="72" dataDxfId="71"/>
-    <tableColumn id="9" xr3:uid="{9B194C8C-85D6-4BE2-B1AE-E11E335186F0}" name="Coluna6" headerRowDxfId="70" dataDxfId="69"/>
-    <tableColumn id="8" xr3:uid="{6F1A2D13-ED4B-47DE-AFA9-D11431CAA734}" name="Coluna5" headerRowDxfId="68" dataDxfId="67"/>
-    <tableColumn id="15" xr3:uid="{0C0DAD0A-A76E-4555-A1F1-F78A8F1BE2C2}" name="Coluna4" headerRowDxfId="66" dataDxfId="65"/>
-    <tableColumn id="14" xr3:uid="{C073F03F-8B8F-474F-AF29-E26DD9C1B19A}" name="Coluna3" headerRowDxfId="64" dataDxfId="63"/>
-    <tableColumn id="11" xr3:uid="{AE04A63A-3540-4CF3-9D9A-59CD3577B22C}" name="Coluna2" headerRowDxfId="62" dataDxfId="61"/>
-    <tableColumn id="10" xr3:uid="{F50D06F5-DC15-417E-BE0C-A36478AC8A38}" name="Coluna1" headerRowDxfId="60" dataDxfId="59"/>
-    <tableColumn id="25" xr3:uid="{FF2B42B8-007D-4B78-A1E6-70321A25B422}" name="Coluna20" headerRowDxfId="58" dataDxfId="57"/>
-    <tableColumn id="24" xr3:uid="{B0850B61-1B8F-418B-98C0-04AB09902DE3}" name="Coluna19" headerRowDxfId="56" dataDxfId="55"/>
-    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="54" dataDxfId="53"/>
-    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="52" dataDxfId="51"/>
-    <tableColumn id="6" xr3:uid="{8E7C1DDF-1846-4221-9B0E-C7E4CC7EA057}" name="Coluna9" headerRowDxfId="50" dataDxfId="49"/>
-    <tableColumn id="7" xr3:uid="{3D7A485C-E68B-4D3B-888E-DCFC8EAEE60D}" name="Coluna10" headerRowDxfId="48" dataDxfId="47"/>
-    <tableColumn id="16" xr3:uid="{FECF52FB-CC27-4CA6-B622-AF9F7DB3B554}" name="Coluna11" headerRowDxfId="46" dataDxfId="45"/>
-    <tableColumn id="17" xr3:uid="{D79F8B63-2EF5-45DD-9134-450A005B41F4}" name="Coluna12" headerRowDxfId="44" dataDxfId="43"/>
-    <tableColumn id="18" xr3:uid="{DAFF39A1-0FA6-4AF0-A3B6-380882A29861}" name="Coluna13" headerRowDxfId="42" dataDxfId="41"/>
-    <tableColumn id="19" xr3:uid="{87AE1228-C62F-45E2-A7B1-A0914F89FBE3}" name="Coluna14" headerRowDxfId="40" dataDxfId="39"/>
-    <tableColumn id="20" xr3:uid="{85EAA474-6B84-4EF5-95FF-852AF2C5EA5E}" name="Coluna15" headerRowDxfId="38" dataDxfId="37"/>
-    <tableColumn id="21" xr3:uid="{5B15C019-4680-4877-A95B-F683BA0C59DD}" name="Coluna16" headerRowDxfId="36" dataDxfId="35"/>
-    <tableColumn id="22" xr3:uid="{5C11667F-4365-4FD8-A625-69FCEAC4D24C}" name="Coluna17" headerRowDxfId="34" dataDxfId="33"/>
-    <tableColumn id="23" xr3:uid="{38F8B48D-5280-437C-BB95-24A464DAF74A}" name="Coluna18" headerRowDxfId="32" dataDxfId="31"/>
+    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="74" dataDxfId="73"/>
+    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="72" dataDxfId="71"/>
+    <tableColumn id="26" xr3:uid="{C91353D4-2D80-49C8-8738-A06C8033990C}" name="Coluna21" headerRowDxfId="70" dataDxfId="69"/>
+    <tableColumn id="5" xr3:uid="{AAB64158-D6DA-4E9F-AC47-A0274997AD5C}" name="Coluna8" headerRowDxfId="68" dataDxfId="67"/>
+    <tableColumn id="4" xr3:uid="{9F1772E8-67AD-410D-A17F-F21B8080770D}" name="Coluna7" headerRowDxfId="66" dataDxfId="65"/>
+    <tableColumn id="9" xr3:uid="{9B194C8C-85D6-4BE2-B1AE-E11E335186F0}" name="Coluna6" headerRowDxfId="64" dataDxfId="63"/>
+    <tableColumn id="8" xr3:uid="{6F1A2D13-ED4B-47DE-AFA9-D11431CAA734}" name="Coluna5" headerRowDxfId="62" dataDxfId="61"/>
+    <tableColumn id="15" xr3:uid="{0C0DAD0A-A76E-4555-A1F1-F78A8F1BE2C2}" name="Coluna4" headerRowDxfId="60" dataDxfId="59"/>
+    <tableColumn id="14" xr3:uid="{C073F03F-8B8F-474F-AF29-E26DD9C1B19A}" name="Coluna3" headerRowDxfId="58" dataDxfId="57"/>
+    <tableColumn id="11" xr3:uid="{AE04A63A-3540-4CF3-9D9A-59CD3577B22C}" name="Coluna2" headerRowDxfId="56" dataDxfId="55"/>
+    <tableColumn id="10" xr3:uid="{F50D06F5-DC15-417E-BE0C-A36478AC8A38}" name="Coluna1" headerRowDxfId="54" dataDxfId="53"/>
+    <tableColumn id="25" xr3:uid="{FF2B42B8-007D-4B78-A1E6-70321A25B422}" name="Coluna20" headerRowDxfId="52" dataDxfId="51"/>
+    <tableColumn id="24" xr3:uid="{B0850B61-1B8F-418B-98C0-04AB09902DE3}" name="Coluna19" headerRowDxfId="50" dataDxfId="49"/>
+    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="48" dataDxfId="47"/>
+    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="46" dataDxfId="45"/>
+    <tableColumn id="6" xr3:uid="{8E7C1DDF-1846-4221-9B0E-C7E4CC7EA057}" name="Coluna9" headerRowDxfId="44" dataDxfId="43"/>
+    <tableColumn id="7" xr3:uid="{3D7A485C-E68B-4D3B-888E-DCFC8EAEE60D}" name="Coluna10" headerRowDxfId="42" dataDxfId="41"/>
+    <tableColumn id="16" xr3:uid="{FECF52FB-CC27-4CA6-B622-AF9F7DB3B554}" name="Coluna11" headerRowDxfId="40" dataDxfId="39"/>
+    <tableColumn id="17" xr3:uid="{D79F8B63-2EF5-45DD-9134-450A005B41F4}" name="Coluna12" headerRowDxfId="38" dataDxfId="37"/>
+    <tableColumn id="18" xr3:uid="{DAFF39A1-0FA6-4AF0-A3B6-380882A29861}" name="Coluna13" headerRowDxfId="36" dataDxfId="35"/>
+    <tableColumn id="19" xr3:uid="{87AE1228-C62F-45E2-A7B1-A0914F89FBE3}" name="Coluna14" headerRowDxfId="34" dataDxfId="33"/>
+    <tableColumn id="20" xr3:uid="{85EAA474-6B84-4EF5-95FF-852AF2C5EA5E}" name="Coluna15" headerRowDxfId="32" dataDxfId="31"/>
+    <tableColumn id="21" xr3:uid="{5B15C019-4680-4877-A95B-F683BA0C59DD}" name="Coluna16" headerRowDxfId="30" dataDxfId="29"/>
+    <tableColumn id="22" xr3:uid="{5C11667F-4365-4FD8-A625-69FCEAC4D24C}" name="Coluna17" headerRowDxfId="28" dataDxfId="27"/>
+    <tableColumn id="23" xr3:uid="{38F8B48D-5280-437C-BB95-24A464DAF74A}" name="Coluna18" headerRowDxfId="26" dataDxfId="25"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -5125,7 +5066,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46216.267276157407</v>
+        <v>46219.566889351852</v>
       </c>
       <c r="C18" s="46" t="s">
         <v>433</v>
@@ -5230,7 +5171,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F75533AB-3BC5-4EED-85BC-780B8F4A6EA8}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA27"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.83203125" style="33" customWidth="1"/>
@@ -5339,7 +5280,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="2" spans="1:27" s="33" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" s="33" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="57">
         <v>2</v>
       </c>
@@ -5411,7 +5352,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V2" s="42" t="s">
-        <v>556</v>
+        <v>449</v>
       </c>
       <c r="W2" s="66" t="str">
         <f>CONCATENATE("Key-ABNT-",A2)</f>
@@ -5424,14 +5365,14 @@
         <v>191</v>
       </c>
       <c r="Z2" s="42" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="AA2" s="42" t="str">
         <f t="shared" ref="AA2:AA6" si="3">_xlfn.TRANSLATE(P2,"pt","en")</f>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" s="33" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" s="33" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="57">
         <v>3</v>
       </c>
@@ -5482,7 +5423,7 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="42" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="Q3" s="42" t="s">
         <v>555</v>
@@ -5503,7 +5444,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V3" s="42" t="s">
-        <v>556</v>
+        <v>449</v>
       </c>
       <c r="W3" s="66" t="str">
         <f t="shared" ref="W3:W27" si="4">CONCATENATE("Key-ABNT-",A3)</f>
@@ -5523,7 +5464,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" s="33" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" s="33" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="57">
         <v>4</v>
       </c>
@@ -5574,7 +5515,7 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="42" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="Q4" s="42" t="s">
         <v>555</v>
@@ -5595,7 +5536,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V4" s="42" t="s">
-        <v>556</v>
+        <v>449</v>
       </c>
       <c r="W4" s="66" t="str">
         <f t="shared" si="4"/>
@@ -5615,7 +5556,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" s="33" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" s="33" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="57">
         <v>5</v>
       </c>
@@ -5666,7 +5607,7 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="42" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="Q5" s="42" t="s">
         <v>555</v>
@@ -5687,7 +5628,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V5" s="42" t="s">
-        <v>556</v>
+        <v>449</v>
       </c>
       <c r="W5" s="66" t="str">
         <f t="shared" si="4"/>
@@ -5707,7 +5648,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" s="33" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" s="33" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="57">
         <v>6</v>
       </c>
@@ -5758,7 +5699,7 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="42" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="Q6" s="42" t="s">
         <v>555</v>
@@ -5779,7 +5720,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V6" s="42" t="s">
-        <v>556</v>
+        <v>449</v>
       </c>
       <c r="W6" s="66" t="str">
         <f t="shared" si="4"/>
@@ -5799,7 +5740,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="57">
         <v>7</v>
       </c>
@@ -5890,7 +5831,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="57">
         <v>8</v>
       </c>
@@ -5981,7 +5922,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="57">
         <v>9</v>
       </c>
@@ -6072,7 +6013,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="57">
         <v>10</v>
       </c>
@@ -6163,7 +6104,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="57">
         <v>11</v>
       </c>
@@ -6254,7 +6195,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="57">
         <v>12</v>
       </c>
@@ -6345,7 +6286,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="57">
         <v>13</v>
       </c>
@@ -6436,7 +6377,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="57">
         <v>14</v>
       </c>
@@ -6527,7 +6468,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="57">
         <v>15</v>
       </c>
@@ -6618,7 +6559,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="57">
         <v>16</v>
       </c>
@@ -6709,7 +6650,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="57">
         <v>17</v>
       </c>
@@ -6800,7 +6741,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="57">
         <v>18</v>
       </c>
@@ -6891,7 +6832,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="57">
         <v>19</v>
       </c>
@@ -6982,7 +6923,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="57">
         <v>20</v>
       </c>
@@ -7075,7 +7016,7 @@
         <v>Programming Phase</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="57">
         <v>21</v>
       </c>
@@ -7168,7 +7109,7 @@
         <v>Preliminary Studies Phase</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="57">
         <v>22</v>
       </c>
@@ -7261,7 +7202,7 @@
         <v>Project Phase</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="57">
         <v>23</v>
       </c>
@@ -7354,7 +7295,7 @@
         <v>Bidding Phase</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="57">
         <v>24</v>
       </c>
@@ -7447,7 +7388,7 @@
         <v>Construction Phase</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="57">
         <v>25</v>
       </c>
@@ -7540,7 +7481,7 @@
         <v>Commissioning Phase</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="57">
         <v>26</v>
       </c>
@@ -7633,7 +7574,7 @@
         <v>Operation Phase</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="57">
         <v>27</v>
       </c>
@@ -7727,35 +7668,25 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A7:A27">
-    <cfRule type="cellIs" dxfId="30" priority="9" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F20">
-    <cfRule type="duplicateValues" dxfId="25" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA1 AA7:AA27">
-    <cfRule type="cellIs" dxfId="21" priority="7" operator="equal">
+  <conditionalFormatting sqref="A2:B27">
+    <cfRule type="cellIs" dxfId="24" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F6">
-    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:B6 B7:B27">
-    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
+  <conditionalFormatting sqref="F20">
+    <cfRule type="duplicateValues" dxfId="19" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA6">
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
+  <conditionalFormatting sqref="AA1:AA27">
+    <cfRule type="cellIs" dxfId="15" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7905,7 +7836,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7950,7 +7881,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21005,65 +20936,65 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="18" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1">
-    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="cellIs" dxfId="16" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="13" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1">
-    <cfRule type="cellIs" dxfId="15" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1">
-    <cfRule type="cellIs" dxfId="14" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1">
-    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="cellIs" dxfId="12" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="17" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P1">
-    <cfRule type="cellIs" dxfId="11" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="9" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="cellIs" dxfId="10" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1">
-    <cfRule type="cellIs" dxfId="9" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1:Y1048576">
-    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V1">
-    <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1">
-    <cfRule type="cellIs" dxfId="6" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_15965_1F.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_1F.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5197899A-31BC-4E05-AEEC-10E109E813B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F2E5284-33BA-4DD6-AEAF-39FB5287077D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4649" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4649" uniqueCount="567">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -1452,141 +1452,42 @@
     <t>Requisito.Sistemas</t>
   </si>
   <si>
-    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 0M.</t>
-  </si>
-  <si>
-    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 0M.</t>
-  </si>
-  <si>
     <t>0M</t>
   </si>
   <si>
-    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 0M.</t>
-  </si>
-  <si>
-    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 0P.</t>
-  </si>
-  <si>
-    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 0P.</t>
-  </si>
-  <si>
     <t>0P</t>
   </si>
   <si>
-    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 0P.</t>
-  </si>
-  <si>
-    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 1D.</t>
-  </si>
-  <si>
-    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 1D.</t>
-  </si>
-  <si>
     <t>1D</t>
   </si>
   <si>
-    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 1D.</t>
-  </si>
-  <si>
-    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 1F.</t>
-  </si>
-  <si>
-    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 1F.</t>
-  </si>
-  <si>
-    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 1F.</t>
-  </si>
-  <si>
-    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 1S.</t>
-  </si>
-  <si>
-    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 1S.</t>
-  </si>
-  <si>
     <t>1S</t>
   </si>
   <si>
-    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 1S.</t>
-  </si>
-  <si>
-    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 2C.</t>
-  </si>
-  <si>
-    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 2C.</t>
-  </si>
-  <si>
     <t>2C</t>
   </si>
   <si>
-    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 2C.</t>
-  </si>
-  <si>
     <t>2N</t>
   </si>
   <si>
     <t>2Q</t>
   </si>
   <si>
-    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 3E.</t>
-  </si>
-  <si>
-    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 3E.</t>
-  </si>
-  <si>
     <t>3E</t>
   </si>
   <si>
-    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 3E.</t>
-  </si>
-  <si>
-    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 3R.</t>
-  </si>
-  <si>
-    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 3R.</t>
-  </si>
-  <si>
     <t>3R</t>
   </si>
   <si>
-    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 3R.</t>
-  </si>
-  <si>
-    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 4A.</t>
-  </si>
-  <si>
-    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 4A.</t>
-  </si>
-  <si>
     <t>4A</t>
   </si>
   <si>
-    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 4A.</t>
-  </si>
-  <si>
-    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 4U.</t>
-  </si>
-  <si>
-    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 4U.</t>
-  </si>
-  <si>
     <t>4U</t>
   </si>
   <si>
-    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 4U.</t>
-  </si>
-  <si>
-    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 5I.</t>
-  </si>
-  <si>
-    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 5I.</t>
-  </si>
-  <si>
     <t>5I</t>
   </si>
   <si>
-    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 5I.</t>
-  </si>
-  <si>
     <t>"Operação"</t>
   </si>
   <si>
@@ -1771,6 +1672,126 @@
   </si>
   <si>
     <t>NBR.Temática</t>
+  </si>
+  <si>
+    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 0M. Códigos de Materiais.</t>
+  </si>
+  <si>
+    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 0M. Códigos de materiales.</t>
+  </si>
+  <si>
+    <t>Interdiciplinar</t>
+  </si>
+  <si>
+    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 0M. Material Codes.</t>
+  </si>
+  <si>
+    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 0P. Códigos de Propriedades.</t>
+  </si>
+  <si>
+    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 0P. Códigos de propiedad.</t>
+  </si>
+  <si>
+    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 0P. Property Codes.</t>
+  </si>
+  <si>
+    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 1D. Códigos de Disciplinas.</t>
+  </si>
+  <si>
+    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 1D. Códigos disciplinarios.</t>
+  </si>
+  <si>
+    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 1D. Discipline Codes.</t>
+  </si>
+  <si>
+    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 1F. Códigos de Fases.</t>
+  </si>
+  <si>
+    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 1F. Códigos de fase.</t>
+  </si>
+  <si>
+    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 1F. Phase Codes.</t>
+  </si>
+  <si>
+    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 1S. Códigos de Serviços.</t>
+  </si>
+  <si>
+    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 1S. Códigos de servicio.</t>
+  </si>
+  <si>
+    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 1S. Service Codes.</t>
+  </si>
+  <si>
+    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 2C. Códigos de Produtos construtivos.</t>
+  </si>
+  <si>
+    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 2C. Códigos de Productos Constructivos.</t>
+  </si>
+  <si>
+    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 2C. Codes of Constructive Products.</t>
+  </si>
+  <si>
+    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 2N. Códigos de Recursos Humanos.</t>
+  </si>
+  <si>
+    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 2N. Códigos de Recursos Humanos.</t>
+  </si>
+  <si>
+    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 2N. Human Resources Codes.</t>
+  </si>
+  <si>
+    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 2Q. Códigos de Equipamentos.</t>
+  </si>
+  <si>
+    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 2Q. Códigos de equipo.</t>
+  </si>
+  <si>
+    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 2Q. Equipment Codes.</t>
+  </si>
+  <si>
+    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 3E. Códigos de Elementos da construção.</t>
+  </si>
+  <si>
+    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 3E. Códigos de elementos de edificio.</t>
+  </si>
+  <si>
+    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 3E. Building Element Codes.</t>
+  </si>
+  <si>
+    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 3R. Códigos de Recursos da construção.</t>
+  </si>
+  <si>
+    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 3R. Códigos de recursos de construcción.</t>
+  </si>
+  <si>
+    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 3R. Building Resource Codes.</t>
+  </si>
+  <si>
+    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 4A. Códigos de Ambientes.</t>
+  </si>
+  <si>
+    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 4A. Códigos de medio ambiente.</t>
+  </si>
+  <si>
+    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 4A. Environment Codes.</t>
+  </si>
+  <si>
+    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 4U. Códigos de Unidades funcionais.</t>
+  </si>
+  <si>
+    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 4U. Códigos de unidad funcional.</t>
+  </si>
+  <si>
+    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 4U. Functional Unit Codes.</t>
+  </si>
+  <si>
+    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 5I. Códigos de Informação da construção.</t>
+  </si>
+  <si>
+    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 5I. Códigos de información de edificación.</t>
+  </si>
+  <si>
+    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 5I. Building Information Codes.</t>
   </si>
 </sst>
 </file>
@@ -2321,7 +2342,59 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{9B49B867-F029-4368-B154-870C7BE57F68}"/>
   </cellStyles>
-  <dxfs count="79">
+  <dxfs count="85">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -4510,33 +4583,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:Y169" headerRowCount="0" totalsRowShown="0" headerRowDxfId="78" headerRowBorderDxfId="77" tableBorderDxfId="76" totalsRowBorderDxfId="75">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:Y169" headerRowCount="0" totalsRowShown="0" headerRowDxfId="84" headerRowBorderDxfId="83" tableBorderDxfId="82" totalsRowBorderDxfId="81">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="74" dataDxfId="73"/>
-    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="72" dataDxfId="71"/>
-    <tableColumn id="26" xr3:uid="{C91353D4-2D80-49C8-8738-A06C8033990C}" name="Coluna21" headerRowDxfId="70" dataDxfId="69"/>
-    <tableColumn id="5" xr3:uid="{AAB64158-D6DA-4E9F-AC47-A0274997AD5C}" name="Coluna8" headerRowDxfId="68" dataDxfId="67"/>
-    <tableColumn id="4" xr3:uid="{9F1772E8-67AD-410D-A17F-F21B8080770D}" name="Coluna7" headerRowDxfId="66" dataDxfId="65"/>
-    <tableColumn id="9" xr3:uid="{9B194C8C-85D6-4BE2-B1AE-E11E335186F0}" name="Coluna6" headerRowDxfId="64" dataDxfId="63"/>
-    <tableColumn id="8" xr3:uid="{6F1A2D13-ED4B-47DE-AFA9-D11431CAA734}" name="Coluna5" headerRowDxfId="62" dataDxfId="61"/>
-    <tableColumn id="15" xr3:uid="{0C0DAD0A-A76E-4555-A1F1-F78A8F1BE2C2}" name="Coluna4" headerRowDxfId="60" dataDxfId="59"/>
-    <tableColumn id="14" xr3:uid="{C073F03F-8B8F-474F-AF29-E26DD9C1B19A}" name="Coluna3" headerRowDxfId="58" dataDxfId="57"/>
-    <tableColumn id="11" xr3:uid="{AE04A63A-3540-4CF3-9D9A-59CD3577B22C}" name="Coluna2" headerRowDxfId="56" dataDxfId="55"/>
-    <tableColumn id="10" xr3:uid="{F50D06F5-DC15-417E-BE0C-A36478AC8A38}" name="Coluna1" headerRowDxfId="54" dataDxfId="53"/>
-    <tableColumn id="25" xr3:uid="{FF2B42B8-007D-4B78-A1E6-70321A25B422}" name="Coluna20" headerRowDxfId="52" dataDxfId="51"/>
-    <tableColumn id="24" xr3:uid="{B0850B61-1B8F-418B-98C0-04AB09902DE3}" name="Coluna19" headerRowDxfId="50" dataDxfId="49"/>
-    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="48" dataDxfId="47"/>
-    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="46" dataDxfId="45"/>
-    <tableColumn id="6" xr3:uid="{8E7C1DDF-1846-4221-9B0E-C7E4CC7EA057}" name="Coluna9" headerRowDxfId="44" dataDxfId="43"/>
-    <tableColumn id="7" xr3:uid="{3D7A485C-E68B-4D3B-888E-DCFC8EAEE60D}" name="Coluna10" headerRowDxfId="42" dataDxfId="41"/>
-    <tableColumn id="16" xr3:uid="{FECF52FB-CC27-4CA6-B622-AF9F7DB3B554}" name="Coluna11" headerRowDxfId="40" dataDxfId="39"/>
-    <tableColumn id="17" xr3:uid="{D79F8B63-2EF5-45DD-9134-450A005B41F4}" name="Coluna12" headerRowDxfId="38" dataDxfId="37"/>
-    <tableColumn id="18" xr3:uid="{DAFF39A1-0FA6-4AF0-A3B6-380882A29861}" name="Coluna13" headerRowDxfId="36" dataDxfId="35"/>
-    <tableColumn id="19" xr3:uid="{87AE1228-C62F-45E2-A7B1-A0914F89FBE3}" name="Coluna14" headerRowDxfId="34" dataDxfId="33"/>
-    <tableColumn id="20" xr3:uid="{85EAA474-6B84-4EF5-95FF-852AF2C5EA5E}" name="Coluna15" headerRowDxfId="32" dataDxfId="31"/>
-    <tableColumn id="21" xr3:uid="{5B15C019-4680-4877-A95B-F683BA0C59DD}" name="Coluna16" headerRowDxfId="30" dataDxfId="29"/>
-    <tableColumn id="22" xr3:uid="{5C11667F-4365-4FD8-A625-69FCEAC4D24C}" name="Coluna17" headerRowDxfId="28" dataDxfId="27"/>
-    <tableColumn id="23" xr3:uid="{38F8B48D-5280-437C-BB95-24A464DAF74A}" name="Coluna18" headerRowDxfId="26" dataDxfId="25"/>
+    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="80" dataDxfId="79"/>
+    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="78" dataDxfId="77"/>
+    <tableColumn id="26" xr3:uid="{C91353D4-2D80-49C8-8738-A06C8033990C}" name="Coluna21" headerRowDxfId="76" dataDxfId="75"/>
+    <tableColumn id="5" xr3:uid="{AAB64158-D6DA-4E9F-AC47-A0274997AD5C}" name="Coluna8" headerRowDxfId="74" dataDxfId="73"/>
+    <tableColumn id="4" xr3:uid="{9F1772E8-67AD-410D-A17F-F21B8080770D}" name="Coluna7" headerRowDxfId="72" dataDxfId="71"/>
+    <tableColumn id="9" xr3:uid="{9B194C8C-85D6-4BE2-B1AE-E11E335186F0}" name="Coluna6" headerRowDxfId="70" dataDxfId="69"/>
+    <tableColumn id="8" xr3:uid="{6F1A2D13-ED4B-47DE-AFA9-D11431CAA734}" name="Coluna5" headerRowDxfId="68" dataDxfId="67"/>
+    <tableColumn id="15" xr3:uid="{0C0DAD0A-A76E-4555-A1F1-F78A8F1BE2C2}" name="Coluna4" headerRowDxfId="66" dataDxfId="65"/>
+    <tableColumn id="14" xr3:uid="{C073F03F-8B8F-474F-AF29-E26DD9C1B19A}" name="Coluna3" headerRowDxfId="64" dataDxfId="63"/>
+    <tableColumn id="11" xr3:uid="{AE04A63A-3540-4CF3-9D9A-59CD3577B22C}" name="Coluna2" headerRowDxfId="62" dataDxfId="61"/>
+    <tableColumn id="10" xr3:uid="{F50D06F5-DC15-417E-BE0C-A36478AC8A38}" name="Coluna1" headerRowDxfId="60" dataDxfId="59"/>
+    <tableColumn id="25" xr3:uid="{FF2B42B8-007D-4B78-A1E6-70321A25B422}" name="Coluna20" headerRowDxfId="58" dataDxfId="57"/>
+    <tableColumn id="24" xr3:uid="{B0850B61-1B8F-418B-98C0-04AB09902DE3}" name="Coluna19" headerRowDxfId="56" dataDxfId="55"/>
+    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="54" dataDxfId="53"/>
+    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="52" dataDxfId="51"/>
+    <tableColumn id="6" xr3:uid="{8E7C1DDF-1846-4221-9B0E-C7E4CC7EA057}" name="Coluna9" headerRowDxfId="50" dataDxfId="49"/>
+    <tableColumn id="7" xr3:uid="{3D7A485C-E68B-4D3B-888E-DCFC8EAEE60D}" name="Coluna10" headerRowDxfId="48" dataDxfId="47"/>
+    <tableColumn id="16" xr3:uid="{FECF52FB-CC27-4CA6-B622-AF9F7DB3B554}" name="Coluna11" headerRowDxfId="46" dataDxfId="45"/>
+    <tableColumn id="17" xr3:uid="{D79F8B63-2EF5-45DD-9134-450A005B41F4}" name="Coluna12" headerRowDxfId="44" dataDxfId="43"/>
+    <tableColumn id="18" xr3:uid="{DAFF39A1-0FA6-4AF0-A3B6-380882A29861}" name="Coluna13" headerRowDxfId="42" dataDxfId="41"/>
+    <tableColumn id="19" xr3:uid="{87AE1228-C62F-45E2-A7B1-A0914F89FBE3}" name="Coluna14" headerRowDxfId="40" dataDxfId="39"/>
+    <tableColumn id="20" xr3:uid="{85EAA474-6B84-4EF5-95FF-852AF2C5EA5E}" name="Coluna15" headerRowDxfId="38" dataDxfId="37"/>
+    <tableColumn id="21" xr3:uid="{5B15C019-4680-4877-A95B-F683BA0C59DD}" name="Coluna16" headerRowDxfId="36" dataDxfId="35"/>
+    <tableColumn id="22" xr3:uid="{5C11667F-4365-4FD8-A625-69FCEAC4D24C}" name="Coluna17" headerRowDxfId="34" dataDxfId="33"/>
+    <tableColumn id="23" xr3:uid="{38F8B48D-5280-437C-BB95-24A464DAF74A}" name="Coluna18" headerRowDxfId="32" dataDxfId="31"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -5063,7 +5136,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46228.454061921293</v>
+        <v>46232.781241898148</v>
       </c>
       <c r="C18" s="46" t="s">
         <v>432</v>
@@ -5282,7 +5355,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="58" t="s">
-        <v>549</v>
+        <v>516</v>
       </c>
       <c r="C2" s="58" t="s">
         <v>445</v>
@@ -5291,7 +5364,7 @@
         <v>447</v>
       </c>
       <c r="E2" s="59" t="s">
-        <v>550</v>
+        <v>517</v>
       </c>
       <c r="F2" s="59" t="s">
         <v>446</v>
@@ -5312,7 +5385,7 @@
         <v>191</v>
       </c>
       <c r="L2" s="61" t="str">
-        <f t="shared" ref="L2:M6" si="0">CONCATENATE("", C2)</f>
+        <f t="shared" ref="L2:N17" si="0">CONCATENATE("", C2)</f>
         <v>Gestão</v>
       </c>
       <c r="M2" s="61" t="str">
@@ -5328,10 +5401,10 @@
         <v>Contêiner</v>
       </c>
       <c r="P2" s="42" t="s">
-        <v>551</v>
+        <v>518</v>
       </c>
       <c r="Q2" s="42" t="s">
-        <v>552</v>
+        <v>519</v>
       </c>
       <c r="R2" s="42" t="s">
         <v>191</v>
@@ -5362,7 +5435,7 @@
         <v>191</v>
       </c>
       <c r="Z2" s="42" t="s">
-        <v>553</v>
+        <v>520</v>
       </c>
       <c r="AA2" s="42" t="str">
         <f t="shared" ref="AA2:AA6" si="3">_xlfn.TRANSLATE(P2,"pt","en")</f>
@@ -5374,7 +5447,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="58" t="s">
-        <v>549</v>
+        <v>516</v>
       </c>
       <c r="C3" s="58" t="s">
         <v>445</v>
@@ -5383,7 +5456,7 @@
         <v>447</v>
       </c>
       <c r="E3" s="59" t="s">
-        <v>550</v>
+        <v>517</v>
       </c>
       <c r="F3" s="59" t="s">
         <v>449</v>
@@ -5420,10 +5493,10 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="42" t="s">
-        <v>554</v>
+        <v>521</v>
       </c>
       <c r="Q3" s="42" t="s">
-        <v>552</v>
+        <v>519</v>
       </c>
       <c r="R3" s="42" t="s">
         <v>191</v>
@@ -5466,7 +5539,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>549</v>
+        <v>516</v>
       </c>
       <c r="C4" s="58" t="s">
         <v>445</v>
@@ -5475,7 +5548,7 @@
         <v>447</v>
       </c>
       <c r="E4" s="59" t="s">
-        <v>550</v>
+        <v>517</v>
       </c>
       <c r="F4" s="59" t="s">
         <v>450</v>
@@ -5512,10 +5585,10 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="42" t="s">
-        <v>555</v>
+        <v>522</v>
       </c>
       <c r="Q4" s="42" t="s">
-        <v>552</v>
+        <v>519</v>
       </c>
       <c r="R4" s="42" t="s">
         <v>191</v>
@@ -5558,7 +5631,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="58" t="s">
-        <v>549</v>
+        <v>516</v>
       </c>
       <c r="C5" s="58" t="s">
         <v>445</v>
@@ -5567,7 +5640,7 @@
         <v>447</v>
       </c>
       <c r="E5" s="59" t="s">
-        <v>550</v>
+        <v>517</v>
       </c>
       <c r="F5" s="59" t="s">
         <v>451</v>
@@ -5604,10 +5677,10 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="42" t="s">
-        <v>556</v>
+        <v>523</v>
       </c>
       <c r="Q5" s="42" t="s">
-        <v>552</v>
+        <v>519</v>
       </c>
       <c r="R5" s="42" t="s">
         <v>191</v>
@@ -5650,7 +5723,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>549</v>
+        <v>516</v>
       </c>
       <c r="C6" s="58" t="s">
         <v>445</v>
@@ -5659,7 +5732,7 @@
         <v>447</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>550</v>
+        <v>517</v>
       </c>
       <c r="F6" s="59" t="s">
         <v>452</v>
@@ -5696,10 +5769,10 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="42" t="s">
-        <v>557</v>
+        <v>524</v>
       </c>
       <c r="Q6" s="42" t="s">
-        <v>552</v>
+        <v>519</v>
       </c>
       <c r="R6" s="42" t="s">
         <v>191</v>
@@ -5742,19 +5815,19 @@
         <v>7</v>
       </c>
       <c r="B7" s="58" t="s">
-        <v>549</v>
+        <v>516</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>558</v>
+        <v>525</v>
       </c>
       <c r="D7" s="32" t="s">
         <v>397</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>508</v>
+        <v>475</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>509</v>
+        <v>476</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>191</v>
@@ -5772,44 +5845,44 @@
         <v>191</v>
       </c>
       <c r="L7" s="61" t="str">
-        <f t="shared" ref="L7:N17" si="5">CONCATENATE("", C7)</f>
+        <f t="shared" si="0"/>
         <v>Normativo</v>
       </c>
       <c r="M7" s="61" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>ABNT</v>
       </c>
       <c r="N7" s="61" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>NBR.Parte</v>
       </c>
       <c r="O7" s="61" t="str">
-        <f t="shared" ref="O7:O27" si="6">F7</f>
+        <f t="shared" ref="O7:O19" si="5">F7</f>
         <v>NBR.0M</v>
       </c>
       <c r="P7" s="61" t="s">
-        <v>453</v>
+        <v>527</v>
       </c>
       <c r="Q7" s="61" t="s">
-        <v>454</v>
+        <v>528</v>
       </c>
       <c r="R7" s="42" t="s">
         <v>191</v>
       </c>
       <c r="S7" s="62" t="str">
-        <f t="shared" ref="S7:U22" si="7">SUBSTITUTE(C7, "_", " ")</f>
+        <f t="shared" ref="S7:U19" si="6">SUBSTITUTE(C7, "_", " ")</f>
         <v>Normativo</v>
       </c>
       <c r="T7" s="62" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
       <c r="U7" s="61" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
       <c r="V7" s="42" t="s">
-        <v>448</v>
+        <v>529</v>
       </c>
       <c r="W7" s="66" t="str">
         <f t="shared" si="4"/>
@@ -5822,10 +5895,10 @@
         <v>191</v>
       </c>
       <c r="Z7" s="42" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="AA7" s="63" t="s">
-        <v>456</v>
+        <v>530</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5833,19 +5906,19 @@
         <v>8</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>549</v>
+        <v>516</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>558</v>
+        <v>525</v>
       </c>
       <c r="D8" s="32" t="s">
         <v>397</v>
       </c>
       <c r="E8" s="32" t="s">
-        <v>508</v>
+        <v>475</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>510</v>
+        <v>477</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>191</v>
@@ -5863,44 +5936,44 @@
         <v>191</v>
       </c>
       <c r="L8" s="61" t="str">
+        <f t="shared" si="0"/>
+        <v>Normativo</v>
+      </c>
+      <c r="M8" s="61" t="str">
+        <f t="shared" si="0"/>
+        <v>ABNT</v>
+      </c>
+      <c r="N8" s="61" t="str">
+        <f t="shared" si="0"/>
+        <v>NBR.Parte</v>
+      </c>
+      <c r="O8" s="61" t="str">
         <f t="shared" si="5"/>
+        <v>NBR.0P</v>
+      </c>
+      <c r="P8" s="61" t="s">
+        <v>531</v>
+      </c>
+      <c r="Q8" s="61" t="s">
+        <v>532</v>
+      </c>
+      <c r="R8" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="S8" s="62" t="str">
+        <f t="shared" si="6"/>
         <v>Normativo</v>
       </c>
-      <c r="M8" s="61" t="str">
-        <f t="shared" si="5"/>
+      <c r="T8" s="62" t="str">
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
-      <c r="N8" s="61" t="str">
-        <f t="shared" si="5"/>
+      <c r="U8" s="61" t="str">
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="O8" s="61" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.0P</v>
-      </c>
-      <c r="P8" s="61" t="s">
-        <v>457</v>
-      </c>
-      <c r="Q8" s="61" t="s">
-        <v>458</v>
-      </c>
-      <c r="R8" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="S8" s="62" t="str">
-        <f t="shared" si="7"/>
-        <v>Normativo</v>
-      </c>
-      <c r="T8" s="62" t="str">
-        <f t="shared" si="7"/>
-        <v>ABNT</v>
-      </c>
-      <c r="U8" s="61" t="str">
-        <f t="shared" si="7"/>
-        <v>NBR.Parte</v>
-      </c>
       <c r="V8" s="42" t="s">
-        <v>448</v>
+        <v>529</v>
       </c>
       <c r="W8" s="66" t="str">
         <f t="shared" si="4"/>
@@ -5913,10 +5986,10 @@
         <v>191</v>
       </c>
       <c r="Z8" s="42" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="AA8" s="63" t="s">
-        <v>460</v>
+        <v>533</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5924,19 +5997,19 @@
         <v>9</v>
       </c>
       <c r="B9" s="58" t="s">
-        <v>549</v>
+        <v>516</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>558</v>
+        <v>525</v>
       </c>
       <c r="D9" s="32" t="s">
         <v>397</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>508</v>
+        <v>475</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>511</v>
+        <v>478</v>
       </c>
       <c r="G9" s="35" t="s">
         <v>191</v>
@@ -5954,44 +6027,44 @@
         <v>191</v>
       </c>
       <c r="L9" s="61" t="str">
+        <f t="shared" si="0"/>
+        <v>Normativo</v>
+      </c>
+      <c r="M9" s="61" t="str">
+        <f t="shared" si="0"/>
+        <v>ABNT</v>
+      </c>
+      <c r="N9" s="61" t="str">
+        <f t="shared" si="0"/>
+        <v>NBR.Parte</v>
+      </c>
+      <c r="O9" s="61" t="str">
         <f t="shared" si="5"/>
+        <v>NBR.1D</v>
+      </c>
+      <c r="P9" s="61" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q9" s="61" t="s">
+        <v>535</v>
+      </c>
+      <c r="R9" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="S9" s="62" t="str">
+        <f t="shared" si="6"/>
         <v>Normativo</v>
       </c>
-      <c r="M9" s="61" t="str">
-        <f t="shared" si="5"/>
+      <c r="T9" s="62" t="str">
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
-      <c r="N9" s="61" t="str">
-        <f t="shared" si="5"/>
+      <c r="U9" s="61" t="str">
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="O9" s="61" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.1D</v>
-      </c>
-      <c r="P9" s="61" t="s">
-        <v>461</v>
-      </c>
-      <c r="Q9" s="61" t="s">
-        <v>462</v>
-      </c>
-      <c r="R9" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="S9" s="62" t="str">
-        <f t="shared" si="7"/>
-        <v>Normativo</v>
-      </c>
-      <c r="T9" s="62" t="str">
-        <f t="shared" si="7"/>
-        <v>ABNT</v>
-      </c>
-      <c r="U9" s="61" t="str">
-        <f t="shared" si="7"/>
-        <v>NBR.Parte</v>
-      </c>
       <c r="V9" s="42" t="s">
-        <v>448</v>
+        <v>529</v>
       </c>
       <c r="W9" s="66" t="str">
         <f t="shared" si="4"/>
@@ -6004,10 +6077,10 @@
         <v>191</v>
       </c>
       <c r="Z9" s="42" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="AA9" s="63" t="s">
-        <v>464</v>
+        <v>536</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6015,19 +6088,19 @@
         <v>10</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>549</v>
+        <v>516</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>558</v>
+        <v>525</v>
       </c>
       <c r="D10" s="32" t="s">
         <v>397</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>508</v>
+        <v>475</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>512</v>
+        <v>479</v>
       </c>
       <c r="G10" s="35" t="s">
         <v>191</v>
@@ -6045,44 +6118,44 @@
         <v>191</v>
       </c>
       <c r="L10" s="61" t="str">
+        <f t="shared" si="0"/>
+        <v>Normativo</v>
+      </c>
+      <c r="M10" s="61" t="str">
+        <f t="shared" si="0"/>
+        <v>ABNT</v>
+      </c>
+      <c r="N10" s="61" t="str">
+        <f t="shared" si="0"/>
+        <v>NBR.Parte</v>
+      </c>
+      <c r="O10" s="61" t="str">
         <f t="shared" si="5"/>
+        <v>NBR.1F</v>
+      </c>
+      <c r="P10" s="61" t="s">
+        <v>537</v>
+      </c>
+      <c r="Q10" s="61" t="s">
+        <v>538</v>
+      </c>
+      <c r="R10" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="S10" s="62" t="str">
+        <f t="shared" si="6"/>
         <v>Normativo</v>
       </c>
-      <c r="M10" s="61" t="str">
-        <f t="shared" si="5"/>
+      <c r="T10" s="62" t="str">
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
-      <c r="N10" s="61" t="str">
-        <f t="shared" si="5"/>
+      <c r="U10" s="61" t="str">
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="O10" s="61" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.1F</v>
-      </c>
-      <c r="P10" s="61" t="s">
-        <v>465</v>
-      </c>
-      <c r="Q10" s="61" t="s">
-        <v>466</v>
-      </c>
-      <c r="R10" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="S10" s="62" t="str">
-        <f t="shared" si="7"/>
-        <v>Normativo</v>
-      </c>
-      <c r="T10" s="62" t="str">
-        <f t="shared" si="7"/>
-        <v>ABNT</v>
-      </c>
-      <c r="U10" s="61" t="str">
-        <f t="shared" si="7"/>
-        <v>NBR.Parte</v>
-      </c>
       <c r="V10" s="42" t="s">
-        <v>448</v>
+        <v>529</v>
       </c>
       <c r="W10" s="66" t="str">
         <f t="shared" si="4"/>
@@ -6098,7 +6171,7 @@
         <v>369</v>
       </c>
       <c r="AA10" s="63" t="s">
-        <v>467</v>
+        <v>539</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6106,19 +6179,19 @@
         <v>11</v>
       </c>
       <c r="B11" s="58" t="s">
-        <v>549</v>
+        <v>516</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>558</v>
+        <v>525</v>
       </c>
       <c r="D11" s="32" t="s">
         <v>397</v>
       </c>
       <c r="E11" s="32" t="s">
-        <v>508</v>
+        <v>475</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>513</v>
+        <v>480</v>
       </c>
       <c r="G11" s="35" t="s">
         <v>191</v>
@@ -6136,44 +6209,44 @@
         <v>191</v>
       </c>
       <c r="L11" s="61" t="str">
+        <f t="shared" si="0"/>
+        <v>Normativo</v>
+      </c>
+      <c r="M11" s="61" t="str">
+        <f t="shared" si="0"/>
+        <v>ABNT</v>
+      </c>
+      <c r="N11" s="61" t="str">
+        <f t="shared" si="0"/>
+        <v>NBR.Parte</v>
+      </c>
+      <c r="O11" s="61" t="str">
         <f t="shared" si="5"/>
+        <v>NBR.1S</v>
+      </c>
+      <c r="P11" s="61" t="s">
+        <v>540</v>
+      </c>
+      <c r="Q11" s="61" t="s">
+        <v>541</v>
+      </c>
+      <c r="R11" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="S11" s="62" t="str">
+        <f t="shared" si="6"/>
         <v>Normativo</v>
       </c>
-      <c r="M11" s="61" t="str">
-        <f t="shared" si="5"/>
+      <c r="T11" s="62" t="str">
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
-      <c r="N11" s="61" t="str">
-        <f t="shared" si="5"/>
+      <c r="U11" s="61" t="str">
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="O11" s="61" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.1S</v>
-      </c>
-      <c r="P11" s="61" t="s">
-        <v>468</v>
-      </c>
-      <c r="Q11" s="61" t="s">
-        <v>469</v>
-      </c>
-      <c r="R11" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="S11" s="62" t="str">
-        <f t="shared" si="7"/>
-        <v>Normativo</v>
-      </c>
-      <c r="T11" s="62" t="str">
-        <f t="shared" si="7"/>
-        <v>ABNT</v>
-      </c>
-      <c r="U11" s="61" t="str">
-        <f t="shared" si="7"/>
-        <v>NBR.Parte</v>
-      </c>
       <c r="V11" s="42" t="s">
-        <v>448</v>
+        <v>529</v>
       </c>
       <c r="W11" s="66" t="str">
         <f t="shared" si="4"/>
@@ -6186,10 +6259,10 @@
         <v>191</v>
       </c>
       <c r="Z11" s="42" t="s">
-        <v>470</v>
+        <v>456</v>
       </c>
       <c r="AA11" s="63" t="s">
-        <v>471</v>
+        <v>542</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6197,19 +6270,19 @@
         <v>12</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>549</v>
+        <v>516</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>558</v>
+        <v>525</v>
       </c>
       <c r="D12" s="32" t="s">
         <v>397</v>
       </c>
       <c r="E12" s="32" t="s">
-        <v>508</v>
+        <v>475</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>514</v>
+        <v>481</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>191</v>
@@ -6227,44 +6300,44 @@
         <v>191</v>
       </c>
       <c r="L12" s="61" t="str">
+        <f t="shared" si="0"/>
+        <v>Normativo</v>
+      </c>
+      <c r="M12" s="61" t="str">
+        <f t="shared" si="0"/>
+        <v>ABNT</v>
+      </c>
+      <c r="N12" s="61" t="str">
+        <f t="shared" si="0"/>
+        <v>NBR.Parte</v>
+      </c>
+      <c r="O12" s="61" t="str">
         <f t="shared" si="5"/>
+        <v>NBR.2C</v>
+      </c>
+      <c r="P12" s="61" t="s">
+        <v>543</v>
+      </c>
+      <c r="Q12" s="61" t="s">
+        <v>544</v>
+      </c>
+      <c r="R12" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="S12" s="62" t="str">
+        <f t="shared" si="6"/>
         <v>Normativo</v>
       </c>
-      <c r="M12" s="61" t="str">
-        <f t="shared" si="5"/>
+      <c r="T12" s="62" t="str">
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
-      <c r="N12" s="61" t="str">
-        <f t="shared" si="5"/>
+      <c r="U12" s="61" t="str">
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="O12" s="61" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.2C</v>
-      </c>
-      <c r="P12" s="61" t="s">
-        <v>472</v>
-      </c>
-      <c r="Q12" s="61" t="s">
-        <v>473</v>
-      </c>
-      <c r="R12" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="S12" s="62" t="str">
-        <f t="shared" si="7"/>
-        <v>Normativo</v>
-      </c>
-      <c r="T12" s="62" t="str">
-        <f t="shared" si="7"/>
-        <v>ABNT</v>
-      </c>
-      <c r="U12" s="61" t="str">
-        <f t="shared" si="7"/>
-        <v>NBR.Parte</v>
-      </c>
       <c r="V12" s="42" t="s">
-        <v>448</v>
+        <v>529</v>
       </c>
       <c r="W12" s="66" t="str">
         <f t="shared" si="4"/>
@@ -6277,10 +6350,10 @@
         <v>191</v>
       </c>
       <c r="Z12" s="42" t="s">
-        <v>474</v>
+        <v>457</v>
       </c>
       <c r="AA12" s="63" t="s">
-        <v>475</v>
+        <v>545</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6288,19 +6361,19 @@
         <v>13</v>
       </c>
       <c r="B13" s="58" t="s">
-        <v>549</v>
+        <v>516</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>558</v>
+        <v>525</v>
       </c>
       <c r="D13" s="32" t="s">
         <v>397</v>
       </c>
       <c r="E13" s="32" t="s">
-        <v>508</v>
+        <v>475</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>515</v>
+        <v>482</v>
       </c>
       <c r="G13" s="35" t="s">
         <v>191</v>
@@ -6318,44 +6391,44 @@
         <v>191</v>
       </c>
       <c r="L13" s="61" t="str">
+        <f t="shared" si="0"/>
+        <v>Normativo</v>
+      </c>
+      <c r="M13" s="61" t="str">
+        <f t="shared" si="0"/>
+        <v>ABNT</v>
+      </c>
+      <c r="N13" s="61" t="str">
+        <f t="shared" si="0"/>
+        <v>NBR.Parte</v>
+      </c>
+      <c r="O13" s="61" t="str">
         <f t="shared" si="5"/>
+        <v>NBR.2N</v>
+      </c>
+      <c r="P13" s="61" t="s">
+        <v>546</v>
+      </c>
+      <c r="Q13" s="61" t="s">
+        <v>547</v>
+      </c>
+      <c r="R13" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="S13" s="62" t="str">
+        <f t="shared" si="6"/>
         <v>Normativo</v>
       </c>
-      <c r="M13" s="61" t="str">
-        <f t="shared" si="5"/>
+      <c r="T13" s="62" t="str">
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
-      <c r="N13" s="61" t="str">
-        <f t="shared" si="5"/>
+      <c r="U13" s="61" t="str">
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="O13" s="61" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.2N</v>
-      </c>
-      <c r="P13" s="61" t="s">
-        <v>472</v>
-      </c>
-      <c r="Q13" s="61" t="s">
-        <v>473</v>
-      </c>
-      <c r="R13" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="S13" s="62" t="str">
-        <f t="shared" si="7"/>
-        <v>Normativo</v>
-      </c>
-      <c r="T13" s="62" t="str">
-        <f t="shared" si="7"/>
-        <v>ABNT</v>
-      </c>
-      <c r="U13" s="61" t="str">
-        <f t="shared" si="7"/>
-        <v>NBR.Parte</v>
-      </c>
       <c r="V13" s="42" t="s">
-        <v>448</v>
+        <v>529</v>
       </c>
       <c r="W13" s="66" t="str">
         <f t="shared" si="4"/>
@@ -6368,10 +6441,10 @@
         <v>191</v>
       </c>
       <c r="Z13" s="42" t="s">
-        <v>476</v>
+        <v>458</v>
       </c>
       <c r="AA13" s="63" t="s">
-        <v>475</v>
+        <v>548</v>
       </c>
     </row>
     <row r="14" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6379,19 +6452,19 @@
         <v>14</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>549</v>
+        <v>516</v>
       </c>
       <c r="C14" s="32" t="s">
-        <v>558</v>
+        <v>525</v>
       </c>
       <c r="D14" s="32" t="s">
         <v>397</v>
       </c>
       <c r="E14" s="32" t="s">
-        <v>508</v>
+        <v>475</v>
       </c>
       <c r="F14" s="25" t="s">
-        <v>516</v>
+        <v>483</v>
       </c>
       <c r="G14" s="35" t="s">
         <v>191</v>
@@ -6409,44 +6482,44 @@
         <v>191</v>
       </c>
       <c r="L14" s="61" t="str">
+        <f t="shared" si="0"/>
+        <v>Normativo</v>
+      </c>
+      <c r="M14" s="61" t="str">
+        <f t="shared" si="0"/>
+        <v>ABNT</v>
+      </c>
+      <c r="N14" s="61" t="str">
+        <f t="shared" si="0"/>
+        <v>NBR.Parte</v>
+      </c>
+      <c r="O14" s="61" t="str">
         <f t="shared" si="5"/>
+        <v>NBR.2Q</v>
+      </c>
+      <c r="P14" s="61" t="s">
+        <v>549</v>
+      </c>
+      <c r="Q14" s="61" t="s">
+        <v>550</v>
+      </c>
+      <c r="R14" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="S14" s="62" t="str">
+        <f t="shared" si="6"/>
         <v>Normativo</v>
       </c>
-      <c r="M14" s="61" t="str">
-        <f t="shared" si="5"/>
+      <c r="T14" s="62" t="str">
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
-      <c r="N14" s="61" t="str">
-        <f t="shared" si="5"/>
+      <c r="U14" s="61" t="str">
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="O14" s="61" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.2Q</v>
-      </c>
-      <c r="P14" s="61" t="s">
-        <v>472</v>
-      </c>
-      <c r="Q14" s="61" t="s">
-        <v>473</v>
-      </c>
-      <c r="R14" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="S14" s="62" t="str">
-        <f t="shared" si="7"/>
-        <v>Normativo</v>
-      </c>
-      <c r="T14" s="62" t="str">
-        <f t="shared" si="7"/>
-        <v>ABNT</v>
-      </c>
-      <c r="U14" s="61" t="str">
-        <f t="shared" si="7"/>
-        <v>NBR.Parte</v>
-      </c>
       <c r="V14" s="42" t="s">
-        <v>448</v>
+        <v>529</v>
       </c>
       <c r="W14" s="66" t="str">
         <f t="shared" si="4"/>
@@ -6459,10 +6532,10 @@
         <v>191</v>
       </c>
       <c r="Z14" s="42" t="s">
-        <v>477</v>
+        <v>459</v>
       </c>
       <c r="AA14" s="63" t="s">
-        <v>475</v>
+        <v>551</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6470,19 +6543,19 @@
         <v>15</v>
       </c>
       <c r="B15" s="58" t="s">
-        <v>549</v>
+        <v>516</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>558</v>
+        <v>525</v>
       </c>
       <c r="D15" s="32" t="s">
         <v>397</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>508</v>
+        <v>475</v>
       </c>
       <c r="F15" s="25" t="s">
-        <v>517</v>
+        <v>484</v>
       </c>
       <c r="G15" s="35" t="s">
         <v>191</v>
@@ -6500,44 +6573,44 @@
         <v>191</v>
       </c>
       <c r="L15" s="61" t="str">
+        <f t="shared" si="0"/>
+        <v>Normativo</v>
+      </c>
+      <c r="M15" s="61" t="str">
+        <f t="shared" si="0"/>
+        <v>ABNT</v>
+      </c>
+      <c r="N15" s="61" t="str">
+        <f t="shared" si="0"/>
+        <v>NBR.Parte</v>
+      </c>
+      <c r="O15" s="61" t="str">
         <f t="shared" si="5"/>
+        <v>NBR.3E</v>
+      </c>
+      <c r="P15" s="61" t="s">
+        <v>552</v>
+      </c>
+      <c r="Q15" s="61" t="s">
+        <v>553</v>
+      </c>
+      <c r="R15" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="S15" s="62" t="str">
+        <f t="shared" si="6"/>
         <v>Normativo</v>
       </c>
-      <c r="M15" s="61" t="str">
-        <f t="shared" si="5"/>
+      <c r="T15" s="62" t="str">
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
-      <c r="N15" s="61" t="str">
-        <f t="shared" si="5"/>
+      <c r="U15" s="61" t="str">
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="O15" s="61" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.3E</v>
-      </c>
-      <c r="P15" s="61" t="s">
-        <v>478</v>
-      </c>
-      <c r="Q15" s="61" t="s">
-        <v>479</v>
-      </c>
-      <c r="R15" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="S15" s="62" t="str">
-        <f t="shared" si="7"/>
-        <v>Normativo</v>
-      </c>
-      <c r="T15" s="62" t="str">
-        <f t="shared" si="7"/>
-        <v>ABNT</v>
-      </c>
-      <c r="U15" s="61" t="str">
-        <f t="shared" si="7"/>
-        <v>NBR.Parte</v>
-      </c>
       <c r="V15" s="42" t="s">
-        <v>448</v>
+        <v>529</v>
       </c>
       <c r="W15" s="66" t="str">
         <f t="shared" si="4"/>
@@ -6550,10 +6623,10 @@
         <v>191</v>
       </c>
       <c r="Z15" s="42" t="s">
-        <v>480</v>
+        <v>460</v>
       </c>
       <c r="AA15" s="63" t="s">
-        <v>481</v>
+        <v>554</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6561,19 +6634,19 @@
         <v>16</v>
       </c>
       <c r="B16" s="58" t="s">
-        <v>549</v>
+        <v>516</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>558</v>
+        <v>525</v>
       </c>
       <c r="D16" s="32" t="s">
         <v>397</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>508</v>
+        <v>475</v>
       </c>
       <c r="F16" s="25" t="s">
-        <v>518</v>
+        <v>485</v>
       </c>
       <c r="G16" s="35" t="s">
         <v>191</v>
@@ -6591,44 +6664,44 @@
         <v>191</v>
       </c>
       <c r="L16" s="61" t="str">
+        <f t="shared" si="0"/>
+        <v>Normativo</v>
+      </c>
+      <c r="M16" s="61" t="str">
+        <f t="shared" si="0"/>
+        <v>ABNT</v>
+      </c>
+      <c r="N16" s="61" t="str">
+        <f t="shared" si="0"/>
+        <v>NBR.Parte</v>
+      </c>
+      <c r="O16" s="61" t="str">
         <f t="shared" si="5"/>
+        <v>NBR.3R</v>
+      </c>
+      <c r="P16" s="61" t="s">
+        <v>555</v>
+      </c>
+      <c r="Q16" s="61" t="s">
+        <v>556</v>
+      </c>
+      <c r="R16" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="S16" s="62" t="str">
+        <f t="shared" si="6"/>
         <v>Normativo</v>
       </c>
-      <c r="M16" s="61" t="str">
-        <f t="shared" si="5"/>
+      <c r="T16" s="62" t="str">
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
-      <c r="N16" s="61" t="str">
-        <f t="shared" si="5"/>
+      <c r="U16" s="61" t="str">
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="O16" s="61" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.3R</v>
-      </c>
-      <c r="P16" s="61" t="s">
-        <v>482</v>
-      </c>
-      <c r="Q16" s="61" t="s">
-        <v>483</v>
-      </c>
-      <c r="R16" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="S16" s="62" t="str">
-        <f t="shared" si="7"/>
-        <v>Normativo</v>
-      </c>
-      <c r="T16" s="62" t="str">
-        <f t="shared" si="7"/>
-        <v>ABNT</v>
-      </c>
-      <c r="U16" s="61" t="str">
-        <f t="shared" si="7"/>
-        <v>NBR.Parte</v>
-      </c>
       <c r="V16" s="42" t="s">
-        <v>448</v>
+        <v>529</v>
       </c>
       <c r="W16" s="66" t="str">
         <f t="shared" si="4"/>
@@ -6641,10 +6714,10 @@
         <v>191</v>
       </c>
       <c r="Z16" s="42" t="s">
-        <v>484</v>
+        <v>461</v>
       </c>
       <c r="AA16" s="63" t="s">
-        <v>485</v>
+        <v>557</v>
       </c>
     </row>
     <row r="17" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6652,19 +6725,19 @@
         <v>17</v>
       </c>
       <c r="B17" s="58" t="s">
-        <v>549</v>
+        <v>516</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>558</v>
+        <v>525</v>
       </c>
       <c r="D17" s="32" t="s">
         <v>397</v>
       </c>
       <c r="E17" s="32" t="s">
-        <v>508</v>
+        <v>475</v>
       </c>
       <c r="F17" s="25" t="s">
-        <v>519</v>
+        <v>486</v>
       </c>
       <c r="G17" s="35" t="s">
         <v>191</v>
@@ -6682,44 +6755,44 @@
         <v>191</v>
       </c>
       <c r="L17" s="61" t="str">
+        <f t="shared" si="0"/>
+        <v>Normativo</v>
+      </c>
+      <c r="M17" s="61" t="str">
+        <f t="shared" si="0"/>
+        <v>ABNT</v>
+      </c>
+      <c r="N17" s="61" t="str">
+        <f t="shared" si="0"/>
+        <v>NBR.Parte</v>
+      </c>
+      <c r="O17" s="61" t="str">
         <f t="shared" si="5"/>
+        <v>NBR.4A</v>
+      </c>
+      <c r="P17" s="61" t="s">
+        <v>558</v>
+      </c>
+      <c r="Q17" s="61" t="s">
+        <v>559</v>
+      </c>
+      <c r="R17" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="S17" s="62" t="str">
+        <f t="shared" si="6"/>
         <v>Normativo</v>
       </c>
-      <c r="M17" s="61" t="str">
-        <f t="shared" si="5"/>
+      <c r="T17" s="62" t="str">
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
-      <c r="N17" s="61" t="str">
-        <f t="shared" si="5"/>
+      <c r="U17" s="61" t="str">
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="O17" s="61" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.4A</v>
-      </c>
-      <c r="P17" s="61" t="s">
-        <v>486</v>
-      </c>
-      <c r="Q17" s="61" t="s">
-        <v>487</v>
-      </c>
-      <c r="R17" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="S17" s="62" t="str">
-        <f t="shared" si="7"/>
-        <v>Normativo</v>
-      </c>
-      <c r="T17" s="62" t="str">
-        <f t="shared" si="7"/>
-        <v>ABNT</v>
-      </c>
-      <c r="U17" s="61" t="str">
-        <f t="shared" si="7"/>
-        <v>NBR.Parte</v>
-      </c>
       <c r="V17" s="42" t="s">
-        <v>448</v>
+        <v>529</v>
       </c>
       <c r="W17" s="66" t="str">
         <f t="shared" si="4"/>
@@ -6732,10 +6805,10 @@
         <v>191</v>
       </c>
       <c r="Z17" s="42" t="s">
-        <v>488</v>
+        <v>462</v>
       </c>
       <c r="AA17" s="63" t="s">
-        <v>489</v>
+        <v>560</v>
       </c>
     </row>
     <row r="18" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6743,19 +6816,19 @@
         <v>18</v>
       </c>
       <c r="B18" s="58" t="s">
-        <v>549</v>
+        <v>516</v>
       </c>
       <c r="C18" s="32" t="s">
-        <v>558</v>
+        <v>525</v>
       </c>
       <c r="D18" s="32" t="s">
         <v>397</v>
       </c>
       <c r="E18" s="32" t="s">
-        <v>508</v>
+        <v>475</v>
       </c>
       <c r="F18" s="25" t="s">
-        <v>520</v>
+        <v>487</v>
       </c>
       <c r="G18" s="35" t="s">
         <v>191</v>
@@ -6773,44 +6846,44 @@
         <v>191</v>
       </c>
       <c r="L18" s="61" t="str">
-        <f t="shared" ref="L18:N27" si="8">CONCATENATE("", C18)</f>
+        <f t="shared" ref="L18:N19" si="7">CONCATENATE("", C18)</f>
         <v>Normativo</v>
       </c>
       <c r="M18" s="61" t="str">
-        <f t="shared" si="8"/>
-        <v>ABNT</v>
-      </c>
-      <c r="N18" s="61" t="str">
-        <f t="shared" si="8"/>
-        <v>NBR.Parte</v>
-      </c>
-      <c r="O18" s="61" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.4U</v>
-      </c>
-      <c r="P18" s="61" t="s">
-        <v>490</v>
-      </c>
-      <c r="Q18" s="61" t="s">
-        <v>491</v>
-      </c>
-      <c r="R18" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="S18" s="62" t="str">
-        <f t="shared" si="7"/>
-        <v>Normativo</v>
-      </c>
-      <c r="T18" s="62" t="str">
         <f t="shared" si="7"/>
         <v>ABNT</v>
       </c>
-      <c r="U18" s="61" t="str">
+      <c r="N18" s="61" t="str">
         <f t="shared" si="7"/>
         <v>NBR.Parte</v>
       </c>
+      <c r="O18" s="61" t="str">
+        <f t="shared" si="5"/>
+        <v>NBR.4U</v>
+      </c>
+      <c r="P18" s="61" t="s">
+        <v>561</v>
+      </c>
+      <c r="Q18" s="61" t="s">
+        <v>562</v>
+      </c>
+      <c r="R18" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="S18" s="62" t="str">
+        <f t="shared" si="6"/>
+        <v>Normativo</v>
+      </c>
+      <c r="T18" s="62" t="str">
+        <f t="shared" si="6"/>
+        <v>ABNT</v>
+      </c>
+      <c r="U18" s="61" t="str">
+        <f t="shared" si="6"/>
+        <v>NBR.Parte</v>
+      </c>
       <c r="V18" s="42" t="s">
-        <v>448</v>
+        <v>529</v>
       </c>
       <c r="W18" s="66" t="str">
         <f t="shared" si="4"/>
@@ -6823,10 +6896,10 @@
         <v>191</v>
       </c>
       <c r="Z18" s="42" t="s">
-        <v>492</v>
+        <v>463</v>
       </c>
       <c r="AA18" s="63" t="s">
-        <v>493</v>
+        <v>563</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6834,19 +6907,19 @@
         <v>19</v>
       </c>
       <c r="B19" s="58" t="s">
-        <v>549</v>
+        <v>516</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>558</v>
+        <v>525</v>
       </c>
       <c r="D19" s="32" t="s">
         <v>397</v>
       </c>
       <c r="E19" s="32" t="s">
-        <v>508</v>
+        <v>475</v>
       </c>
       <c r="F19" s="25" t="s">
-        <v>521</v>
+        <v>488</v>
       </c>
       <c r="G19" s="35" t="s">
         <v>191</v>
@@ -6864,44 +6937,44 @@
         <v>191</v>
       </c>
       <c r="L19" s="61" t="str">
-        <f t="shared" si="8"/>
-        <v>Normativo</v>
-      </c>
-      <c r="M19" s="61" t="str">
-        <f t="shared" si="8"/>
-        <v>ABNT</v>
-      </c>
-      <c r="N19" s="61" t="str">
-        <f t="shared" si="8"/>
-        <v>NBR.Parte</v>
-      </c>
-      <c r="O19" s="61" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.5I</v>
-      </c>
-      <c r="P19" s="61" t="s">
-        <v>494</v>
-      </c>
-      <c r="Q19" s="61" t="s">
-        <v>495</v>
-      </c>
-      <c r="R19" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="S19" s="62" t="str">
         <f t="shared" si="7"/>
         <v>Normativo</v>
       </c>
-      <c r="T19" s="62" t="str">
+      <c r="M19" s="61" t="str">
         <f t="shared" si="7"/>
         <v>ABNT</v>
       </c>
-      <c r="U19" s="61" t="str">
+      <c r="N19" s="61" t="str">
         <f t="shared" si="7"/>
         <v>NBR.Parte</v>
       </c>
+      <c r="O19" s="61" t="str">
+        <f t="shared" si="5"/>
+        <v>NBR.5I</v>
+      </c>
+      <c r="P19" s="61" t="s">
+        <v>564</v>
+      </c>
+      <c r="Q19" s="61" t="s">
+        <v>565</v>
+      </c>
+      <c r="R19" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="S19" s="62" t="str">
+        <f t="shared" si="6"/>
+        <v>Normativo</v>
+      </c>
+      <c r="T19" s="62" t="str">
+        <f t="shared" si="6"/>
+        <v>ABNT</v>
+      </c>
+      <c r="U19" s="61" t="str">
+        <f t="shared" si="6"/>
+        <v>NBR.Parte</v>
+      </c>
       <c r="V19" s="42" t="s">
-        <v>448</v>
+        <v>529</v>
       </c>
       <c r="W19" s="66" t="str">
         <f t="shared" si="4"/>
@@ -6914,10 +6987,10 @@
         <v>191</v>
       </c>
       <c r="Z19" s="42" t="s">
-        <v>496</v>
+        <v>464</v>
       </c>
       <c r="AA19" s="63" t="s">
-        <v>497</v>
+        <v>566</v>
       </c>
     </row>
     <row r="20" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6925,19 +6998,19 @@
         <v>20</v>
       </c>
       <c r="B20" s="58" t="s">
-        <v>549</v>
+        <v>516</v>
       </c>
       <c r="C20" s="32" t="s">
-        <v>558</v>
+        <v>525</v>
       </c>
       <c r="D20" s="32" t="s">
-        <v>559</v>
+        <v>526</v>
       </c>
       <c r="E20" s="32" t="s">
-        <v>527</v>
+        <v>494</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>522</v>
+        <v>489</v>
       </c>
       <c r="G20" s="60" t="s">
         <v>191</v>
@@ -6955,7 +7028,7 @@
         <v>191</v>
       </c>
       <c r="L20" s="61" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="L18:N27" si="8">CONCATENATE("", C20)</f>
         <v>Normativo</v>
       </c>
       <c r="M20" s="61" t="str">
@@ -6967,11 +7040,11 @@
         <v>NBR.Fases</v>
       </c>
       <c r="O20" s="61" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="O7:O27" si="9">F20</f>
         <v>NBR.F.Programação</v>
       </c>
       <c r="P20" s="42" t="s">
-        <v>528</v>
+        <v>495</v>
       </c>
       <c r="Q20" s="42" t="str">
         <f>_xlfn.TRANSLATE(P20,"pt","es")</f>
@@ -6981,15 +7054,15 @@
         <v>191</v>
       </c>
       <c r="S20" s="62" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="S7:U22" si="10">SUBSTITUTE(C20, "_", " ")</f>
         <v>Normativo</v>
       </c>
       <c r="T20" s="62" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>NBR.Temática</v>
       </c>
       <c r="U20" s="61" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>NBR.Fases</v>
       </c>
       <c r="V20" s="42" t="s">
@@ -7006,7 +7079,7 @@
         <v>191</v>
       </c>
       <c r="Z20" s="62" t="s">
-        <v>536</v>
+        <v>503</v>
       </c>
       <c r="AA20" s="42" t="str">
         <f>_xlfn.TRANSLATE(P20,"pt","en")</f>
@@ -7018,19 +7091,19 @@
         <v>21</v>
       </c>
       <c r="B21" s="58" t="s">
-        <v>549</v>
+        <v>516</v>
       </c>
       <c r="C21" s="32" t="s">
-        <v>558</v>
+        <v>525</v>
       </c>
       <c r="D21" s="32" t="s">
-        <v>559</v>
+        <v>526</v>
       </c>
       <c r="E21" s="32" t="s">
-        <v>527</v>
+        <v>494</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>523</v>
+        <v>490</v>
       </c>
       <c r="G21" s="35" t="s">
         <v>191</v>
@@ -7060,29 +7133,29 @@
         <v>NBR.Fases</v>
       </c>
       <c r="O21" s="61" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>NBR.F.Estudo.Preliminar</v>
       </c>
       <c r="P21" s="61" t="s">
-        <v>535</v>
+        <v>502</v>
       </c>
       <c r="Q21" s="42" t="str">
-        <f t="shared" ref="Q21:Q27" si="9">_xlfn.TRANSLATE(P21,"pt","es")</f>
+        <f t="shared" ref="Q21:Q27" si="11">_xlfn.TRANSLATE(P21,"pt","es")</f>
         <v>Fase de Estudios Preliminares</v>
       </c>
       <c r="R21" s="42" t="s">
         <v>191</v>
       </c>
       <c r="S21" s="62" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>Normativo</v>
       </c>
       <c r="T21" s="62" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>NBR.Temática</v>
       </c>
       <c r="U21" s="61" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>NBR.Fases</v>
       </c>
       <c r="V21" s="42" t="s">
@@ -7099,10 +7172,10 @@
         <v>191</v>
       </c>
       <c r="Z21" s="62" t="s">
-        <v>537</v>
+        <v>504</v>
       </c>
       <c r="AA21" s="42" t="str">
-        <f t="shared" ref="AA21:AA27" si="10">_xlfn.TRANSLATE(P21,"pt","en")</f>
+        <f t="shared" ref="AA21:AA27" si="12">_xlfn.TRANSLATE(P21,"pt","en")</f>
         <v>Preliminary Studies Phase</v>
       </c>
     </row>
@@ -7111,19 +7184,19 @@
         <v>22</v>
       </c>
       <c r="B22" s="58" t="s">
-        <v>549</v>
+        <v>516</v>
       </c>
       <c r="C22" s="32" t="s">
-        <v>558</v>
+        <v>525</v>
       </c>
       <c r="D22" s="32" t="s">
-        <v>559</v>
+        <v>526</v>
       </c>
       <c r="E22" s="32" t="s">
-        <v>527</v>
+        <v>494</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>544</v>
+        <v>511</v>
       </c>
       <c r="G22" s="35" t="s">
         <v>191</v>
@@ -7153,29 +7226,29 @@
         <v>NBR.Fases</v>
       </c>
       <c r="O22" s="61" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>NBR.F.Projetual</v>
       </c>
       <c r="P22" s="61" t="s">
-        <v>529</v>
+        <v>496</v>
       </c>
       <c r="Q22" s="42" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Fase del proyecto</v>
       </c>
       <c r="R22" s="42" t="s">
         <v>191</v>
       </c>
       <c r="S22" s="62" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>Normativo</v>
       </c>
       <c r="T22" s="62" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>NBR.Temática</v>
       </c>
       <c r="U22" s="61" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>NBR.Fases</v>
       </c>
       <c r="V22" s="42" t="s">
@@ -7192,10 +7265,10 @@
         <v>191</v>
       </c>
       <c r="Z22" s="62" t="s">
-        <v>538</v>
+        <v>505</v>
       </c>
       <c r="AA22" s="42" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Project Phase</v>
       </c>
     </row>
@@ -7204,19 +7277,19 @@
         <v>23</v>
       </c>
       <c r="B23" s="58" t="s">
-        <v>549</v>
+        <v>516</v>
       </c>
       <c r="C23" s="32" t="s">
-        <v>558</v>
+        <v>525</v>
       </c>
       <c r="D23" s="32" t="s">
-        <v>559</v>
+        <v>526</v>
       </c>
       <c r="E23" s="32" t="s">
-        <v>527</v>
+        <v>494</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>545</v>
+        <v>512</v>
       </c>
       <c r="G23" s="35" t="s">
         <v>191</v>
@@ -7246,29 +7319,29 @@
         <v>NBR.Fases</v>
       </c>
       <c r="O23" s="61" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>NBR.F.Licitação</v>
       </c>
       <c r="P23" s="61" t="s">
-        <v>534</v>
+        <v>501</v>
       </c>
       <c r="Q23" s="42" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Fase de subasta</v>
       </c>
       <c r="R23" s="42" t="s">
         <v>191</v>
       </c>
       <c r="S23" s="62" t="str">
-        <f t="shared" ref="S23:U27" si="11">SUBSTITUTE(C23, "_", " ")</f>
+        <f t="shared" ref="S23:U27" si="13">SUBSTITUTE(C23, "_", " ")</f>
         <v>Normativo</v>
       </c>
       <c r="T23" s="62" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>NBR.Temática</v>
       </c>
       <c r="U23" s="61" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>NBR.Fases</v>
       </c>
       <c r="V23" s="42" t="s">
@@ -7285,10 +7358,10 @@
         <v>191</v>
       </c>
       <c r="Z23" s="62" t="s">
-        <v>539</v>
+        <v>506</v>
       </c>
       <c r="AA23" s="42" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bidding Phase</v>
       </c>
     </row>
@@ -7297,19 +7370,19 @@
         <v>24</v>
       </c>
       <c r="B24" s="58" t="s">
-        <v>549</v>
+        <v>516</v>
       </c>
       <c r="C24" s="32" t="s">
-        <v>558</v>
+        <v>525</v>
       </c>
       <c r="D24" s="32" t="s">
-        <v>559</v>
+        <v>526</v>
       </c>
       <c r="E24" s="32" t="s">
-        <v>527</v>
+        <v>494</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>524</v>
+        <v>491</v>
       </c>
       <c r="G24" s="35" t="s">
         <v>191</v>
@@ -7339,29 +7412,29 @@
         <v>NBR.Fases</v>
       </c>
       <c r="O24" s="61" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>NBR.F.Construtiva</v>
       </c>
       <c r="P24" s="61" t="s">
-        <v>533</v>
+        <v>500</v>
       </c>
       <c r="Q24" s="42" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Fase de construcción</v>
       </c>
       <c r="R24" s="42" t="s">
         <v>191</v>
       </c>
       <c r="S24" s="62" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Normativo</v>
       </c>
       <c r="T24" s="62" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>NBR.Temática</v>
       </c>
       <c r="U24" s="61" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>NBR.Fases</v>
       </c>
       <c r="V24" s="42" t="s">
@@ -7378,10 +7451,10 @@
         <v>191</v>
       </c>
       <c r="Z24" s="62" t="s">
-        <v>543</v>
+        <v>510</v>
       </c>
       <c r="AA24" s="42" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Construction Phase</v>
       </c>
     </row>
@@ -7390,19 +7463,19 @@
         <v>25</v>
       </c>
       <c r="B25" s="58" t="s">
-        <v>549</v>
+        <v>516</v>
       </c>
       <c r="C25" s="32" t="s">
-        <v>558</v>
+        <v>525</v>
       </c>
       <c r="D25" s="32" t="s">
-        <v>559</v>
+        <v>526</v>
       </c>
       <c r="E25" s="32" t="s">
-        <v>527</v>
+        <v>494</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>525</v>
+        <v>492</v>
       </c>
       <c r="G25" s="35" t="s">
         <v>191</v>
@@ -7432,29 +7505,29 @@
         <v>NBR.Fases</v>
       </c>
       <c r="O25" s="61" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>NBR.F.Comissionamento</v>
       </c>
       <c r="P25" s="61" t="s">
-        <v>530</v>
+        <v>497</v>
       </c>
       <c r="Q25" s="42" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Fase de puesta en servicio</v>
       </c>
       <c r="R25" s="42" t="s">
         <v>191</v>
       </c>
       <c r="S25" s="62" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Normativo</v>
       </c>
       <c r="T25" s="62" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>NBR.Temática</v>
       </c>
       <c r="U25" s="61" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>NBR.Fases</v>
       </c>
       <c r="V25" s="42" t="s">
@@ -7471,10 +7544,10 @@
         <v>191</v>
       </c>
       <c r="Z25" s="62" t="s">
-        <v>540</v>
+        <v>507</v>
       </c>
       <c r="AA25" s="42" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Commissioning Phase</v>
       </c>
     </row>
@@ -7483,19 +7556,19 @@
         <v>26</v>
       </c>
       <c r="B26" s="58" t="s">
-        <v>549</v>
+        <v>516</v>
       </c>
       <c r="C26" s="32" t="s">
-        <v>558</v>
+        <v>525</v>
       </c>
       <c r="D26" s="32" t="s">
-        <v>559</v>
+        <v>526</v>
       </c>
       <c r="E26" s="32" t="s">
-        <v>527</v>
+        <v>494</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>546</v>
+        <v>513</v>
       </c>
       <c r="G26" s="35" t="s">
         <v>191</v>
@@ -7525,29 +7598,29 @@
         <v>NBR.Fases</v>
       </c>
       <c r="O26" s="61" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>NBR.F.Operacional</v>
       </c>
       <c r="P26" s="61" t="s">
-        <v>531</v>
+        <v>498</v>
       </c>
       <c r="Q26" s="42" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Fase de Operación</v>
       </c>
       <c r="R26" s="42" t="s">
         <v>191</v>
       </c>
       <c r="S26" s="62" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Normativo</v>
       </c>
       <c r="T26" s="62" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>NBR.Temática</v>
       </c>
       <c r="U26" s="61" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>NBR.Fases</v>
       </c>
       <c r="V26" s="42" t="s">
@@ -7564,10 +7637,10 @@
         <v>191</v>
       </c>
       <c r="Z26" s="62" t="s">
-        <v>541</v>
+        <v>508</v>
       </c>
       <c r="AA26" s="42" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Operation Phase</v>
       </c>
     </row>
@@ -7576,19 +7649,19 @@
         <v>27</v>
       </c>
       <c r="B27" s="58" t="s">
-        <v>549</v>
+        <v>516</v>
       </c>
       <c r="C27" s="32" t="s">
-        <v>558</v>
+        <v>525</v>
       </c>
       <c r="D27" s="32" t="s">
-        <v>559</v>
+        <v>526</v>
       </c>
       <c r="E27" s="32" t="s">
-        <v>527</v>
+        <v>494</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>526</v>
+        <v>493</v>
       </c>
       <c r="G27" s="35" t="s">
         <v>191</v>
@@ -7618,29 +7691,29 @@
         <v>NBR.Fases</v>
       </c>
       <c r="O27" s="61" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>NBR.F.Fechamento.Demolição</v>
       </c>
       <c r="P27" s="61" t="s">
-        <v>532</v>
+        <v>499</v>
       </c>
       <c r="Q27" s="42" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Fase de cierre y demolición</v>
       </c>
       <c r="R27" s="42" t="s">
         <v>191</v>
       </c>
       <c r="S27" s="62" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Normativo</v>
       </c>
       <c r="T27" s="62" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>NBR.Temática</v>
       </c>
       <c r="U27" s="61" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>NBR.Fases</v>
       </c>
       <c r="V27" s="42" t="s">
@@ -7657,33 +7730,46 @@
         <v>191</v>
       </c>
       <c r="Z27" s="62" t="s">
-        <v>542</v>
+        <v>509</v>
       </c>
       <c r="AA27" s="42" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Closure and Demolition Phase</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:B27">
-    <cfRule type="cellIs" dxfId="24" priority="1" operator="equal">
+  <conditionalFormatting sqref="A2:B6 A20:B27">
+    <cfRule type="cellIs" dxfId="30" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F6">
-    <cfRule type="duplicateValues" dxfId="23" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F20">
-    <cfRule type="duplicateValues" dxfId="19" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="29"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA1:AA27">
-    <cfRule type="cellIs" dxfId="15" priority="6" operator="equal">
+  <conditionalFormatting sqref="AA1:AA6 AA20:AA27">
+    <cfRule type="cellIs" dxfId="21" priority="12" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A7:B19">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7:F19">
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA7:AA19">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7833,7 +7919,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7878,7 +7964,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8002,7 +8088,7 @@
         <v>367</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>558</v>
+        <v>525</v>
       </c>
       <c r="D2" s="64" t="s">
         <v>191</v>
@@ -8026,13 +8112,13 @@
         <v>366</v>
       </c>
       <c r="K2" s="50" t="s">
-        <v>505</v>
+        <v>472</v>
       </c>
       <c r="L2" s="49" t="s">
         <v>422</v>
       </c>
       <c r="M2" s="50" t="s">
-        <v>506</v>
+        <v>473</v>
       </c>
       <c r="N2" s="36" t="s">
         <v>1</v>
@@ -8079,10 +8165,10 @@
         <v>371</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>508</v>
+        <v>475</v>
       </c>
       <c r="D3" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E3" s="65" t="s">
         <v>367</v>
@@ -8103,13 +8189,13 @@
         <v>366</v>
       </c>
       <c r="K3" s="50" t="s">
-        <v>505</v>
+        <v>472</v>
       </c>
       <c r="L3" s="49" t="s">
         <v>422</v>
       </c>
       <c r="M3" s="50" t="s">
-        <v>547</v>
+        <v>514</v>
       </c>
       <c r="N3" s="36" t="s">
         <v>1</v>
@@ -8156,10 +8242,10 @@
         <v>369</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>512</v>
+        <v>479</v>
       </c>
       <c r="D4" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E4" s="65" t="s">
         <v>371</v>
@@ -8180,13 +8266,13 @@
         <v>366</v>
       </c>
       <c r="K4" s="50" t="s">
-        <v>505</v>
+        <v>472</v>
       </c>
       <c r="L4" s="49" t="s">
         <v>422</v>
       </c>
       <c r="M4" s="50" t="s">
-        <v>548</v>
+        <v>515</v>
       </c>
       <c r="N4" s="36" t="s">
         <v>1</v>
@@ -8233,10 +8319,10 @@
         <v>199</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>522</v>
+        <v>489</v>
       </c>
       <c r="D5" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E5" s="65" t="s">
         <v>371</v>
@@ -8263,7 +8349,7 @@
         <v>422</v>
       </c>
       <c r="M5" s="37" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="N5" s="36" t="s">
         <v>1</v>
@@ -8310,10 +8396,10 @@
         <v>200</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>522</v>
+        <v>489</v>
       </c>
       <c r="D6" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E6" s="65" t="s">
         <v>371</v>
@@ -8340,7 +8426,7 @@
         <v>422</v>
       </c>
       <c r="M6" s="37" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="N6" s="36" t="s">
         <v>1</v>
@@ -8387,10 +8473,10 @@
         <v>201</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>522</v>
+        <v>489</v>
       </c>
       <c r="D7" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E7" s="65" t="s">
         <v>371</v>
@@ -8417,7 +8503,7 @@
         <v>422</v>
       </c>
       <c r="M7" s="37" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="N7" s="36" t="s">
         <v>1</v>
@@ -8464,10 +8550,10 @@
         <v>202</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>522</v>
+        <v>489</v>
       </c>
       <c r="D8" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E8" s="65" t="s">
         <v>371</v>
@@ -8494,7 +8580,7 @@
         <v>422</v>
       </c>
       <c r="M8" s="37" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="N8" s="36" t="s">
         <v>1</v>
@@ -8541,10 +8627,10 @@
         <v>203</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>522</v>
+        <v>489</v>
       </c>
       <c r="D9" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E9" s="65" t="s">
         <v>371</v>
@@ -8571,7 +8657,7 @@
         <v>422</v>
       </c>
       <c r="M9" s="37" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="N9" s="36" t="s">
         <v>1</v>
@@ -8618,10 +8704,10 @@
         <v>204</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>522</v>
+        <v>489</v>
       </c>
       <c r="D10" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E10" s="65" t="s">
         <v>371</v>
@@ -8648,7 +8734,7 @@
         <v>422</v>
       </c>
       <c r="M10" s="37" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="N10" s="36" t="s">
         <v>1</v>
@@ -8695,10 +8781,10 @@
         <v>205</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>522</v>
+        <v>489</v>
       </c>
       <c r="D11" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E11" s="65" t="s">
         <v>371</v>
@@ -8725,7 +8811,7 @@
         <v>422</v>
       </c>
       <c r="M11" s="37" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="N11" s="36" t="s">
         <v>1</v>
@@ -8772,10 +8858,10 @@
         <v>206</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>522</v>
+        <v>489</v>
       </c>
       <c r="D12" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E12" s="65" t="s">
         <v>371</v>
@@ -8802,7 +8888,7 @@
         <v>422</v>
       </c>
       <c r="M12" s="37" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="N12" s="36" t="s">
         <v>1</v>
@@ -8849,10 +8935,10 @@
         <v>207</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>522</v>
+        <v>489</v>
       </c>
       <c r="D13" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E13" s="65" t="s">
         <v>371</v>
@@ -8879,7 +8965,7 @@
         <v>422</v>
       </c>
       <c r="M13" s="37" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="N13" s="36" t="s">
         <v>1</v>
@@ -8926,10 +9012,10 @@
         <v>208</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>522</v>
+        <v>489</v>
       </c>
       <c r="D14" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E14" s="65" t="s">
         <v>371</v>
@@ -8956,7 +9042,7 @@
         <v>422</v>
       </c>
       <c r="M14" s="37" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="N14" s="36" t="s">
         <v>1</v>
@@ -9003,10 +9089,10 @@
         <v>209</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>522</v>
+        <v>489</v>
       </c>
       <c r="D15" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E15" s="65" t="s">
         <v>371</v>
@@ -9033,7 +9119,7 @@
         <v>422</v>
       </c>
       <c r="M15" s="37" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="N15" s="36" t="s">
         <v>1</v>
@@ -9080,10 +9166,10 @@
         <v>210</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>522</v>
+        <v>489</v>
       </c>
       <c r="D16" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E16" s="65" t="s">
         <v>371</v>
@@ -9110,7 +9196,7 @@
         <v>422</v>
       </c>
       <c r="M16" s="37" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="N16" s="36" t="s">
         <v>1</v>
@@ -9157,10 +9243,10 @@
         <v>211</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>522</v>
+        <v>489</v>
       </c>
       <c r="D17" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E17" s="65" t="s">
         <v>371</v>
@@ -9187,7 +9273,7 @@
         <v>422</v>
       </c>
       <c r="M17" s="37" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="N17" s="36" t="s">
         <v>1</v>
@@ -9234,10 +9320,10 @@
         <v>212</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>522</v>
+        <v>489</v>
       </c>
       <c r="D18" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E18" s="65" t="s">
         <v>371</v>
@@ -9264,7 +9350,7 @@
         <v>422</v>
       </c>
       <c r="M18" s="37" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="N18" s="36" t="s">
         <v>1</v>
@@ -9311,10 +9397,10 @@
         <v>213</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>522</v>
+        <v>489</v>
       </c>
       <c r="D19" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E19" s="65" t="s">
         <v>371</v>
@@ -9341,7 +9427,7 @@
         <v>422</v>
       </c>
       <c r="M19" s="37" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="N19" s="36" t="s">
         <v>1</v>
@@ -9388,10 +9474,10 @@
         <v>214</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>522</v>
+        <v>489</v>
       </c>
       <c r="D20" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E20" s="65" t="s">
         <v>371</v>
@@ -9418,7 +9504,7 @@
         <v>422</v>
       </c>
       <c r="M20" s="37" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="N20" s="36" t="s">
         <v>1</v>
@@ -9465,10 +9551,10 @@
         <v>215</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>522</v>
+        <v>489</v>
       </c>
       <c r="D21" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E21" s="65" t="s">
         <v>371</v>
@@ -9495,7 +9581,7 @@
         <v>422</v>
       </c>
       <c r="M21" s="37" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="N21" s="36" t="s">
         <v>1</v>
@@ -9542,10 +9628,10 @@
         <v>216</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>522</v>
+        <v>489</v>
       </c>
       <c r="D22" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E22" s="65" t="s">
         <v>371</v>
@@ -9572,7 +9658,7 @@
         <v>422</v>
       </c>
       <c r="M22" s="37" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="N22" s="36" t="s">
         <v>1</v>
@@ -9619,10 +9705,10 @@
         <v>217</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>522</v>
+        <v>489</v>
       </c>
       <c r="D23" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E23" s="65" t="s">
         <v>371</v>
@@ -9649,7 +9735,7 @@
         <v>422</v>
       </c>
       <c r="M23" s="37" t="s">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="N23" s="36" t="s">
         <v>1</v>
@@ -9696,10 +9782,10 @@
         <v>218</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>523</v>
+        <v>490</v>
       </c>
       <c r="D24" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E24" s="65" t="s">
         <v>371</v>
@@ -9726,7 +9812,7 @@
         <v>422</v>
       </c>
       <c r="M24" s="37" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="N24" s="36" t="s">
         <v>1</v>
@@ -9773,10 +9859,10 @@
         <v>219</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>523</v>
+        <v>490</v>
       </c>
       <c r="D25" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E25" s="65" t="s">
         <v>371</v>
@@ -9803,7 +9889,7 @@
         <v>422</v>
       </c>
       <c r="M25" s="37" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="N25" s="36" t="s">
         <v>1</v>
@@ -9850,10 +9936,10 @@
         <v>220</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>523</v>
+        <v>490</v>
       </c>
       <c r="D26" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E26" s="65" t="s">
         <v>371</v>
@@ -9880,7 +9966,7 @@
         <v>422</v>
       </c>
       <c r="M26" s="37" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="N26" s="36" t="s">
         <v>1</v>
@@ -9927,10 +10013,10 @@
         <v>221</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>523</v>
+        <v>490</v>
       </c>
       <c r="D27" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E27" s="65" t="s">
         <v>371</v>
@@ -9957,7 +10043,7 @@
         <v>422</v>
       </c>
       <c r="M27" s="37" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="N27" s="36" t="s">
         <v>1</v>
@@ -10004,10 +10090,10 @@
         <v>222</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>523</v>
+        <v>490</v>
       </c>
       <c r="D28" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E28" s="65" t="s">
         <v>371</v>
@@ -10034,7 +10120,7 @@
         <v>422</v>
       </c>
       <c r="M28" s="37" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="N28" s="36" t="s">
         <v>1</v>
@@ -10081,10 +10167,10 @@
         <v>223</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>523</v>
+        <v>490</v>
       </c>
       <c r="D29" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E29" s="65" t="s">
         <v>371</v>
@@ -10111,7 +10197,7 @@
         <v>422</v>
       </c>
       <c r="M29" s="37" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="N29" s="36" t="s">
         <v>1</v>
@@ -10158,10 +10244,10 @@
         <v>224</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>523</v>
+        <v>490</v>
       </c>
       <c r="D30" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E30" s="65" t="s">
         <v>371</v>
@@ -10188,7 +10274,7 @@
         <v>422</v>
       </c>
       <c r="M30" s="37" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="N30" s="36" t="s">
         <v>1</v>
@@ -10235,10 +10321,10 @@
         <v>225</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>523</v>
+        <v>490</v>
       </c>
       <c r="D31" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E31" s="65" t="s">
         <v>371</v>
@@ -10265,7 +10351,7 @@
         <v>422</v>
       </c>
       <c r="M31" s="37" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="N31" s="36" t="s">
         <v>1</v>
@@ -10312,10 +10398,10 @@
         <v>226</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>523</v>
+        <v>490</v>
       </c>
       <c r="D32" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E32" s="65" t="s">
         <v>371</v>
@@ -10342,7 +10428,7 @@
         <v>422</v>
       </c>
       <c r="M32" s="37" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="N32" s="36" t="s">
         <v>1</v>
@@ -10389,10 +10475,10 @@
         <v>227</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>523</v>
+        <v>490</v>
       </c>
       <c r="D33" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E33" s="65" t="s">
         <v>371</v>
@@ -10419,7 +10505,7 @@
         <v>422</v>
       </c>
       <c r="M33" s="37" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="N33" s="36" t="s">
         <v>1</v>
@@ -10466,10 +10552,10 @@
         <v>228</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>523</v>
+        <v>490</v>
       </c>
       <c r="D34" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E34" s="65" t="s">
         <v>371</v>
@@ -10496,7 +10582,7 @@
         <v>422</v>
       </c>
       <c r="M34" s="37" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="N34" s="36" t="s">
         <v>1</v>
@@ -10543,10 +10629,10 @@
         <v>229</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>523</v>
+        <v>490</v>
       </c>
       <c r="D35" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E35" s="65" t="s">
         <v>371</v>
@@ -10573,7 +10659,7 @@
         <v>422</v>
       </c>
       <c r="M35" s="37" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="N35" s="36" t="s">
         <v>1</v>
@@ -10620,10 +10706,10 @@
         <v>230</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>523</v>
+        <v>490</v>
       </c>
       <c r="D36" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E36" s="65" t="s">
         <v>371</v>
@@ -10650,7 +10736,7 @@
         <v>422</v>
       </c>
       <c r="M36" s="37" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="N36" s="36" t="s">
         <v>1</v>
@@ -10697,10 +10783,10 @@
         <v>231</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>523</v>
+        <v>490</v>
       </c>
       <c r="D37" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E37" s="65" t="s">
         <v>371</v>
@@ -10727,7 +10813,7 @@
         <v>422</v>
       </c>
       <c r="M37" s="37" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="N37" s="36" t="s">
         <v>1</v>
@@ -10774,10 +10860,10 @@
         <v>232</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>523</v>
+        <v>490</v>
       </c>
       <c r="D38" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E38" s="65" t="s">
         <v>371</v>
@@ -10804,7 +10890,7 @@
         <v>422</v>
       </c>
       <c r="M38" s="37" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="N38" s="36" t="s">
         <v>1</v>
@@ -10851,10 +10937,10 @@
         <v>233</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>523</v>
+        <v>490</v>
       </c>
       <c r="D39" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E39" s="65" t="s">
         <v>371</v>
@@ -10881,7 +10967,7 @@
         <v>422</v>
       </c>
       <c r="M39" s="37" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="N39" s="36" t="s">
         <v>1</v>
@@ -10928,10 +11014,10 @@
         <v>234</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>523</v>
+        <v>490</v>
       </c>
       <c r="D40" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E40" s="65" t="s">
         <v>371</v>
@@ -10958,7 +11044,7 @@
         <v>422</v>
       </c>
       <c r="M40" s="37" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="N40" s="36" t="s">
         <v>1</v>
@@ -11005,10 +11091,10 @@
         <v>235</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>523</v>
+        <v>490</v>
       </c>
       <c r="D41" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E41" s="65" t="s">
         <v>371</v>
@@ -11035,7 +11121,7 @@
         <v>422</v>
       </c>
       <c r="M41" s="37" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="N41" s="36" t="s">
         <v>1</v>
@@ -11082,10 +11168,10 @@
         <v>236</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>523</v>
+        <v>490</v>
       </c>
       <c r="D42" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E42" s="65" t="s">
         <v>371</v>
@@ -11112,7 +11198,7 @@
         <v>422</v>
       </c>
       <c r="M42" s="37" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="N42" s="36" t="s">
         <v>1</v>
@@ -11159,10 +11245,10 @@
         <v>237</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>523</v>
+        <v>490</v>
       </c>
       <c r="D43" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E43" s="65" t="s">
         <v>371</v>
@@ -11189,7 +11275,7 @@
         <v>422</v>
       </c>
       <c r="M43" s="37" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="N43" s="36" t="s">
         <v>1</v>
@@ -11236,10 +11322,10 @@
         <v>238</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>523</v>
+        <v>490</v>
       </c>
       <c r="D44" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E44" s="65" t="s">
         <v>371</v>
@@ -11266,7 +11352,7 @@
         <v>422</v>
       </c>
       <c r="M44" s="37" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="N44" s="36" t="s">
         <v>1</v>
@@ -11313,10 +11399,10 @@
         <v>239</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>523</v>
+        <v>490</v>
       </c>
       <c r="D45" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E45" s="65" t="s">
         <v>371</v>
@@ -11343,7 +11429,7 @@
         <v>422</v>
       </c>
       <c r="M45" s="37" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="N45" s="36" t="s">
         <v>1</v>
@@ -11390,10 +11476,10 @@
         <v>240</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>523</v>
+        <v>490</v>
       </c>
       <c r="D46" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E46" s="65" t="s">
         <v>371</v>
@@ -11420,7 +11506,7 @@
         <v>422</v>
       </c>
       <c r="M46" s="37" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="N46" s="36" t="s">
         <v>1</v>
@@ -11467,10 +11553,10 @@
         <v>241</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>523</v>
+        <v>490</v>
       </c>
       <c r="D47" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E47" s="65" t="s">
         <v>371</v>
@@ -11497,7 +11583,7 @@
         <v>422</v>
       </c>
       <c r="M47" s="37" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="N47" s="36" t="s">
         <v>1</v>
@@ -11544,10 +11630,10 @@
         <v>242</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>523</v>
+        <v>490</v>
       </c>
       <c r="D48" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E48" s="65" t="s">
         <v>371</v>
@@ -11574,7 +11660,7 @@
         <v>422</v>
       </c>
       <c r="M48" s="37" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="N48" s="36" t="s">
         <v>1</v>
@@ -11621,10 +11707,10 @@
         <v>243</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>523</v>
+        <v>490</v>
       </c>
       <c r="D49" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E49" s="65" t="s">
         <v>371</v>
@@ -11651,7 +11737,7 @@
         <v>422</v>
       </c>
       <c r="M49" s="37" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="N49" s="36" t="s">
         <v>1</v>
@@ -11698,10 +11784,10 @@
         <v>244</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>523</v>
+        <v>490</v>
       </c>
       <c r="D50" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E50" s="65" t="s">
         <v>371</v>
@@ -11728,7 +11814,7 @@
         <v>422</v>
       </c>
       <c r="M50" s="37" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="N50" s="36" t="s">
         <v>1</v>
@@ -11775,10 +11861,10 @@
         <v>245</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>523</v>
+        <v>490</v>
       </c>
       <c r="D51" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E51" s="65" t="s">
         <v>371</v>
@@ -11805,7 +11891,7 @@
         <v>422</v>
       </c>
       <c r="M51" s="37" t="s">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="N51" s="36" t="s">
         <v>1</v>
@@ -11852,10 +11938,10 @@
         <v>246</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>544</v>
+        <v>511</v>
       </c>
       <c r="D52" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E52" s="65" t="s">
         <v>371</v>
@@ -11929,10 +12015,10 @@
         <v>247</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>544</v>
+        <v>511</v>
       </c>
       <c r="D53" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E53" s="65" t="s">
         <v>371</v>
@@ -12006,10 +12092,10 @@
         <v>248</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>544</v>
+        <v>511</v>
       </c>
       <c r="D54" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E54" s="65" t="s">
         <v>371</v>
@@ -12083,10 +12169,10 @@
         <v>249</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>544</v>
+        <v>511</v>
       </c>
       <c r="D55" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E55" s="65" t="s">
         <v>371</v>
@@ -12160,10 +12246,10 @@
         <v>250</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>544</v>
+        <v>511</v>
       </c>
       <c r="D56" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E56" s="65" t="s">
         <v>371</v>
@@ -12237,10 +12323,10 @@
         <v>251</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>544</v>
+        <v>511</v>
       </c>
       <c r="D57" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E57" s="65" t="s">
         <v>371</v>
@@ -12314,10 +12400,10 @@
         <v>252</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>544</v>
+        <v>511</v>
       </c>
       <c r="D58" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E58" s="65" t="s">
         <v>371</v>
@@ -12391,10 +12477,10 @@
         <v>253</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>544</v>
+        <v>511</v>
       </c>
       <c r="D59" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E59" s="65" t="s">
         <v>371</v>
@@ -12468,10 +12554,10 @@
         <v>254</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>544</v>
+        <v>511</v>
       </c>
       <c r="D60" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E60" s="65" t="s">
         <v>371</v>
@@ -12545,10 +12631,10 @@
         <v>255</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>544</v>
+        <v>511</v>
       </c>
       <c r="D61" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E61" s="65" t="s">
         <v>371</v>
@@ -12622,10 +12708,10 @@
         <v>256</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>544</v>
+        <v>511</v>
       </c>
       <c r="D62" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E62" s="65" t="s">
         <v>371</v>
@@ -12699,10 +12785,10 @@
         <v>257</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>544</v>
+        <v>511</v>
       </c>
       <c r="D63" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E63" s="65" t="s">
         <v>371</v>
@@ -12776,10 +12862,10 @@
         <v>258</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>544</v>
+        <v>511</v>
       </c>
       <c r="D64" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E64" s="65" t="s">
         <v>371</v>
@@ -12853,10 +12939,10 @@
         <v>259</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>544</v>
+        <v>511</v>
       </c>
       <c r="D65" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E65" s="65" t="s">
         <v>371</v>
@@ -12930,10 +13016,10 @@
         <v>260</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>544</v>
+        <v>511</v>
       </c>
       <c r="D66" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E66" s="65" t="s">
         <v>371</v>
@@ -13007,10 +13093,10 @@
         <v>261</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>544</v>
+        <v>511</v>
       </c>
       <c r="D67" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E67" s="65" t="s">
         <v>371</v>
@@ -13084,10 +13170,10 @@
         <v>262</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>544</v>
+        <v>511</v>
       </c>
       <c r="D68" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E68" s="65" t="s">
         <v>371</v>
@@ -13161,10 +13247,10 @@
         <v>263</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>544</v>
+        <v>511</v>
       </c>
       <c r="D69" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E69" s="65" t="s">
         <v>371</v>
@@ -13238,10 +13324,10 @@
         <v>264</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>544</v>
+        <v>511</v>
       </c>
       <c r="D70" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E70" s="65" t="s">
         <v>371</v>
@@ -13315,10 +13401,10 @@
         <v>265</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>544</v>
+        <v>511</v>
       </c>
       <c r="D71" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E71" s="65" t="s">
         <v>371</v>
@@ -13392,10 +13478,10 @@
         <v>266</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>544</v>
+        <v>511</v>
       </c>
       <c r="D72" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E72" s="65" t="s">
         <v>371</v>
@@ -13469,10 +13555,10 @@
         <v>267</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>544</v>
+        <v>511</v>
       </c>
       <c r="D73" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E73" s="65" t="s">
         <v>371</v>
@@ -13546,10 +13632,10 @@
         <v>268</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>544</v>
+        <v>511</v>
       </c>
       <c r="D74" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E74" s="65" t="s">
         <v>371</v>
@@ -13623,10 +13709,10 @@
         <v>269</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>544</v>
+        <v>511</v>
       </c>
       <c r="D75" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E75" s="65" t="s">
         <v>371</v>
@@ -13700,10 +13786,10 @@
         <v>270</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>544</v>
+        <v>511</v>
       </c>
       <c r="D76" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E76" s="65" t="s">
         <v>371</v>
@@ -13777,10 +13863,10 @@
         <v>271</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>544</v>
+        <v>511</v>
       </c>
       <c r="D77" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E77" s="65" t="s">
         <v>371</v>
@@ -13854,10 +13940,10 @@
         <v>272</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>544</v>
+        <v>511</v>
       </c>
       <c r="D78" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E78" s="65" t="s">
         <v>371</v>
@@ -13931,10 +14017,10 @@
         <v>273</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>545</v>
+        <v>512</v>
       </c>
       <c r="D79" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E79" s="65" t="s">
         <v>371</v>
@@ -13961,7 +14047,7 @@
         <v>422</v>
       </c>
       <c r="M79" s="37" t="s">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="N79" s="36" t="s">
         <v>1</v>
@@ -14008,10 +14094,10 @@
         <v>274</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>545</v>
+        <v>512</v>
       </c>
       <c r="D80" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E80" s="65" t="s">
         <v>371</v>
@@ -14038,7 +14124,7 @@
         <v>422</v>
       </c>
       <c r="M80" s="37" t="s">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="N80" s="36" t="s">
         <v>1</v>
@@ -14085,10 +14171,10 @@
         <v>275</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>545</v>
+        <v>512</v>
       </c>
       <c r="D81" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E81" s="65" t="s">
         <v>371</v>
@@ -14115,7 +14201,7 @@
         <v>422</v>
       </c>
       <c r="M81" s="37" t="s">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="N81" s="36" t="s">
         <v>1</v>
@@ -14162,10 +14248,10 @@
         <v>276</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>545</v>
+        <v>512</v>
       </c>
       <c r="D82" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E82" s="65" t="s">
         <v>371</v>
@@ -14192,7 +14278,7 @@
         <v>422</v>
       </c>
       <c r="M82" s="37" t="s">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="N82" s="36" t="s">
         <v>1</v>
@@ -14239,10 +14325,10 @@
         <v>277</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>545</v>
+        <v>512</v>
       </c>
       <c r="D83" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E83" s="65" t="s">
         <v>371</v>
@@ -14269,7 +14355,7 @@
         <v>422</v>
       </c>
       <c r="M83" s="37" t="s">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="N83" s="36" t="s">
         <v>1</v>
@@ -14316,10 +14402,10 @@
         <v>278</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>545</v>
+        <v>512</v>
       </c>
       <c r="D84" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E84" s="65" t="s">
         <v>371</v>
@@ -14346,7 +14432,7 @@
         <v>422</v>
       </c>
       <c r="M84" s="37" t="s">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="N84" s="36" t="s">
         <v>1</v>
@@ -14393,10 +14479,10 @@
         <v>279</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>545</v>
+        <v>512</v>
       </c>
       <c r="D85" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E85" s="65" t="s">
         <v>371</v>
@@ -14423,7 +14509,7 @@
         <v>422</v>
       </c>
       <c r="M85" s="37" t="s">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="N85" s="36" t="s">
         <v>1</v>
@@ -14470,10 +14556,10 @@
         <v>280</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>545</v>
+        <v>512</v>
       </c>
       <c r="D86" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E86" s="65" t="s">
         <v>371</v>
@@ -14500,7 +14586,7 @@
         <v>422</v>
       </c>
       <c r="M86" s="37" t="s">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="N86" s="36" t="s">
         <v>1</v>
@@ -14547,10 +14633,10 @@
         <v>281</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>545</v>
+        <v>512</v>
       </c>
       <c r="D87" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E87" s="65" t="s">
         <v>371</v>
@@ -14577,7 +14663,7 @@
         <v>422</v>
       </c>
       <c r="M87" s="37" t="s">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="N87" s="36" t="s">
         <v>1</v>
@@ -14624,10 +14710,10 @@
         <v>282</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>545</v>
+        <v>512</v>
       </c>
       <c r="D88" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E88" s="65" t="s">
         <v>371</v>
@@ -14654,7 +14740,7 @@
         <v>422</v>
       </c>
       <c r="M88" s="37" t="s">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="N88" s="36" t="s">
         <v>1</v>
@@ -14701,10 +14787,10 @@
         <v>283</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>545</v>
+        <v>512</v>
       </c>
       <c r="D89" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E89" s="65" t="s">
         <v>371</v>
@@ -14731,7 +14817,7 @@
         <v>422</v>
       </c>
       <c r="M89" s="37" t="s">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="N89" s="36" t="s">
         <v>1</v>
@@ -14778,10 +14864,10 @@
         <v>284</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>545</v>
+        <v>512</v>
       </c>
       <c r="D90" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E90" s="65" t="s">
         <v>371</v>
@@ -14808,7 +14894,7 @@
         <v>422</v>
       </c>
       <c r="M90" s="37" t="s">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="N90" s="36" t="s">
         <v>1</v>
@@ -14855,10 +14941,10 @@
         <v>285</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>545</v>
+        <v>512</v>
       </c>
       <c r="D91" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E91" s="65" t="s">
         <v>371</v>
@@ -14885,7 +14971,7 @@
         <v>422</v>
       </c>
       <c r="M91" s="37" t="s">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="N91" s="36" t="s">
         <v>1</v>
@@ -14932,10 +15018,10 @@
         <v>286</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>545</v>
+        <v>512</v>
       </c>
       <c r="D92" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E92" s="65" t="s">
         <v>371</v>
@@ -14962,7 +15048,7 @@
         <v>422</v>
       </c>
       <c r="M92" s="37" t="s">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="N92" s="36" t="s">
         <v>1</v>
@@ -15009,10 +15095,10 @@
         <v>287</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>545</v>
+        <v>512</v>
       </c>
       <c r="D93" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E93" s="65" t="s">
         <v>371</v>
@@ -15039,7 +15125,7 @@
         <v>422</v>
       </c>
       <c r="M93" s="37" t="s">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="N93" s="36" t="s">
         <v>1</v>
@@ -15086,10 +15172,10 @@
         <v>288</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>545</v>
+        <v>512</v>
       </c>
       <c r="D94" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E94" s="65" t="s">
         <v>371</v>
@@ -15116,7 +15202,7 @@
         <v>422</v>
       </c>
       <c r="M94" s="37" t="s">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="N94" s="36" t="s">
         <v>1</v>
@@ -15163,10 +15249,10 @@
         <v>289</v>
       </c>
       <c r="C95" s="12" t="s">
-        <v>545</v>
+        <v>512</v>
       </c>
       <c r="D95" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E95" s="65" t="s">
         <v>371</v>
@@ -15193,7 +15279,7 @@
         <v>422</v>
       </c>
       <c r="M95" s="37" t="s">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="N95" s="36" t="s">
         <v>1</v>
@@ -15240,10 +15326,10 @@
         <v>290</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>524</v>
+        <v>491</v>
       </c>
       <c r="D96" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E96" s="65" t="s">
         <v>371</v>
@@ -15270,7 +15356,7 @@
         <v>422</v>
       </c>
       <c r="M96" s="37" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="N96" s="36" t="s">
         <v>1</v>
@@ -15317,10 +15403,10 @@
         <v>291</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>524</v>
+        <v>491</v>
       </c>
       <c r="D97" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E97" s="65" t="s">
         <v>371</v>
@@ -15347,7 +15433,7 @@
         <v>422</v>
       </c>
       <c r="M97" s="37" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="N97" s="36" t="s">
         <v>1</v>
@@ -15394,10 +15480,10 @@
         <v>292</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>524</v>
+        <v>491</v>
       </c>
       <c r="D98" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E98" s="65" t="s">
         <v>371</v>
@@ -15424,7 +15510,7 @@
         <v>422</v>
       </c>
       <c r="M98" s="37" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="N98" s="36" t="s">
         <v>1</v>
@@ -15471,10 +15557,10 @@
         <v>293</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>524</v>
+        <v>491</v>
       </c>
       <c r="D99" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E99" s="65" t="s">
         <v>371</v>
@@ -15501,7 +15587,7 @@
         <v>422</v>
       </c>
       <c r="M99" s="37" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="N99" s="36" t="s">
         <v>1</v>
@@ -15548,10 +15634,10 @@
         <v>294</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>524</v>
+        <v>491</v>
       </c>
       <c r="D100" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E100" s="65" t="s">
         <v>371</v>
@@ -15578,7 +15664,7 @@
         <v>422</v>
       </c>
       <c r="M100" s="37" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="N100" s="36" t="s">
         <v>1</v>
@@ -15625,10 +15711,10 @@
         <v>295</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>524</v>
+        <v>491</v>
       </c>
       <c r="D101" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E101" s="65" t="s">
         <v>371</v>
@@ -15655,7 +15741,7 @@
         <v>422</v>
       </c>
       <c r="M101" s="37" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="N101" s="36" t="s">
         <v>1</v>
@@ -15702,10 +15788,10 @@
         <v>296</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>524</v>
+        <v>491</v>
       </c>
       <c r="D102" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E102" s="65" t="s">
         <v>371</v>
@@ -15732,7 +15818,7 @@
         <v>422</v>
       </c>
       <c r="M102" s="37" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="N102" s="36" t="s">
         <v>1</v>
@@ -15779,10 +15865,10 @@
         <v>297</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>524</v>
+        <v>491</v>
       </c>
       <c r="D103" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E103" s="65" t="s">
         <v>371</v>
@@ -15809,7 +15895,7 @@
         <v>422</v>
       </c>
       <c r="M103" s="37" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="N103" s="36" t="s">
         <v>1</v>
@@ -15856,10 +15942,10 @@
         <v>298</v>
       </c>
       <c r="C104" s="12" t="s">
-        <v>524</v>
+        <v>491</v>
       </c>
       <c r="D104" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E104" s="65" t="s">
         <v>371</v>
@@ -15886,7 +15972,7 @@
         <v>422</v>
       </c>
       <c r="M104" s="37" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="N104" s="36" t="s">
         <v>1</v>
@@ -15933,10 +16019,10 @@
         <v>299</v>
       </c>
       <c r="C105" s="12" t="s">
-        <v>524</v>
+        <v>491</v>
       </c>
       <c r="D105" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E105" s="65" t="s">
         <v>371</v>
@@ -15963,7 +16049,7 @@
         <v>422</v>
       </c>
       <c r="M105" s="37" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="N105" s="36" t="s">
         <v>1</v>
@@ -16010,10 +16096,10 @@
         <v>300</v>
       </c>
       <c r="C106" s="12" t="s">
-        <v>524</v>
+        <v>491</v>
       </c>
       <c r="D106" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E106" s="65" t="s">
         <v>371</v>
@@ -16040,7 +16126,7 @@
         <v>422</v>
       </c>
       <c r="M106" s="37" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="N106" s="36" t="s">
         <v>1</v>
@@ -16087,10 +16173,10 @@
         <v>301</v>
       </c>
       <c r="C107" s="12" t="s">
-        <v>524</v>
+        <v>491</v>
       </c>
       <c r="D107" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E107" s="65" t="s">
         <v>371</v>
@@ -16117,7 +16203,7 @@
         <v>422</v>
       </c>
       <c r="M107" s="37" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="N107" s="36" t="s">
         <v>1</v>
@@ -16164,10 +16250,10 @@
         <v>302</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>524</v>
+        <v>491</v>
       </c>
       <c r="D108" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E108" s="65" t="s">
         <v>371</v>
@@ -16194,7 +16280,7 @@
         <v>422</v>
       </c>
       <c r="M108" s="37" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="N108" s="36" t="s">
         <v>1</v>
@@ -16241,10 +16327,10 @@
         <v>303</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>524</v>
+        <v>491</v>
       </c>
       <c r="D109" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E109" s="65" t="s">
         <v>371</v>
@@ -16271,7 +16357,7 @@
         <v>422</v>
       </c>
       <c r="M109" s="37" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="N109" s="36" t="s">
         <v>1</v>
@@ -16318,10 +16404,10 @@
         <v>304</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>524</v>
+        <v>491</v>
       </c>
       <c r="D110" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E110" s="65" t="s">
         <v>371</v>
@@ -16348,7 +16434,7 @@
         <v>422</v>
       </c>
       <c r="M110" s="37" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="N110" s="36" t="s">
         <v>1</v>
@@ -16395,10 +16481,10 @@
         <v>305</v>
       </c>
       <c r="C111" s="12" t="s">
-        <v>524</v>
+        <v>491</v>
       </c>
       <c r="D111" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E111" s="65" t="s">
         <v>371</v>
@@ -16425,7 +16511,7 @@
         <v>422</v>
       </c>
       <c r="M111" s="37" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="N111" s="36" t="s">
         <v>1</v>
@@ -16472,10 +16558,10 @@
         <v>306</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>524</v>
+        <v>491</v>
       </c>
       <c r="D112" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E112" s="65" t="s">
         <v>371</v>
@@ -16502,7 +16588,7 @@
         <v>422</v>
       </c>
       <c r="M112" s="37" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="N112" s="36" t="s">
         <v>1</v>
@@ -16549,10 +16635,10 @@
         <v>307</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>524</v>
+        <v>491</v>
       </c>
       <c r="D113" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E113" s="65" t="s">
         <v>371</v>
@@ -16579,7 +16665,7 @@
         <v>422</v>
       </c>
       <c r="M113" s="37" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="N113" s="36" t="s">
         <v>1</v>
@@ -16626,10 +16712,10 @@
         <v>308</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>524</v>
+        <v>491</v>
       </c>
       <c r="D114" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E114" s="65" t="s">
         <v>371</v>
@@ -16656,7 +16742,7 @@
         <v>422</v>
       </c>
       <c r="M114" s="37" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="N114" s="36" t="s">
         <v>1</v>
@@ -16703,10 +16789,10 @@
         <v>309</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>524</v>
+        <v>491</v>
       </c>
       <c r="D115" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E115" s="65" t="s">
         <v>371</v>
@@ -16733,7 +16819,7 @@
         <v>422</v>
       </c>
       <c r="M115" s="37" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="N115" s="36" t="s">
         <v>1</v>
@@ -16780,10 +16866,10 @@
         <v>310</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>524</v>
+        <v>491</v>
       </c>
       <c r="D116" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E116" s="65" t="s">
         <v>371</v>
@@ -16810,7 +16896,7 @@
         <v>422</v>
       </c>
       <c r="M116" s="37" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="N116" s="36" t="s">
         <v>1</v>
@@ -16857,10 +16943,10 @@
         <v>311</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>524</v>
+        <v>491</v>
       </c>
       <c r="D117" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E117" s="65" t="s">
         <v>371</v>
@@ -16887,7 +16973,7 @@
         <v>422</v>
       </c>
       <c r="M117" s="37" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="N117" s="36" t="s">
         <v>1</v>
@@ -16934,10 +17020,10 @@
         <v>312</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>524</v>
+        <v>491</v>
       </c>
       <c r="D118" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E118" s="65" t="s">
         <v>371</v>
@@ -16964,7 +17050,7 @@
         <v>422</v>
       </c>
       <c r="M118" s="37" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="N118" s="36" t="s">
         <v>1</v>
@@ -17011,10 +17097,10 @@
         <v>313</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>524</v>
+        <v>491</v>
       </c>
       <c r="D119" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E119" s="65" t="s">
         <v>371</v>
@@ -17041,7 +17127,7 @@
         <v>422</v>
       </c>
       <c r="M119" s="37" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="N119" s="36" t="s">
         <v>1</v>
@@ -17088,10 +17174,10 @@
         <v>314</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>524</v>
+        <v>491</v>
       </c>
       <c r="D120" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E120" s="65" t="s">
         <v>371</v>
@@ -17118,7 +17204,7 @@
         <v>422</v>
       </c>
       <c r="M120" s="37" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="N120" s="36" t="s">
         <v>1</v>
@@ -17165,10 +17251,10 @@
         <v>315</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>524</v>
+        <v>491</v>
       </c>
       <c r="D121" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E121" s="65" t="s">
         <v>371</v>
@@ -17195,7 +17281,7 @@
         <v>422</v>
       </c>
       <c r="M121" s="37" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="N121" s="36" t="s">
         <v>1</v>
@@ -17242,10 +17328,10 @@
         <v>316</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>524</v>
+        <v>491</v>
       </c>
       <c r="D122" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E122" s="65" t="s">
         <v>371</v>
@@ -17272,7 +17358,7 @@
         <v>422</v>
       </c>
       <c r="M122" s="37" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="N122" s="36" t="s">
         <v>1</v>
@@ -17319,10 +17405,10 @@
         <v>317</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>524</v>
+        <v>491</v>
       </c>
       <c r="D123" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E123" s="65" t="s">
         <v>371</v>
@@ -17349,7 +17435,7 @@
         <v>422</v>
       </c>
       <c r="M123" s="37" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="N123" s="36" t="s">
         <v>1</v>
@@ -17396,10 +17482,10 @@
         <v>318</v>
       </c>
       <c r="C124" s="12" t="s">
-        <v>524</v>
+        <v>491</v>
       </c>
       <c r="D124" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E124" s="65" t="s">
         <v>371</v>
@@ -17426,7 +17512,7 @@
         <v>422</v>
       </c>
       <c r="M124" s="37" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="N124" s="36" t="s">
         <v>1</v>
@@ -17473,10 +17559,10 @@
         <v>319</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>524</v>
+        <v>491</v>
       </c>
       <c r="D125" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E125" s="65" t="s">
         <v>371</v>
@@ -17503,7 +17589,7 @@
         <v>422</v>
       </c>
       <c r="M125" s="37" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="N125" s="36" t="s">
         <v>1</v>
@@ -17550,10 +17636,10 @@
         <v>320</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>524</v>
+        <v>491</v>
       </c>
       <c r="D126" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E126" s="65" t="s">
         <v>371</v>
@@ -17580,7 +17666,7 @@
         <v>422</v>
       </c>
       <c r="M126" s="37" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="N126" s="36" t="s">
         <v>1</v>
@@ -17627,10 +17713,10 @@
         <v>321</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>524</v>
+        <v>491</v>
       </c>
       <c r="D127" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E127" s="65" t="s">
         <v>371</v>
@@ -17657,7 +17743,7 @@
         <v>422</v>
       </c>
       <c r="M127" s="37" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="N127" s="36" t="s">
         <v>1</v>
@@ -17704,10 +17790,10 @@
         <v>322</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>524</v>
+        <v>491</v>
       </c>
       <c r="D128" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E128" s="65" t="s">
         <v>371</v>
@@ -17734,7 +17820,7 @@
         <v>422</v>
       </c>
       <c r="M128" s="37" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="N128" s="36" t="s">
         <v>1</v>
@@ -17781,10 +17867,10 @@
         <v>323</v>
       </c>
       <c r="C129" s="12" t="s">
-        <v>524</v>
+        <v>491</v>
       </c>
       <c r="D129" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E129" s="65" t="s">
         <v>371</v>
@@ -17811,7 +17897,7 @@
         <v>422</v>
       </c>
       <c r="M129" s="37" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="N129" s="36" t="s">
         <v>1</v>
@@ -17858,10 +17944,10 @@
         <v>324</v>
       </c>
       <c r="C130" s="12" t="s">
-        <v>524</v>
+        <v>491</v>
       </c>
       <c r="D130" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E130" s="65" t="s">
         <v>371</v>
@@ -17888,7 +17974,7 @@
         <v>422</v>
       </c>
       <c r="M130" s="37" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="N130" s="36" t="s">
         <v>1</v>
@@ -17935,10 +18021,10 @@
         <v>325</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>524</v>
+        <v>491</v>
       </c>
       <c r="D131" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E131" s="65" t="s">
         <v>371</v>
@@ -17965,7 +18051,7 @@
         <v>422</v>
       </c>
       <c r="M131" s="37" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="N131" s="36" t="s">
         <v>1</v>
@@ -18012,10 +18098,10 @@
         <v>326</v>
       </c>
       <c r="C132" s="12" t="s">
-        <v>524</v>
+        <v>491</v>
       </c>
       <c r="D132" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E132" s="65" t="s">
         <v>371</v>
@@ -18042,7 +18128,7 @@
         <v>422</v>
       </c>
       <c r="M132" s="37" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="N132" s="36" t="s">
         <v>1</v>
@@ -18089,10 +18175,10 @@
         <v>327</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>524</v>
+        <v>491</v>
       </c>
       <c r="D133" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E133" s="65" t="s">
         <v>371</v>
@@ -18119,7 +18205,7 @@
         <v>422</v>
       </c>
       <c r="M133" s="37" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="N133" s="36" t="s">
         <v>1</v>
@@ -18166,10 +18252,10 @@
         <v>328</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>524</v>
+        <v>491</v>
       </c>
       <c r="D134" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E134" s="65" t="s">
         <v>371</v>
@@ -18196,7 +18282,7 @@
         <v>422</v>
       </c>
       <c r="M134" s="37" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="N134" s="36" t="s">
         <v>1</v>
@@ -18243,10 +18329,10 @@
         <v>329</v>
       </c>
       <c r="C135" s="12" t="s">
-        <v>524</v>
+        <v>491</v>
       </c>
       <c r="D135" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E135" s="65" t="s">
         <v>371</v>
@@ -18273,7 +18359,7 @@
         <v>422</v>
       </c>
       <c r="M135" s="37" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="N135" s="36" t="s">
         <v>1</v>
@@ -18320,10 +18406,10 @@
         <v>330</v>
       </c>
       <c r="C136" s="12" t="s">
-        <v>524</v>
+        <v>491</v>
       </c>
       <c r="D136" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E136" s="65" t="s">
         <v>371</v>
@@ -18350,7 +18436,7 @@
         <v>422</v>
       </c>
       <c r="M136" s="37" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="N136" s="36" t="s">
         <v>1</v>
@@ -18397,10 +18483,10 @@
         <v>331</v>
       </c>
       <c r="C137" s="12" t="s">
-        <v>524</v>
+        <v>491</v>
       </c>
       <c r="D137" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E137" s="65" t="s">
         <v>371</v>
@@ -18427,7 +18513,7 @@
         <v>422</v>
       </c>
       <c r="M137" s="37" t="s">
-        <v>501</v>
+        <v>468</v>
       </c>
       <c r="N137" s="36" t="s">
         <v>1</v>
@@ -18474,10 +18560,10 @@
         <v>332</v>
       </c>
       <c r="C138" s="12" t="s">
-        <v>525</v>
+        <v>492</v>
       </c>
       <c r="D138" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E138" s="65" t="s">
         <v>371</v>
@@ -18504,7 +18590,7 @@
         <v>422</v>
       </c>
       <c r="M138" s="37" t="s">
-        <v>500</v>
+        <v>467</v>
       </c>
       <c r="N138" s="36" t="s">
         <v>1</v>
@@ -18551,10 +18637,10 @@
         <v>333</v>
       </c>
       <c r="C139" s="12" t="s">
-        <v>525</v>
+        <v>492</v>
       </c>
       <c r="D139" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E139" s="65" t="s">
         <v>371</v>
@@ -18581,7 +18667,7 @@
         <v>422</v>
       </c>
       <c r="M139" s="37" t="s">
-        <v>500</v>
+        <v>467</v>
       </c>
       <c r="N139" s="36" t="s">
         <v>1</v>
@@ -18628,10 +18714,10 @@
         <v>334</v>
       </c>
       <c r="C140" s="12" t="s">
-        <v>525</v>
+        <v>492</v>
       </c>
       <c r="D140" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E140" s="65" t="s">
         <v>371</v>
@@ -18658,7 +18744,7 @@
         <v>422</v>
       </c>
       <c r="M140" s="37" t="s">
-        <v>500</v>
+        <v>467</v>
       </c>
       <c r="N140" s="36" t="s">
         <v>1</v>
@@ -18705,10 +18791,10 @@
         <v>335</v>
       </c>
       <c r="C141" s="12" t="s">
-        <v>525</v>
+        <v>492</v>
       </c>
       <c r="D141" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E141" s="65" t="s">
         <v>371</v>
@@ -18735,7 +18821,7 @@
         <v>422</v>
       </c>
       <c r="M141" s="37" t="s">
-        <v>500</v>
+        <v>467</v>
       </c>
       <c r="N141" s="36" t="s">
         <v>1</v>
@@ -18782,10 +18868,10 @@
         <v>336</v>
       </c>
       <c r="C142" s="12" t="s">
-        <v>525</v>
+        <v>492</v>
       </c>
       <c r="D142" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E142" s="65" t="s">
         <v>371</v>
@@ -18812,7 +18898,7 @@
         <v>422</v>
       </c>
       <c r="M142" s="37" t="s">
-        <v>500</v>
+        <v>467</v>
       </c>
       <c r="N142" s="36" t="s">
         <v>1</v>
@@ -18859,10 +18945,10 @@
         <v>337</v>
       </c>
       <c r="C143" s="12" t="s">
-        <v>525</v>
+        <v>492</v>
       </c>
       <c r="D143" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E143" s="65" t="s">
         <v>371</v>
@@ -18889,7 +18975,7 @@
         <v>422</v>
       </c>
       <c r="M143" s="37" t="s">
-        <v>500</v>
+        <v>467</v>
       </c>
       <c r="N143" s="36" t="s">
         <v>1</v>
@@ -18936,10 +19022,10 @@
         <v>338</v>
       </c>
       <c r="C144" s="12" t="s">
-        <v>546</v>
+        <v>513</v>
       </c>
       <c r="D144" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E144" s="65" t="s">
         <v>371</v>
@@ -18966,7 +19052,7 @@
         <v>422</v>
       </c>
       <c r="M144" s="37" t="s">
-        <v>498</v>
+        <v>465</v>
       </c>
       <c r="N144" s="36" t="s">
         <v>1</v>
@@ -19013,10 +19099,10 @@
         <v>339</v>
       </c>
       <c r="C145" s="12" t="s">
-        <v>546</v>
+        <v>513</v>
       </c>
       <c r="D145" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E145" s="65" t="s">
         <v>371</v>
@@ -19043,7 +19129,7 @@
         <v>422</v>
       </c>
       <c r="M145" s="37" t="s">
-        <v>498</v>
+        <v>465</v>
       </c>
       <c r="N145" s="36" t="s">
         <v>1</v>
@@ -19090,10 +19176,10 @@
         <v>340</v>
       </c>
       <c r="C146" s="12" t="s">
-        <v>546</v>
+        <v>513</v>
       </c>
       <c r="D146" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E146" s="65" t="s">
         <v>371</v>
@@ -19120,7 +19206,7 @@
         <v>422</v>
       </c>
       <c r="M146" s="37" t="s">
-        <v>498</v>
+        <v>465</v>
       </c>
       <c r="N146" s="36" t="s">
         <v>1</v>
@@ -19167,10 +19253,10 @@
         <v>341</v>
       </c>
       <c r="C147" s="12" t="s">
-        <v>546</v>
+        <v>513</v>
       </c>
       <c r="D147" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E147" s="65" t="s">
         <v>371</v>
@@ -19197,7 +19283,7 @@
         <v>422</v>
       </c>
       <c r="M147" s="37" t="s">
-        <v>498</v>
+        <v>465</v>
       </c>
       <c r="N147" s="36" t="s">
         <v>1</v>
@@ -19244,10 +19330,10 @@
         <v>342</v>
       </c>
       <c r="C148" s="12" t="s">
-        <v>546</v>
+        <v>513</v>
       </c>
       <c r="D148" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E148" s="65" t="s">
         <v>371</v>
@@ -19274,7 +19360,7 @@
         <v>422</v>
       </c>
       <c r="M148" s="37" t="s">
-        <v>498</v>
+        <v>465</v>
       </c>
       <c r="N148" s="36" t="s">
         <v>1</v>
@@ -19321,10 +19407,10 @@
         <v>343</v>
       </c>
       <c r="C149" s="12" t="s">
-        <v>546</v>
+        <v>513</v>
       </c>
       <c r="D149" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E149" s="65" t="s">
         <v>371</v>
@@ -19351,7 +19437,7 @@
         <v>422</v>
       </c>
       <c r="M149" s="37" t="s">
-        <v>498</v>
+        <v>465</v>
       </c>
       <c r="N149" s="36" t="s">
         <v>1</v>
@@ -19398,10 +19484,10 @@
         <v>344</v>
       </c>
       <c r="C150" s="12" t="s">
-        <v>546</v>
+        <v>513</v>
       </c>
       <c r="D150" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E150" s="65" t="s">
         <v>371</v>
@@ -19428,7 +19514,7 @@
         <v>422</v>
       </c>
       <c r="M150" s="37" t="s">
-        <v>498</v>
+        <v>465</v>
       </c>
       <c r="N150" s="36" t="s">
         <v>1</v>
@@ -19475,10 +19561,10 @@
         <v>345</v>
       </c>
       <c r="C151" s="12" t="s">
-        <v>546</v>
+        <v>513</v>
       </c>
       <c r="D151" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E151" s="65" t="s">
         <v>371</v>
@@ -19505,7 +19591,7 @@
         <v>422</v>
       </c>
       <c r="M151" s="37" t="s">
-        <v>498</v>
+        <v>465</v>
       </c>
       <c r="N151" s="36" t="s">
         <v>1</v>
@@ -19552,10 +19638,10 @@
         <v>346</v>
       </c>
       <c r="C152" s="12" t="s">
-        <v>546</v>
+        <v>513</v>
       </c>
       <c r="D152" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E152" s="65" t="s">
         <v>371</v>
@@ -19582,7 +19668,7 @@
         <v>422</v>
       </c>
       <c r="M152" s="37" t="s">
-        <v>498</v>
+        <v>465</v>
       </c>
       <c r="N152" s="36" t="s">
         <v>1</v>
@@ -19629,10 +19715,10 @@
         <v>347</v>
       </c>
       <c r="C153" s="12" t="s">
-        <v>546</v>
+        <v>513</v>
       </c>
       <c r="D153" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E153" s="65" t="s">
         <v>371</v>
@@ -19659,7 +19745,7 @@
         <v>422</v>
       </c>
       <c r="M153" s="37" t="s">
-        <v>498</v>
+        <v>465</v>
       </c>
       <c r="N153" s="36" t="s">
         <v>1</v>
@@ -19706,10 +19792,10 @@
         <v>348</v>
       </c>
       <c r="C154" s="12" t="s">
-        <v>546</v>
+        <v>513</v>
       </c>
       <c r="D154" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E154" s="65" t="s">
         <v>371</v>
@@ -19736,7 +19822,7 @@
         <v>422</v>
       </c>
       <c r="M154" s="37" t="s">
-        <v>498</v>
+        <v>465</v>
       </c>
       <c r="N154" s="36" t="s">
         <v>1</v>
@@ -19783,10 +19869,10 @@
         <v>349</v>
       </c>
       <c r="C155" s="12" t="s">
-        <v>546</v>
+        <v>513</v>
       </c>
       <c r="D155" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E155" s="65" t="s">
         <v>371</v>
@@ -19813,7 +19899,7 @@
         <v>422</v>
       </c>
       <c r="M155" s="37" t="s">
-        <v>498</v>
+        <v>465</v>
       </c>
       <c r="N155" s="36" t="s">
         <v>1</v>
@@ -19860,10 +19946,10 @@
         <v>350</v>
       </c>
       <c r="C156" s="12" t="s">
-        <v>546</v>
+        <v>513</v>
       </c>
       <c r="D156" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E156" s="65" t="s">
         <v>371</v>
@@ -19890,7 +19976,7 @@
         <v>422</v>
       </c>
       <c r="M156" s="37" t="s">
-        <v>498</v>
+        <v>465</v>
       </c>
       <c r="N156" s="36" t="s">
         <v>1</v>
@@ -19937,10 +20023,10 @@
         <v>351</v>
       </c>
       <c r="C157" s="12" t="s">
-        <v>546</v>
+        <v>513</v>
       </c>
       <c r="D157" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E157" s="65" t="s">
         <v>371</v>
@@ -19967,7 +20053,7 @@
         <v>422</v>
       </c>
       <c r="M157" s="37" t="s">
-        <v>498</v>
+        <v>465</v>
       </c>
       <c r="N157" s="36" t="s">
         <v>1</v>
@@ -20014,10 +20100,10 @@
         <v>352</v>
       </c>
       <c r="C158" s="12" t="s">
-        <v>546</v>
+        <v>513</v>
       </c>
       <c r="D158" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E158" s="65" t="s">
         <v>371</v>
@@ -20044,7 +20130,7 @@
         <v>422</v>
       </c>
       <c r="M158" s="37" t="s">
-        <v>498</v>
+        <v>465</v>
       </c>
       <c r="N158" s="36" t="s">
         <v>1</v>
@@ -20091,10 +20177,10 @@
         <v>353</v>
       </c>
       <c r="C159" s="12" t="s">
-        <v>546</v>
+        <v>513</v>
       </c>
       <c r="D159" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E159" s="65" t="s">
         <v>371</v>
@@ -20121,7 +20207,7 @@
         <v>422</v>
       </c>
       <c r="M159" s="37" t="s">
-        <v>498</v>
+        <v>465</v>
       </c>
       <c r="N159" s="36" t="s">
         <v>1</v>
@@ -20168,10 +20254,10 @@
         <v>354</v>
       </c>
       <c r="C160" s="12" t="s">
-        <v>526</v>
+        <v>493</v>
       </c>
       <c r="D160" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E160" s="65" t="s">
         <v>371</v>
@@ -20198,7 +20284,7 @@
         <v>422</v>
       </c>
       <c r="M160" s="37" t="s">
-        <v>499</v>
+        <v>466</v>
       </c>
       <c r="N160" s="36" t="s">
         <v>1</v>
@@ -20245,10 +20331,10 @@
         <v>355</v>
       </c>
       <c r="C161" s="12" t="s">
-        <v>526</v>
+        <v>493</v>
       </c>
       <c r="D161" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E161" s="65" t="s">
         <v>371</v>
@@ -20275,7 +20361,7 @@
         <v>422</v>
       </c>
       <c r="M161" s="37" t="s">
-        <v>499</v>
+        <v>466</v>
       </c>
       <c r="N161" s="36" t="s">
         <v>1</v>
@@ -20322,10 +20408,10 @@
         <v>356</v>
       </c>
       <c r="C162" s="12" t="s">
-        <v>526</v>
+        <v>493</v>
       </c>
       <c r="D162" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E162" s="65" t="s">
         <v>371</v>
@@ -20352,7 +20438,7 @@
         <v>422</v>
       </c>
       <c r="M162" s="37" t="s">
-        <v>499</v>
+        <v>466</v>
       </c>
       <c r="N162" s="36" t="s">
         <v>1</v>
@@ -20399,10 +20485,10 @@
         <v>357</v>
       </c>
       <c r="C163" s="12" t="s">
-        <v>526</v>
+        <v>493</v>
       </c>
       <c r="D163" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E163" s="65" t="s">
         <v>371</v>
@@ -20429,7 +20515,7 @@
         <v>422</v>
       </c>
       <c r="M163" s="37" t="s">
-        <v>499</v>
+        <v>466</v>
       </c>
       <c r="N163" s="36" t="s">
         <v>1</v>
@@ -20476,10 +20562,10 @@
         <v>358</v>
       </c>
       <c r="C164" s="12" t="s">
-        <v>526</v>
+        <v>493</v>
       </c>
       <c r="D164" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E164" s="65" t="s">
         <v>371</v>
@@ -20506,7 +20592,7 @@
         <v>422</v>
       </c>
       <c r="M164" s="37" t="s">
-        <v>499</v>
+        <v>466</v>
       </c>
       <c r="N164" s="36" t="s">
         <v>1</v>
@@ -20553,10 +20639,10 @@
         <v>359</v>
       </c>
       <c r="C165" s="12" t="s">
-        <v>526</v>
+        <v>493</v>
       </c>
       <c r="D165" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E165" s="65" t="s">
         <v>371</v>
@@ -20583,7 +20669,7 @@
         <v>422</v>
       </c>
       <c r="M165" s="37" t="s">
-        <v>499</v>
+        <v>466</v>
       </c>
       <c r="N165" s="36" t="s">
         <v>1</v>
@@ -20630,10 +20716,10 @@
         <v>360</v>
       </c>
       <c r="C166" s="12" t="s">
-        <v>526</v>
+        <v>493</v>
       </c>
       <c r="D166" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E166" s="65" t="s">
         <v>371</v>
@@ -20660,7 +20746,7 @@
         <v>422</v>
       </c>
       <c r="M166" s="37" t="s">
-        <v>499</v>
+        <v>466</v>
       </c>
       <c r="N166" s="36" t="s">
         <v>1</v>
@@ -20707,10 +20793,10 @@
         <v>361</v>
       </c>
       <c r="C167" s="12" t="s">
-        <v>526</v>
+        <v>493</v>
       </c>
       <c r="D167" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E167" s="65" t="s">
         <v>371</v>
@@ -20737,7 +20823,7 @@
         <v>422</v>
       </c>
       <c r="M167" s="37" t="s">
-        <v>499</v>
+        <v>466</v>
       </c>
       <c r="N167" s="36" t="s">
         <v>1</v>
@@ -20784,10 +20870,10 @@
         <v>362</v>
       </c>
       <c r="C168" s="12" t="s">
-        <v>526</v>
+        <v>493</v>
       </c>
       <c r="D168" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E168" s="65" t="s">
         <v>371</v>
@@ -20814,7 +20900,7 @@
         <v>422</v>
       </c>
       <c r="M168" s="37" t="s">
-        <v>499</v>
+        <v>466</v>
       </c>
       <c r="N168" s="36" t="s">
         <v>1</v>
@@ -20861,10 +20947,10 @@
         <v>363</v>
       </c>
       <c r="C169" s="12" t="s">
-        <v>526</v>
+        <v>493</v>
       </c>
       <c r="D169" s="64" t="s">
-        <v>507</v>
+        <v>474</v>
       </c>
       <c r="E169" s="65" t="s">
         <v>371</v>
@@ -20891,7 +20977,7 @@
         <v>422</v>
       </c>
       <c r="M169" s="37" t="s">
-        <v>499</v>
+        <v>466</v>
       </c>
       <c r="N169" s="40" t="s">
         <v>1</v>
@@ -20933,65 +21019,65 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="12" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1">
-    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="cellIs" dxfId="10" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="13" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1">
-    <cfRule type="cellIs" dxfId="9" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1">
-    <cfRule type="cellIs" dxfId="8" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1">
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="cellIs" dxfId="6" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="17" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P1">
-    <cfRule type="cellIs" dxfId="5" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="9" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="cellIs" dxfId="4" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1">
-    <cfRule type="cellIs" dxfId="3" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1:Y1048576">
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V1">
-    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1">
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_15965_1F.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_1F.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F2E5284-33BA-4DD6-AEAF-39FB5287077D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B45A4C2-1F8D-4344-A2EB-9883020DB383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4649" uniqueCount="567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4688" uniqueCount="593">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -1792,13 +1792,91 @@
   </si>
   <si>
     <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 5I. Building Information Codes.</t>
+  </si>
+  <si>
+    <t>Fonte1</t>
+  </si>
+  <si>
+    <t>https://brasil.un.org/pt-br/sdgs</t>
+  </si>
+  <si>
+    <t>Fonte2</t>
+  </si>
+  <si>
+    <t>https://eaesp.fgv.br/centros/centro-estudos-sustentabilidade/projetos/programa-brasileiro-ghg-protocol</t>
+  </si>
+  <si>
+    <t>Fonte3</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/fazenda/pt-br/acesso-a-informacao/acoes-e-programas/transformacao-ecologica/transformacao-ecologica</t>
+  </si>
+  <si>
+    <t>FonteVegetação1</t>
+  </si>
+  <si>
+    <t>https://museunacional.ufrj.br/hortobotanico</t>
+  </si>
+  <si>
+    <t>FonteVegetação2</t>
+  </si>
+  <si>
+    <t>https://www.embrapa.br/florestas/publicacoes</t>
+  </si>
+  <si>
+    <t>FonteVegetação3</t>
+  </si>
+  <si>
+    <t>https://www.arvoresgigantes.org</t>
+  </si>
+  <si>
+    <t>FonteVegetação4</t>
+  </si>
+  <si>
+    <t>https://www.scielo.br/j/abb</t>
+  </si>
+  <si>
+    <t>FonteVegetação5</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/inpa/pt-br/Pesquisa/colecoes/botanica</t>
+  </si>
+  <si>
+    <t>FonteVegetação6</t>
+  </si>
+  <si>
+    <t>https://botanicasaopaulo.org</t>
+  </si>
+  <si>
+    <t>FonteVegetação7</t>
+  </si>
+  <si>
+    <t>https://pesquisa.in.gov.br/imprensa</t>
+  </si>
+  <si>
+    <t>FonteVegetação8</t>
+  </si>
+  <si>
+    <t>https://mapas.florestal.gov.br</t>
+  </si>
+  <si>
+    <t>FonteTSB</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/fazenda/pt-br/orgaos/spe/taxonomia-sustentavel-brasileira/cadernos</t>
+  </si>
+  <si>
+    <t>FonteSINAPI</t>
+  </si>
+  <si>
+    <t>https://www.caixa.gov.br/site/Paginas/downloads.aspx#categoria_888</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="8"/>
       <color theme="1"/>
@@ -1886,8 +1964,34 @@
       <name val="Arial Nova Cond Light"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="8"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <color theme="10"/>
+      <name val="Arial Nova Cond Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial Nova Cond"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="6"/>
+      <color theme="10"/>
+      <name val="Arial Nova Cond Light"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="27">
+  <fills count="28">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2044,6 +2148,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="7">
     <border>
@@ -2132,11 +2242,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2337,64 +2448,31 @@
     <xf numFmtId="0" fontId="3" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="17" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hiperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{9B49B867-F029-4368-B154-870C7BE57F68}"/>
   </cellStyles>
-  <dxfs count="85">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="80">
     <dxf>
       <font>
         <b val="0"/>
@@ -2524,6 +2602,16 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -4583,33 +4671,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:Y169" headerRowCount="0" totalsRowShown="0" headerRowDxfId="84" headerRowBorderDxfId="83" tableBorderDxfId="82" totalsRowBorderDxfId="81">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:Y169" headerRowCount="0" totalsRowShown="0" headerRowDxfId="79" headerRowBorderDxfId="78" tableBorderDxfId="77" totalsRowBorderDxfId="76">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="80" dataDxfId="79"/>
-    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="78" dataDxfId="77"/>
-    <tableColumn id="26" xr3:uid="{C91353D4-2D80-49C8-8738-A06C8033990C}" name="Coluna21" headerRowDxfId="76" dataDxfId="75"/>
-    <tableColumn id="5" xr3:uid="{AAB64158-D6DA-4E9F-AC47-A0274997AD5C}" name="Coluna8" headerRowDxfId="74" dataDxfId="73"/>
-    <tableColumn id="4" xr3:uid="{9F1772E8-67AD-410D-A17F-F21B8080770D}" name="Coluna7" headerRowDxfId="72" dataDxfId="71"/>
-    <tableColumn id="9" xr3:uid="{9B194C8C-85D6-4BE2-B1AE-E11E335186F0}" name="Coluna6" headerRowDxfId="70" dataDxfId="69"/>
-    <tableColumn id="8" xr3:uid="{6F1A2D13-ED4B-47DE-AFA9-D11431CAA734}" name="Coluna5" headerRowDxfId="68" dataDxfId="67"/>
-    <tableColumn id="15" xr3:uid="{0C0DAD0A-A76E-4555-A1F1-F78A8F1BE2C2}" name="Coluna4" headerRowDxfId="66" dataDxfId="65"/>
-    <tableColumn id="14" xr3:uid="{C073F03F-8B8F-474F-AF29-E26DD9C1B19A}" name="Coluna3" headerRowDxfId="64" dataDxfId="63"/>
-    <tableColumn id="11" xr3:uid="{AE04A63A-3540-4CF3-9D9A-59CD3577B22C}" name="Coluna2" headerRowDxfId="62" dataDxfId="61"/>
-    <tableColumn id="10" xr3:uid="{F50D06F5-DC15-417E-BE0C-A36478AC8A38}" name="Coluna1" headerRowDxfId="60" dataDxfId="59"/>
-    <tableColumn id="25" xr3:uid="{FF2B42B8-007D-4B78-A1E6-70321A25B422}" name="Coluna20" headerRowDxfId="58" dataDxfId="57"/>
-    <tableColumn id="24" xr3:uid="{B0850B61-1B8F-418B-98C0-04AB09902DE3}" name="Coluna19" headerRowDxfId="56" dataDxfId="55"/>
-    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="54" dataDxfId="53"/>
-    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="52" dataDxfId="51"/>
-    <tableColumn id="6" xr3:uid="{8E7C1DDF-1846-4221-9B0E-C7E4CC7EA057}" name="Coluna9" headerRowDxfId="50" dataDxfId="49"/>
-    <tableColumn id="7" xr3:uid="{3D7A485C-E68B-4D3B-888E-DCFC8EAEE60D}" name="Coluna10" headerRowDxfId="48" dataDxfId="47"/>
-    <tableColumn id="16" xr3:uid="{FECF52FB-CC27-4CA6-B622-AF9F7DB3B554}" name="Coluna11" headerRowDxfId="46" dataDxfId="45"/>
-    <tableColumn id="17" xr3:uid="{D79F8B63-2EF5-45DD-9134-450A005B41F4}" name="Coluna12" headerRowDxfId="44" dataDxfId="43"/>
-    <tableColumn id="18" xr3:uid="{DAFF39A1-0FA6-4AF0-A3B6-380882A29861}" name="Coluna13" headerRowDxfId="42" dataDxfId="41"/>
-    <tableColumn id="19" xr3:uid="{87AE1228-C62F-45E2-A7B1-A0914F89FBE3}" name="Coluna14" headerRowDxfId="40" dataDxfId="39"/>
-    <tableColumn id="20" xr3:uid="{85EAA474-6B84-4EF5-95FF-852AF2C5EA5E}" name="Coluna15" headerRowDxfId="38" dataDxfId="37"/>
-    <tableColumn id="21" xr3:uid="{5B15C019-4680-4877-A95B-F683BA0C59DD}" name="Coluna16" headerRowDxfId="36" dataDxfId="35"/>
-    <tableColumn id="22" xr3:uid="{5C11667F-4365-4FD8-A625-69FCEAC4D24C}" name="Coluna17" headerRowDxfId="34" dataDxfId="33"/>
-    <tableColumn id="23" xr3:uid="{38F8B48D-5280-437C-BB95-24A464DAF74A}" name="Coluna18" headerRowDxfId="32" dataDxfId="31"/>
+    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="75" dataDxfId="74"/>
+    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="73" dataDxfId="72"/>
+    <tableColumn id="26" xr3:uid="{C91353D4-2D80-49C8-8738-A06C8033990C}" name="Coluna21" headerRowDxfId="71" dataDxfId="70"/>
+    <tableColumn id="5" xr3:uid="{AAB64158-D6DA-4E9F-AC47-A0274997AD5C}" name="Coluna8" headerRowDxfId="69" dataDxfId="68"/>
+    <tableColumn id="4" xr3:uid="{9F1772E8-67AD-410D-A17F-F21B8080770D}" name="Coluna7" headerRowDxfId="67" dataDxfId="66"/>
+    <tableColumn id="9" xr3:uid="{9B194C8C-85D6-4BE2-B1AE-E11E335186F0}" name="Coluna6" headerRowDxfId="65" dataDxfId="64"/>
+    <tableColumn id="8" xr3:uid="{6F1A2D13-ED4B-47DE-AFA9-D11431CAA734}" name="Coluna5" headerRowDxfId="63" dataDxfId="62"/>
+    <tableColumn id="15" xr3:uid="{0C0DAD0A-A76E-4555-A1F1-F78A8F1BE2C2}" name="Coluna4" headerRowDxfId="61" dataDxfId="60"/>
+    <tableColumn id="14" xr3:uid="{C073F03F-8B8F-474F-AF29-E26DD9C1B19A}" name="Coluna3" headerRowDxfId="59" dataDxfId="58"/>
+    <tableColumn id="11" xr3:uid="{AE04A63A-3540-4CF3-9D9A-59CD3577B22C}" name="Coluna2" headerRowDxfId="57" dataDxfId="56"/>
+    <tableColumn id="10" xr3:uid="{F50D06F5-DC15-417E-BE0C-A36478AC8A38}" name="Coluna1" headerRowDxfId="55" dataDxfId="54"/>
+    <tableColumn id="25" xr3:uid="{FF2B42B8-007D-4B78-A1E6-70321A25B422}" name="Coluna20" headerRowDxfId="53" dataDxfId="52"/>
+    <tableColumn id="24" xr3:uid="{B0850B61-1B8F-418B-98C0-04AB09902DE3}" name="Coluna19" headerRowDxfId="51" dataDxfId="50"/>
+    <tableColumn id="12" xr3:uid="{72731FBF-D3F4-42FD-AF7E-09CD79716DE3}" name="Fato (11)" headerRowDxfId="49" dataDxfId="48"/>
+    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="47" dataDxfId="46"/>
+    <tableColumn id="6" xr3:uid="{8E7C1DDF-1846-4221-9B0E-C7E4CC7EA057}" name="Coluna9" headerRowDxfId="45" dataDxfId="44"/>
+    <tableColumn id="7" xr3:uid="{3D7A485C-E68B-4D3B-888E-DCFC8EAEE60D}" name="Coluna10" headerRowDxfId="43" dataDxfId="42"/>
+    <tableColumn id="16" xr3:uid="{FECF52FB-CC27-4CA6-B622-AF9F7DB3B554}" name="Coluna11" headerRowDxfId="41" dataDxfId="40"/>
+    <tableColumn id="17" xr3:uid="{D79F8B63-2EF5-45DD-9134-450A005B41F4}" name="Coluna12" headerRowDxfId="39" dataDxfId="38"/>
+    <tableColumn id="18" xr3:uid="{DAFF39A1-0FA6-4AF0-A3B6-380882A29861}" name="Coluna13" headerRowDxfId="37" dataDxfId="36"/>
+    <tableColumn id="19" xr3:uid="{87AE1228-C62F-45E2-A7B1-A0914F89FBE3}" name="Coluna14" headerRowDxfId="35" dataDxfId="34"/>
+    <tableColumn id="20" xr3:uid="{85EAA474-6B84-4EF5-95FF-852AF2C5EA5E}" name="Coluna15" headerRowDxfId="33" dataDxfId="32"/>
+    <tableColumn id="21" xr3:uid="{5B15C019-4680-4877-A95B-F683BA0C59DD}" name="Coluna16" headerRowDxfId="31" dataDxfId="30"/>
+    <tableColumn id="22" xr3:uid="{5C11667F-4365-4FD8-A625-69FCEAC4D24C}" name="Coluna17" headerRowDxfId="29" dataDxfId="28"/>
+    <tableColumn id="23" xr3:uid="{38F8B48D-5280-437C-BB95-24A464DAF74A}" name="Coluna18" headerRowDxfId="27" dataDxfId="26"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -4933,7 +5021,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B000FC7-022F-4B0D-BBFB-289DF5E27855}">
   <sheetPr codeName="Planilha1"/>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.69921875" bestFit="1" customWidth="1"/>
@@ -5136,7 +5224,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46232.781241898148</v>
+        <v>46233.478444675929</v>
       </c>
       <c r="C18" s="46" t="s">
         <v>432</v>
@@ -5232,7 +5320,157 @@
         <v>434</v>
       </c>
     </row>
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="43" t="s">
+        <v>567</v>
+      </c>
+      <c r="B27" s="68" t="s">
+        <v>568</v>
+      </c>
+      <c r="C27" s="46" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="43" t="s">
+        <v>569</v>
+      </c>
+      <c r="B28" s="69" t="s">
+        <v>570</v>
+      </c>
+      <c r="C28" s="46" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="43" t="s">
+        <v>571</v>
+      </c>
+      <c r="B29" s="69" t="s">
+        <v>572</v>
+      </c>
+      <c r="C29" s="46" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" s="71" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="43" t="s">
+        <v>573</v>
+      </c>
+      <c r="B30" s="70" t="s">
+        <v>574</v>
+      </c>
+      <c r="C30" s="46" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" s="71" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="43" t="s">
+        <v>575</v>
+      </c>
+      <c r="B31" s="70" t="s">
+        <v>576</v>
+      </c>
+      <c r="C31" s="46" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" s="71" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="43" t="s">
+        <v>577</v>
+      </c>
+      <c r="B32" s="70" t="s">
+        <v>578</v>
+      </c>
+      <c r="C32" s="46" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" s="71" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="43" t="s">
+        <v>579</v>
+      </c>
+      <c r="B33" s="72" t="s">
+        <v>580</v>
+      </c>
+      <c r="C33" s="46" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" s="71" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="43" t="s">
+        <v>581</v>
+      </c>
+      <c r="B34" s="72" t="s">
+        <v>582</v>
+      </c>
+      <c r="C34" s="46" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" s="71" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="43" t="s">
+        <v>583</v>
+      </c>
+      <c r="B35" s="70" t="s">
+        <v>584</v>
+      </c>
+      <c r="C35" s="46" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" s="71" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="43" t="s">
+        <v>585</v>
+      </c>
+      <c r="B36" s="72" t="s">
+        <v>586</v>
+      </c>
+      <c r="C36" s="46" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" s="71" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="43" t="s">
+        <v>587</v>
+      </c>
+      <c r="B37" s="70" t="s">
+        <v>588</v>
+      </c>
+      <c r="C37" s="46" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="B38" s="73" t="s">
+        <v>590</v>
+      </c>
+      <c r="C38" s="46" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" s="75" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="43" t="s">
+        <v>591</v>
+      </c>
+      <c r="B39" s="74" t="s">
+        <v>592</v>
+      </c>
+      <c r="C39" s="46" t="s">
+        <v>432</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B27" r:id="rId1" xr:uid="{94E2545C-B95D-4E22-98A1-AA30974B36CE}"/>
+    <hyperlink ref="B29" r:id="rId2" xr:uid="{E8B4456F-BD7E-4A63-9D52-731D742146F0}"/>
+    <hyperlink ref="B28" r:id="rId3" xr:uid="{9A6614D6-89C0-4316-9281-E6CC91269BA8}"/>
+    <hyperlink ref="B38" r:id="rId4" xr:uid="{B22D1ABD-43E9-47D5-970B-5555FF497D5B}"/>
+    <hyperlink ref="B39" r:id="rId5" location="categoria_888" xr:uid="{9BF7F46A-BE7E-405F-A116-32647CBD6CCA}"/>
+  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
@@ -7028,7 +7266,7 @@
         <v>191</v>
       </c>
       <c r="L20" s="61" t="str">
-        <f t="shared" ref="L18:N27" si="8">CONCATENATE("", C20)</f>
+        <f t="shared" ref="L20:N27" si="8">CONCATENATE("", C20)</f>
         <v>Normativo</v>
       </c>
       <c r="M20" s="61" t="str">
@@ -7040,7 +7278,7 @@
         <v>NBR.Fases</v>
       </c>
       <c r="O20" s="61" t="str">
-        <f t="shared" ref="O7:O27" si="9">F20</f>
+        <f t="shared" ref="O20:O27" si="9">F20</f>
         <v>NBR.F.Programação</v>
       </c>
       <c r="P20" s="42" t="s">
@@ -7054,7 +7292,7 @@
         <v>191</v>
       </c>
       <c r="S20" s="62" t="str">
-        <f t="shared" ref="S7:U22" si="10">SUBSTITUTE(C20, "_", " ")</f>
+        <f t="shared" ref="S20:U22" si="10">SUBSTITUTE(C20, "_", " ")</f>
         <v>Normativo</v>
       </c>
       <c r="T20" s="62" t="str">
@@ -7738,38 +7976,28 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:B6 A20:B27">
-    <cfRule type="cellIs" dxfId="30" priority="7" operator="equal">
+  <conditionalFormatting sqref="A2:B27">
+    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F6">
-    <cfRule type="duplicateValues" dxfId="29" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7:F19">
+    <cfRule type="duplicateValues" dxfId="20" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F20">
-    <cfRule type="duplicateValues" dxfId="25" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="29"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA1:AA6 AA20:AA27">
-    <cfRule type="cellIs" dxfId="21" priority="12" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A7:B19">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7:F19">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA7:AA19">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+  <conditionalFormatting sqref="AA1:AA27">
+    <cfRule type="cellIs" dxfId="15" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7919,7 +8147,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7964,7 +8192,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21019,65 +21247,65 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="18" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1">
-    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="cellIs" dxfId="16" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="13" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1">
-    <cfRule type="cellIs" dxfId="15" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1">
-    <cfRule type="cellIs" dxfId="14" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1">
-    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="cellIs" dxfId="12" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="17" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P1">
-    <cfRule type="cellIs" dxfId="11" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="9" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="cellIs" dxfId="10" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1">
-    <cfRule type="cellIs" dxfId="9" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1:Y1048576">
-    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V1">
-    <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1">
-    <cfRule type="cellIs" dxfId="6" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_15965_1F.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_1F.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B45A4C2-1F8D-4344-A2EB-9883020DB383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37DA5B2A-4067-4C09-ABBF-E002185DB78C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4688" uniqueCount="593">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4688" uniqueCount="592">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -1641,9 +1641,6 @@
     <t>"Fases do ciclo de vida da edificação"</t>
   </si>
   <si>
-    <t>Conceito</t>
-  </si>
-  <si>
     <t>Contêineres</t>
   </si>
   <si>
@@ -1668,21 +1665,12 @@
     <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos de Sistemas Prediais para o Projeto.</t>
   </si>
   <si>
-    <t>Normativo</t>
-  </si>
-  <si>
-    <t>NBR.Temática</t>
-  </si>
-  <si>
     <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 0M. Códigos de Materiais.</t>
   </si>
   <si>
     <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 0M. Códigos de materiales.</t>
   </si>
   <si>
-    <t>Interdiciplinar</t>
-  </si>
-  <si>
     <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 0M. Material Codes.</t>
   </si>
   <si>
@@ -1870,6 +1858,15 @@
   </si>
   <si>
     <t>https://www.caixa.gov.br/site/Paginas/downloads.aspx#categoria_888</t>
+  </si>
+  <si>
+    <t>Conceitos</t>
+  </si>
+  <si>
+    <t>Normativos</t>
+  </si>
+  <si>
+    <t>NBR.Temáticas</t>
   </si>
 </sst>
 </file>
@@ -5224,7 +5221,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46233.478444675929</v>
+        <v>46243.560153009261</v>
       </c>
       <c r="C18" s="46" t="s">
         <v>432</v>
@@ -5322,10 +5319,10 @@
     </row>
     <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="43" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="B27" s="68" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="C27" s="46" t="s">
         <v>432</v>
@@ -5333,10 +5330,10 @@
     </row>
     <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="43" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="B28" s="69" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="C28" s="46" t="s">
         <v>432</v>
@@ -5344,10 +5341,10 @@
     </row>
     <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="43" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="B29" s="69" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="C29" s="46" t="s">
         <v>432</v>
@@ -5355,10 +5352,10 @@
     </row>
     <row r="30" spans="1:3" s="71" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="43" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="B30" s="70" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="C30" s="46" t="s">
         <v>432</v>
@@ -5366,10 +5363,10 @@
     </row>
     <row r="31" spans="1:3" s="71" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="43" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="B31" s="70" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="C31" s="46" t="s">
         <v>432</v>
@@ -5377,10 +5374,10 @@
     </row>
     <row r="32" spans="1:3" s="71" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="43" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="B32" s="70" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="C32" s="46" t="s">
         <v>432</v>
@@ -5388,10 +5385,10 @@
     </row>
     <row r="33" spans="1:3" s="71" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="43" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="B33" s="72" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="C33" s="46" t="s">
         <v>432</v>
@@ -5399,10 +5396,10 @@
     </row>
     <row r="34" spans="1:3" s="71" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="43" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="B34" s="72" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="C34" s="46" t="s">
         <v>432</v>
@@ -5410,10 +5407,10 @@
     </row>
     <row r="35" spans="1:3" s="71" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="43" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="B35" s="70" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="C35" s="46" t="s">
         <v>432</v>
@@ -5421,10 +5418,10 @@
     </row>
     <row r="36" spans="1:3" s="71" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="43" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="B36" s="72" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="C36" s="46" t="s">
         <v>432</v>
@@ -5432,10 +5429,10 @@
     </row>
     <row r="37" spans="1:3" s="71" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="43" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="B37" s="70" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="C37" s="46" t="s">
         <v>432</v>
@@ -5443,10 +5440,10 @@
     </row>
     <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="B38" s="73" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="C38" s="46" t="s">
         <v>432</v>
@@ -5454,10 +5451,10 @@
     </row>
     <row r="39" spans="1:3" s="75" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="43" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="B39" s="74" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="C39" s="46" t="s">
         <v>432</v>
@@ -5484,7 +5481,8 @@
     <col min="1" max="1" width="2.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.796875" style="33" customWidth="1"/>
     <col min="3" max="3" width="7" style="33" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="7.796875" style="33" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="33" customWidth="1"/>
+    <col min="5" max="5" width="7.796875" style="33" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.296875" style="33" customWidth="1"/>
     <col min="7" max="11" width="8.796875" style="33" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7.19921875" bestFit="1" customWidth="1"/>
@@ -5593,7 +5591,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="58" t="s">
-        <v>516</v>
+        <v>589</v>
       </c>
       <c r="C2" s="58" t="s">
         <v>445</v>
@@ -5602,7 +5600,7 @@
         <v>447</v>
       </c>
       <c r="E2" s="59" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="F2" s="59" t="s">
         <v>446</v>
@@ -5639,10 +5637,10 @@
         <v>Contêiner</v>
       </c>
       <c r="P2" s="42" t="s">
+        <v>517</v>
+      </c>
+      <c r="Q2" s="42" t="s">
         <v>518</v>
-      </c>
-      <c r="Q2" s="42" t="s">
-        <v>519</v>
       </c>
       <c r="R2" s="42" t="s">
         <v>191</v>
@@ -5673,7 +5671,7 @@
         <v>191</v>
       </c>
       <c r="Z2" s="42" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AA2" s="42" t="str">
         <f t="shared" ref="AA2:AA6" si="3">_xlfn.TRANSLATE(P2,"pt","en")</f>
@@ -5685,7 +5683,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="58" t="s">
-        <v>516</v>
+        <v>589</v>
       </c>
       <c r="C3" s="58" t="s">
         <v>445</v>
@@ -5694,7 +5692,7 @@
         <v>447</v>
       </c>
       <c r="E3" s="59" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="F3" s="59" t="s">
         <v>449</v>
@@ -5731,10 +5729,10 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="42" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="Q3" s="42" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="R3" s="42" t="s">
         <v>191</v>
@@ -5777,7 +5775,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>516</v>
+        <v>589</v>
       </c>
       <c r="C4" s="58" t="s">
         <v>445</v>
@@ -5786,7 +5784,7 @@
         <v>447</v>
       </c>
       <c r="E4" s="59" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="F4" s="59" t="s">
         <v>450</v>
@@ -5823,10 +5821,10 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="42" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="Q4" s="42" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="R4" s="42" t="s">
         <v>191</v>
@@ -5869,7 +5867,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="58" t="s">
-        <v>516</v>
+        <v>589</v>
       </c>
       <c r="C5" s="58" t="s">
         <v>445</v>
@@ -5878,7 +5876,7 @@
         <v>447</v>
       </c>
       <c r="E5" s="59" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="F5" s="59" t="s">
         <v>451</v>
@@ -5915,10 +5913,10 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="42" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="Q5" s="42" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="R5" s="42" t="s">
         <v>191</v>
@@ -5961,7 +5959,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>516</v>
+        <v>589</v>
       </c>
       <c r="C6" s="58" t="s">
         <v>445</v>
@@ -5970,7 +5968,7 @@
         <v>447</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="F6" s="59" t="s">
         <v>452</v>
@@ -6007,10 +6005,10 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="42" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="Q6" s="42" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="R6" s="42" t="s">
         <v>191</v>
@@ -6053,10 +6051,10 @@
         <v>7</v>
       </c>
       <c r="B7" s="58" t="s">
-        <v>516</v>
+        <v>589</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>525</v>
+        <v>590</v>
       </c>
       <c r="D7" s="32" t="s">
         <v>397</v>
@@ -6084,7 +6082,7 @@
       </c>
       <c r="L7" s="61" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M7" s="61" t="str">
         <f t="shared" si="0"/>
@@ -6099,17 +6097,17 @@
         <v>NBR.0M</v>
       </c>
       <c r="P7" s="61" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="Q7" s="61" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="R7" s="42" t="s">
         <v>191</v>
       </c>
       <c r="S7" s="62" t="str">
         <f t="shared" ref="S7:U19" si="6">SUBSTITUTE(C7, "_", " ")</f>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T7" s="62" t="str">
         <f t="shared" si="6"/>
@@ -6120,7 +6118,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V7" s="42" t="s">
-        <v>529</v>
+        <v>448</v>
       </c>
       <c r="W7" s="66" t="str">
         <f t="shared" si="4"/>
@@ -6136,7 +6134,7 @@
         <v>453</v>
       </c>
       <c r="AA7" s="63" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6144,10 +6142,10 @@
         <v>8</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>516</v>
+        <v>589</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>525</v>
+        <v>590</v>
       </c>
       <c r="D8" s="32" t="s">
         <v>397</v>
@@ -6175,7 +6173,7 @@
       </c>
       <c r="L8" s="61" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M8" s="61" t="str">
         <f t="shared" si="0"/>
@@ -6190,17 +6188,17 @@
         <v>NBR.0P</v>
       </c>
       <c r="P8" s="61" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="Q8" s="61" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="R8" s="42" t="s">
         <v>191</v>
       </c>
       <c r="S8" s="62" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T8" s="62" t="str">
         <f t="shared" si="6"/>
@@ -6211,7 +6209,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V8" s="42" t="s">
-        <v>529</v>
+        <v>448</v>
       </c>
       <c r="W8" s="66" t="str">
         <f t="shared" si="4"/>
@@ -6227,7 +6225,7 @@
         <v>454</v>
       </c>
       <c r="AA8" s="63" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6235,10 +6233,10 @@
         <v>9</v>
       </c>
       <c r="B9" s="58" t="s">
-        <v>516</v>
+        <v>589</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>525</v>
+        <v>590</v>
       </c>
       <c r="D9" s="32" t="s">
         <v>397</v>
@@ -6266,7 +6264,7 @@
       </c>
       <c r="L9" s="61" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M9" s="61" t="str">
         <f t="shared" si="0"/>
@@ -6281,17 +6279,17 @@
         <v>NBR.1D</v>
       </c>
       <c r="P9" s="61" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="Q9" s="61" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="R9" s="42" t="s">
         <v>191</v>
       </c>
       <c r="S9" s="62" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T9" s="62" t="str">
         <f t="shared" si="6"/>
@@ -6302,7 +6300,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V9" s="42" t="s">
-        <v>529</v>
+        <v>448</v>
       </c>
       <c r="W9" s="66" t="str">
         <f t="shared" si="4"/>
@@ -6318,7 +6316,7 @@
         <v>455</v>
       </c>
       <c r="AA9" s="63" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6326,10 +6324,10 @@
         <v>10</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>516</v>
+        <v>589</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>525</v>
+        <v>590</v>
       </c>
       <c r="D10" s="32" t="s">
         <v>397</v>
@@ -6357,7 +6355,7 @@
       </c>
       <c r="L10" s="61" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M10" s="61" t="str">
         <f t="shared" si="0"/>
@@ -6372,17 +6370,17 @@
         <v>NBR.1F</v>
       </c>
       <c r="P10" s="61" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="Q10" s="61" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="R10" s="42" t="s">
         <v>191</v>
       </c>
       <c r="S10" s="62" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T10" s="62" t="str">
         <f t="shared" si="6"/>
@@ -6393,7 +6391,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V10" s="42" t="s">
-        <v>529</v>
+        <v>448</v>
       </c>
       <c r="W10" s="66" t="str">
         <f t="shared" si="4"/>
@@ -6409,7 +6407,7 @@
         <v>369</v>
       </c>
       <c r="AA10" s="63" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6417,10 +6415,10 @@
         <v>11</v>
       </c>
       <c r="B11" s="58" t="s">
-        <v>516</v>
+        <v>589</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>525</v>
+        <v>590</v>
       </c>
       <c r="D11" s="32" t="s">
         <v>397</v>
@@ -6448,7 +6446,7 @@
       </c>
       <c r="L11" s="61" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M11" s="61" t="str">
         <f t="shared" si="0"/>
@@ -6463,17 +6461,17 @@
         <v>NBR.1S</v>
       </c>
       <c r="P11" s="61" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="Q11" s="61" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="R11" s="42" t="s">
         <v>191</v>
       </c>
       <c r="S11" s="62" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T11" s="62" t="str">
         <f t="shared" si="6"/>
@@ -6484,7 +6482,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V11" s="42" t="s">
-        <v>529</v>
+        <v>448</v>
       </c>
       <c r="W11" s="66" t="str">
         <f t="shared" si="4"/>
@@ -6500,7 +6498,7 @@
         <v>456</v>
       </c>
       <c r="AA11" s="63" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6508,10 +6506,10 @@
         <v>12</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>516</v>
+        <v>589</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>525</v>
+        <v>590</v>
       </c>
       <c r="D12" s="32" t="s">
         <v>397</v>
@@ -6539,7 +6537,7 @@
       </c>
       <c r="L12" s="61" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M12" s="61" t="str">
         <f t="shared" si="0"/>
@@ -6554,17 +6552,17 @@
         <v>NBR.2C</v>
       </c>
       <c r="P12" s="61" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="Q12" s="61" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="R12" s="42" t="s">
         <v>191</v>
       </c>
       <c r="S12" s="62" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T12" s="62" t="str">
         <f t="shared" si="6"/>
@@ -6575,7 +6573,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V12" s="42" t="s">
-        <v>529</v>
+        <v>448</v>
       </c>
       <c r="W12" s="66" t="str">
         <f t="shared" si="4"/>
@@ -6591,7 +6589,7 @@
         <v>457</v>
       </c>
       <c r="AA12" s="63" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6599,10 +6597,10 @@
         <v>13</v>
       </c>
       <c r="B13" s="58" t="s">
-        <v>516</v>
+        <v>589</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>525</v>
+        <v>590</v>
       </c>
       <c r="D13" s="32" t="s">
         <v>397</v>
@@ -6630,7 +6628,7 @@
       </c>
       <c r="L13" s="61" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M13" s="61" t="str">
         <f t="shared" si="0"/>
@@ -6645,17 +6643,17 @@
         <v>NBR.2N</v>
       </c>
       <c r="P13" s="61" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="Q13" s="61" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="R13" s="42" t="s">
         <v>191</v>
       </c>
       <c r="S13" s="62" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T13" s="62" t="str">
         <f t="shared" si="6"/>
@@ -6666,7 +6664,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V13" s="42" t="s">
-        <v>529</v>
+        <v>448</v>
       </c>
       <c r="W13" s="66" t="str">
         <f t="shared" si="4"/>
@@ -6682,7 +6680,7 @@
         <v>458</v>
       </c>
       <c r="AA13" s="63" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
     </row>
     <row r="14" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6690,10 +6688,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>516</v>
+        <v>589</v>
       </c>
       <c r="C14" s="32" t="s">
-        <v>525</v>
+        <v>590</v>
       </c>
       <c r="D14" s="32" t="s">
         <v>397</v>
@@ -6721,7 +6719,7 @@
       </c>
       <c r="L14" s="61" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M14" s="61" t="str">
         <f t="shared" si="0"/>
@@ -6736,17 +6734,17 @@
         <v>NBR.2Q</v>
       </c>
       <c r="P14" s="61" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="Q14" s="61" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="R14" s="42" t="s">
         <v>191</v>
       </c>
       <c r="S14" s="62" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T14" s="62" t="str">
         <f t="shared" si="6"/>
@@ -6757,7 +6755,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V14" s="42" t="s">
-        <v>529</v>
+        <v>448</v>
       </c>
       <c r="W14" s="66" t="str">
         <f t="shared" si="4"/>
@@ -6773,7 +6771,7 @@
         <v>459</v>
       </c>
       <c r="AA14" s="63" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6781,10 +6779,10 @@
         <v>15</v>
       </c>
       <c r="B15" s="58" t="s">
-        <v>516</v>
+        <v>589</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>525</v>
+        <v>590</v>
       </c>
       <c r="D15" s="32" t="s">
         <v>397</v>
@@ -6812,7 +6810,7 @@
       </c>
       <c r="L15" s="61" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M15" s="61" t="str">
         <f t="shared" si="0"/>
@@ -6827,17 +6825,17 @@
         <v>NBR.3E</v>
       </c>
       <c r="P15" s="61" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="Q15" s="61" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="R15" s="42" t="s">
         <v>191</v>
       </c>
       <c r="S15" s="62" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T15" s="62" t="str">
         <f t="shared" si="6"/>
@@ -6848,7 +6846,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V15" s="42" t="s">
-        <v>529</v>
+        <v>448</v>
       </c>
       <c r="W15" s="66" t="str">
         <f t="shared" si="4"/>
@@ -6864,7 +6862,7 @@
         <v>460</v>
       </c>
       <c r="AA15" s="63" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6872,10 +6870,10 @@
         <v>16</v>
       </c>
       <c r="B16" s="58" t="s">
-        <v>516</v>
+        <v>589</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>525</v>
+        <v>590</v>
       </c>
       <c r="D16" s="32" t="s">
         <v>397</v>
@@ -6903,7 +6901,7 @@
       </c>
       <c r="L16" s="61" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M16" s="61" t="str">
         <f t="shared" si="0"/>
@@ -6918,17 +6916,17 @@
         <v>NBR.3R</v>
       </c>
       <c r="P16" s="61" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="Q16" s="61" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="R16" s="42" t="s">
         <v>191</v>
       </c>
       <c r="S16" s="62" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T16" s="62" t="str">
         <f t="shared" si="6"/>
@@ -6939,7 +6937,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V16" s="42" t="s">
-        <v>529</v>
+        <v>448</v>
       </c>
       <c r="W16" s="66" t="str">
         <f t="shared" si="4"/>
@@ -6955,7 +6953,7 @@
         <v>461</v>
       </c>
       <c r="AA16" s="63" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
     </row>
     <row r="17" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6963,10 +6961,10 @@
         <v>17</v>
       </c>
       <c r="B17" s="58" t="s">
-        <v>516</v>
+        <v>589</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>525</v>
+        <v>590</v>
       </c>
       <c r="D17" s="32" t="s">
         <v>397</v>
@@ -6994,7 +6992,7 @@
       </c>
       <c r="L17" s="61" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M17" s="61" t="str">
         <f t="shared" si="0"/>
@@ -7009,17 +7007,17 @@
         <v>NBR.4A</v>
       </c>
       <c r="P17" s="61" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="Q17" s="61" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="R17" s="42" t="s">
         <v>191</v>
       </c>
       <c r="S17" s="62" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T17" s="62" t="str">
         <f t="shared" si="6"/>
@@ -7030,7 +7028,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V17" s="42" t="s">
-        <v>529</v>
+        <v>448</v>
       </c>
       <c r="W17" s="66" t="str">
         <f t="shared" si="4"/>
@@ -7046,7 +7044,7 @@
         <v>462</v>
       </c>
       <c r="AA17" s="63" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
     </row>
     <row r="18" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7054,10 +7052,10 @@
         <v>18</v>
       </c>
       <c r="B18" s="58" t="s">
-        <v>516</v>
+        <v>589</v>
       </c>
       <c r="C18" s="32" t="s">
-        <v>525</v>
+        <v>590</v>
       </c>
       <c r="D18" s="32" t="s">
         <v>397</v>
@@ -7085,7 +7083,7 @@
       </c>
       <c r="L18" s="61" t="str">
         <f t="shared" ref="L18:N19" si="7">CONCATENATE("", C18)</f>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M18" s="61" t="str">
         <f t="shared" si="7"/>
@@ -7100,17 +7098,17 @@
         <v>NBR.4U</v>
       </c>
       <c r="P18" s="61" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="Q18" s="61" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="R18" s="42" t="s">
         <v>191</v>
       </c>
       <c r="S18" s="62" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T18" s="62" t="str">
         <f t="shared" si="6"/>
@@ -7121,7 +7119,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V18" s="42" t="s">
-        <v>529</v>
+        <v>448</v>
       </c>
       <c r="W18" s="66" t="str">
         <f t="shared" si="4"/>
@@ -7137,7 +7135,7 @@
         <v>463</v>
       </c>
       <c r="AA18" s="63" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7145,10 +7143,10 @@
         <v>19</v>
       </c>
       <c r="B19" s="58" t="s">
-        <v>516</v>
+        <v>589</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>525</v>
+        <v>590</v>
       </c>
       <c r="D19" s="32" t="s">
         <v>397</v>
@@ -7176,7 +7174,7 @@
       </c>
       <c r="L19" s="61" t="str">
         <f t="shared" si="7"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M19" s="61" t="str">
         <f t="shared" si="7"/>
@@ -7191,17 +7189,17 @@
         <v>NBR.5I</v>
       </c>
       <c r="P19" s="61" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="Q19" s="61" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="R19" s="42" t="s">
         <v>191</v>
       </c>
       <c r="S19" s="62" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T19" s="62" t="str">
         <f t="shared" si="6"/>
@@ -7212,7 +7210,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V19" s="42" t="s">
-        <v>529</v>
+        <v>448</v>
       </c>
       <c r="W19" s="66" t="str">
         <f t="shared" si="4"/>
@@ -7228,7 +7226,7 @@
         <v>464</v>
       </c>
       <c r="AA19" s="63" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
     </row>
     <row r="20" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7236,13 +7234,13 @@
         <v>20</v>
       </c>
       <c r="B20" s="58" t="s">
-        <v>516</v>
+        <v>589</v>
       </c>
       <c r="C20" s="32" t="s">
-        <v>525</v>
+        <v>590</v>
       </c>
       <c r="D20" s="32" t="s">
-        <v>526</v>
+        <v>591</v>
       </c>
       <c r="E20" s="32" t="s">
         <v>494</v>
@@ -7267,11 +7265,11 @@
       </c>
       <c r="L20" s="61" t="str">
         <f t="shared" ref="L20:N27" si="8">CONCATENATE("", C20)</f>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M20" s="61" t="str">
         <f t="shared" si="8"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N20" s="61" t="str">
         <f t="shared" si="8"/>
@@ -7293,11 +7291,11 @@
       </c>
       <c r="S20" s="62" t="str">
         <f t="shared" ref="S20:U22" si="10">SUBSTITUTE(C20, "_", " ")</f>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T20" s="62" t="str">
         <f t="shared" si="10"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U20" s="61" t="str">
         <f t="shared" si="10"/>
@@ -7329,13 +7327,13 @@
         <v>21</v>
       </c>
       <c r="B21" s="58" t="s">
-        <v>516</v>
+        <v>589</v>
       </c>
       <c r="C21" s="32" t="s">
-        <v>525</v>
+        <v>590</v>
       </c>
       <c r="D21" s="32" t="s">
-        <v>526</v>
+        <v>591</v>
       </c>
       <c r="E21" s="32" t="s">
         <v>494</v>
@@ -7360,11 +7358,11 @@
       </c>
       <c r="L21" s="61" t="str">
         <f t="shared" si="8"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M21" s="61" t="str">
         <f t="shared" si="8"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N21" s="61" t="str">
         <f t="shared" si="8"/>
@@ -7386,11 +7384,11 @@
       </c>
       <c r="S21" s="62" t="str">
         <f t="shared" si="10"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T21" s="62" t="str">
         <f t="shared" si="10"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U21" s="61" t="str">
         <f t="shared" si="10"/>
@@ -7422,13 +7420,13 @@
         <v>22</v>
       </c>
       <c r="B22" s="58" t="s">
-        <v>516</v>
+        <v>589</v>
       </c>
       <c r="C22" s="32" t="s">
-        <v>525</v>
+        <v>590</v>
       </c>
       <c r="D22" s="32" t="s">
-        <v>526</v>
+        <v>591</v>
       </c>
       <c r="E22" s="32" t="s">
         <v>494</v>
@@ -7453,11 +7451,11 @@
       </c>
       <c r="L22" s="61" t="str">
         <f t="shared" si="8"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M22" s="61" t="str">
         <f t="shared" si="8"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N22" s="61" t="str">
         <f t="shared" si="8"/>
@@ -7479,11 +7477,11 @@
       </c>
       <c r="S22" s="62" t="str">
         <f t="shared" si="10"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T22" s="62" t="str">
         <f t="shared" si="10"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U22" s="61" t="str">
         <f t="shared" si="10"/>
@@ -7515,13 +7513,13 @@
         <v>23</v>
       </c>
       <c r="B23" s="58" t="s">
-        <v>516</v>
+        <v>589</v>
       </c>
       <c r="C23" s="32" t="s">
-        <v>525</v>
+        <v>590</v>
       </c>
       <c r="D23" s="32" t="s">
-        <v>526</v>
+        <v>591</v>
       </c>
       <c r="E23" s="32" t="s">
         <v>494</v>
@@ -7546,11 +7544,11 @@
       </c>
       <c r="L23" s="61" t="str">
         <f t="shared" si="8"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M23" s="61" t="str">
         <f t="shared" si="8"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N23" s="61" t="str">
         <f t="shared" si="8"/>
@@ -7572,11 +7570,11 @@
       </c>
       <c r="S23" s="62" t="str">
         <f t="shared" ref="S23:U27" si="13">SUBSTITUTE(C23, "_", " ")</f>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T23" s="62" t="str">
         <f t="shared" si="13"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U23" s="61" t="str">
         <f t="shared" si="13"/>
@@ -7608,13 +7606,13 @@
         <v>24</v>
       </c>
       <c r="B24" s="58" t="s">
-        <v>516</v>
+        <v>589</v>
       </c>
       <c r="C24" s="32" t="s">
-        <v>525</v>
+        <v>590</v>
       </c>
       <c r="D24" s="32" t="s">
-        <v>526</v>
+        <v>591</v>
       </c>
       <c r="E24" s="32" t="s">
         <v>494</v>
@@ -7639,11 +7637,11 @@
       </c>
       <c r="L24" s="61" t="str">
         <f t="shared" si="8"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M24" s="61" t="str">
         <f t="shared" si="8"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N24" s="61" t="str">
         <f t="shared" si="8"/>
@@ -7665,11 +7663,11 @@
       </c>
       <c r="S24" s="62" t="str">
         <f t="shared" si="13"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T24" s="62" t="str">
         <f t="shared" si="13"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U24" s="61" t="str">
         <f t="shared" si="13"/>
@@ -7701,13 +7699,13 @@
         <v>25</v>
       </c>
       <c r="B25" s="58" t="s">
-        <v>516</v>
+        <v>589</v>
       </c>
       <c r="C25" s="32" t="s">
-        <v>525</v>
+        <v>590</v>
       </c>
       <c r="D25" s="32" t="s">
-        <v>526</v>
+        <v>591</v>
       </c>
       <c r="E25" s="32" t="s">
         <v>494</v>
@@ -7732,11 +7730,11 @@
       </c>
       <c r="L25" s="61" t="str">
         <f t="shared" si="8"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M25" s="61" t="str">
         <f t="shared" si="8"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N25" s="61" t="str">
         <f t="shared" si="8"/>
@@ -7758,11 +7756,11 @@
       </c>
       <c r="S25" s="62" t="str">
         <f t="shared" si="13"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T25" s="62" t="str">
         <f t="shared" si="13"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U25" s="61" t="str">
         <f t="shared" si="13"/>
@@ -7794,13 +7792,13 @@
         <v>26</v>
       </c>
       <c r="B26" s="58" t="s">
-        <v>516</v>
+        <v>589</v>
       </c>
       <c r="C26" s="32" t="s">
-        <v>525</v>
+        <v>590</v>
       </c>
       <c r="D26" s="32" t="s">
-        <v>526</v>
+        <v>591</v>
       </c>
       <c r="E26" s="32" t="s">
         <v>494</v>
@@ -7825,11 +7823,11 @@
       </c>
       <c r="L26" s="61" t="str">
         <f t="shared" si="8"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M26" s="61" t="str">
         <f t="shared" si="8"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N26" s="61" t="str">
         <f t="shared" si="8"/>
@@ -7851,11 +7849,11 @@
       </c>
       <c r="S26" s="62" t="str">
         <f t="shared" si="13"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T26" s="62" t="str">
         <f t="shared" si="13"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U26" s="61" t="str">
         <f t="shared" si="13"/>
@@ -7887,13 +7885,13 @@
         <v>27</v>
       </c>
       <c r="B27" s="58" t="s">
-        <v>516</v>
+        <v>589</v>
       </c>
       <c r="C27" s="32" t="s">
-        <v>525</v>
+        <v>590</v>
       </c>
       <c r="D27" s="32" t="s">
-        <v>526</v>
+        <v>591</v>
       </c>
       <c r="E27" s="32" t="s">
         <v>494</v>
@@ -7918,11 +7916,11 @@
       </c>
       <c r="L27" s="61" t="str">
         <f t="shared" si="8"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M27" s="61" t="str">
         <f t="shared" si="8"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N27" s="61" t="str">
         <f t="shared" si="8"/>
@@ -7944,11 +7942,11 @@
       </c>
       <c r="S27" s="62" t="str">
         <f t="shared" si="13"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T27" s="62" t="str">
         <f t="shared" si="13"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U27" s="61" t="str">
         <f t="shared" si="13"/>
@@ -8316,7 +8314,7 @@
         <v>367</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>525</v>
+        <v>590</v>
       </c>
       <c r="D2" s="64" t="s">
         <v>191</v>
